--- a/research/traditional_assets/database/data/germany/germany_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ43"/>
+  <dimension ref="A1:AQ42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.11425</v>
+        <v>0.08865000000000001</v>
       </c>
       <c r="E2">
-        <v>0.186</v>
+        <v>0.205</v>
       </c>
       <c r="F2">
-        <v>-0.07049999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="G2">
-        <v>0.100792381216572</v>
+        <v>0.1132358172111711</v>
       </c>
       <c r="H2">
-        <v>0.09522954964497905</v>
+        <v>0.1074716911396</v>
       </c>
       <c r="I2">
-        <v>0.09903813354592181</v>
+        <v>0.05921890461852366</v>
       </c>
       <c r="J2">
-        <v>0.08898338767417732</v>
+        <v>0.05243150751464514</v>
       </c>
       <c r="K2">
-        <v>1858.517</v>
+        <v>999.2329999999999</v>
       </c>
       <c r="L2">
-        <v>0.1299278269233163</v>
+        <v>0.07506457691742831</v>
       </c>
       <c r="M2">
-        <v>133.87485</v>
+        <v>128.46371</v>
       </c>
       <c r="N2">
-        <v>0.009155907480195008</v>
+        <v>0.01113334065365885</v>
       </c>
       <c r="O2">
-        <v>0.07203315869588495</v>
+        <v>0.1285623172973671</v>
       </c>
       <c r="P2">
-        <v>130.67785</v>
+        <v>128.14771</v>
       </c>
       <c r="Q2">
-        <v>0.00893725971913919</v>
+        <v>0.011105954431927</v>
       </c>
       <c r="R2">
-        <v>0.07031296996476223</v>
+        <v>0.1282460747393251</v>
       </c>
       <c r="S2">
-        <v>3.197000000000001</v>
+        <v>0.3159999999999989</v>
       </c>
       <c r="T2">
-        <v>0.02388051228442086</v>
+        <v>0.00245983865793693</v>
       </c>
       <c r="U2">
-        <v>5535.673</v>
+        <v>2486.338</v>
       </c>
       <c r="V2">
-        <v>0.3785932146972604</v>
+        <v>0.2154791258491354</v>
       </c>
       <c r="W2">
-        <v>0.1618729096989966</v>
+        <v>0.001943402147206495</v>
       </c>
       <c r="X2">
-        <v>0.04409381800658754</v>
+        <v>0.07347764511358229</v>
       </c>
       <c r="Y2">
-        <v>0.1177790916924091</v>
+        <v>-0.0715342429663758</v>
       </c>
       <c r="Z2">
-        <v>1.638129420417204</v>
+        <v>1.282149588602843</v>
       </c>
       <c r="AA2">
-        <v>0.08344661845101325</v>
+        <v>-0.008457387843040842</v>
       </c>
       <c r="AB2">
-        <v>0.04380391651249452</v>
+        <v>0.07182240185627822</v>
       </c>
       <c r="AC2">
-        <v>0.03957365435953098</v>
+        <v>-0.07768284985717794</v>
       </c>
       <c r="AD2">
-        <v>1968.653</v>
+        <v>2170.429</v>
       </c>
       <c r="AE2">
-        <v>28.15577570476596</v>
+        <v>18.99482214676379</v>
       </c>
       <c r="AF2">
-        <v>1996.808775704766</v>
+        <v>2189.423822146764</v>
       </c>
       <c r="AG2">
-        <v>-3538.864224295234</v>
+        <v>-296.9141778532367</v>
       </c>
       <c r="AH2">
-        <v>0.1201557783587649</v>
+        <v>0.1594851550186042</v>
       </c>
       <c r="AI2">
-        <v>0.1315401843154307</v>
+        <v>0.1540918455624718</v>
       </c>
       <c r="AJ2">
-        <v>-0.3193106141524255</v>
+        <v>-0.02641177563344595</v>
       </c>
       <c r="AK2">
-        <v>-0.3669290712694693</v>
+        <v>-0.02532916379176706</v>
       </c>
       <c r="AL2">
-        <v>150.037</v>
+        <v>128.711</v>
       </c>
       <c r="AM2">
-        <v>97.97500000000001</v>
+        <v>80.227</v>
       </c>
       <c r="AN2">
-        <v>1.244107301523905</v>
+        <v>1.915450037374781</v>
       </c>
       <c r="AO2">
-        <v>9.447169698141124</v>
+        <v>6.125684673415637</v>
       </c>
       <c r="AP2">
-        <v>-2.236415874482415</v>
+        <v>-0.2620331156034519</v>
       </c>
       <c r="AQ2">
-        <v>14.46721102322021</v>
+        <v>9.827651538758772</v>
       </c>
     </row>
     <row r="3">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.683982683982684</v>
+        <v>0.6616702355460384</v>
       </c>
       <c r="H3">
-        <v>0.683982683982684</v>
+        <v>0.6616702355460384</v>
       </c>
       <c r="I3">
-        <v>0.2965367965367965</v>
+        <v>0.2462526766595289</v>
       </c>
       <c r="J3">
-        <v>0.2265674400505861</v>
+        <v>0.1231263383297644</v>
       </c>
       <c r="K3">
-        <v>6.12</v>
+        <v>-0.767</v>
       </c>
       <c r="L3">
-        <v>0.1324675324675325</v>
+        <v>-0.01642398286937901</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,7 +758,7 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,10 +770,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB3">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,22 +794,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>10.3</v>
+        <v>9.82</v>
       </c>
       <c r="AM3">
-        <v>9.615</v>
+        <v>8.77</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>1.330097087378641</v>
+        <v>1.171079429735234</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>1.424856994279771</v>
+        <v>1.311288483466363</v>
       </c>
     </row>
     <row r="4">
@@ -820,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Netfonds AG (DB:NF4)</t>
+          <t>MLP SE (XTRA:MLP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -828,59 +828,71 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.09</v>
+      </c>
+      <c r="E4">
+        <v>0.323</v>
+      </c>
       <c r="G4">
-        <v>0.02778091473743648</v>
+        <v>0.1204989384288747</v>
       </c>
       <c r="H4">
-        <v>0.02778091473743648</v>
+        <v>0.1192144373673036</v>
       </c>
       <c r="I4">
-        <v>0.01174477696216827</v>
+        <v>0.09915074309978769</v>
       </c>
       <c r="J4">
-        <v>0.005872388481084134</v>
+        <v>0.06671443188964044</v>
       </c>
       <c r="K4">
-        <v>0.093</v>
+        <v>64.5</v>
       </c>
       <c r="L4">
-        <v>0.0005251270468661773</v>
+        <v>0.06847133757961783</v>
       </c>
       <c r="M4">
-        <v>0.4351200000000001</v>
+        <v>25.016</v>
       </c>
       <c r="N4">
-        <v>0.004032622798887859</v>
+        <v>0.04167249708479094</v>
       </c>
       <c r="O4">
-        <v>4.678709677419356</v>
+        <v>0.38784496124031</v>
       </c>
       <c r="P4">
-        <v>0.4351200000000001</v>
+        <v>24.7</v>
       </c>
       <c r="Q4">
-        <v>0.004032622798887859</v>
+        <v>0.04114609361985674</v>
       </c>
       <c r="R4">
-        <v>4.678709677419356</v>
+        <v>0.3829457364341085</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.3159999999999989</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.01263191557403258</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>978</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.629185407296352</v>
+      </c>
+      <c r="W4">
+        <v>0.1205832865956254</v>
       </c>
       <c r="X4">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y4">
+        <v>0.0481290675549205</v>
       </c>
       <c r="AB4">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -892,31 +904,37 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>-978</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>2.589356632247815</v>
+      </c>
+      <c r="AK4">
+        <v>2.051174496644295</v>
       </c>
       <c r="AL4">
-        <v>1.28</v>
+        <v>5.09</v>
       </c>
       <c r="AM4">
-        <v>1.259</v>
+        <v>2.82</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>1.625</v>
+        <v>18.34970530451866</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>-9.504373177842565</v>
       </c>
       <c r="AQ4">
-        <v>1.652104845115171</v>
+        <v>33.12056737588653</v>
       </c>
     </row>
     <row r="5">
@@ -927,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Elbstein AG (HMSE:EBS)</t>
+          <t>Netfonds AG (DB:NF4)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -936,46 +954,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.365</v>
+        <v>0.225</v>
       </c>
       <c r="E5">
-        <v>0.414</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="G5">
-        <v>0.7633410672853829</v>
+        <v>0.07825295723384895</v>
       </c>
       <c r="H5">
-        <v>0.7633410672853829</v>
+        <v>0.07825295723384895</v>
       </c>
       <c r="I5">
-        <v>0.7633410672853829</v>
+        <v>0.06005459508644222</v>
       </c>
       <c r="J5">
-        <v>0.7628998296742352</v>
+        <v>0.05536143969264988</v>
       </c>
       <c r="K5">
-        <v>3.46</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L5">
-        <v>0.8027842227378191</v>
+        <v>0.04344858962693358</v>
       </c>
       <c r="M5">
-        <v>1.83</v>
+        <v>0.62764</v>
       </c>
       <c r="N5">
-        <v>0.01995637949836423</v>
+        <v>0.006606736842105263</v>
       </c>
       <c r="O5">
-        <v>0.5289017341040463</v>
+        <v>0.06572146596858638</v>
       </c>
       <c r="P5">
-        <v>1.83</v>
+        <v>0.62764</v>
       </c>
       <c r="Q5">
-        <v>0.01995637949836423</v>
+        <v>0.006606736842105263</v>
       </c>
       <c r="R5">
-        <v>0.5289017341040463</v>
+        <v>0.06572146596858638</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -990,10 +1008,10 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB5">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1014,22 +1032,22 @@
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>0.049</v>
+        <v>2.93</v>
       </c>
       <c r="AM5">
-        <v>-0.171</v>
+        <v>2.108</v>
       </c>
       <c r="AN5">
         <v>0</v>
       </c>
       <c r="AO5">
-        <v>67.14285714285714</v>
+        <v>4.505119453924914</v>
       </c>
       <c r="AP5">
         <v>0</v>
       </c>
       <c r="AQ5">
-        <v>-19.23976608187135</v>
+        <v>6.261859582542693</v>
       </c>
     </row>
     <row r="6">
@@ -1049,22 +1067,22 @@
         </is>
       </c>
       <c r="G6">
-        <v>0.05107351984385166</v>
+        <v>0.0513787281935847</v>
       </c>
       <c r="H6">
-        <v>0.05107351984385166</v>
+        <v>0.0513787281935847</v>
       </c>
       <c r="I6">
-        <v>0.05335068314899154</v>
+        <v>0.04890264490714688</v>
       </c>
       <c r="J6">
-        <v>0.03706039821800176</v>
+        <v>0.0351504950457445</v>
       </c>
       <c r="K6">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="L6">
-        <v>0.01984385165907612</v>
+        <v>0.01710748452447946</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1094,52 +1112,52 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>0.04440499248411723</v>
+        <v>0.07493330833489958</v>
       </c>
       <c r="AB6">
-        <v>0.0436827902959593</v>
+        <v>0.07095114655702905</v>
       </c>
       <c r="AD6">
-        <v>1.54</v>
+        <v>5.63</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.54</v>
+        <v>5.63</v>
       </c>
       <c r="AG6">
-        <v>1.54</v>
+        <v>5.63</v>
       </c>
       <c r="AH6">
-        <v>0.02573529411764706</v>
+        <v>0.09521393539658379</v>
       </c>
       <c r="AI6">
-        <v>0.06405990016638935</v>
+        <v>0.2090605272929818</v>
       </c>
       <c r="AJ6">
-        <v>0.02573529411764706</v>
+        <v>0.09521393539658379</v>
       </c>
       <c r="AK6">
-        <v>0.06405990016638935</v>
+        <v>0.2090605272929818</v>
       </c>
       <c r="AL6">
-        <v>0.163</v>
+        <v>0.091</v>
       </c>
       <c r="AM6">
-        <v>-0.834</v>
+        <v>0.091</v>
       </c>
       <c r="AN6">
-        <v>0.183115338882283</v>
+        <v>0.6269487750556793</v>
       </c>
       <c r="AO6">
-        <v>50.30674846625767</v>
+        <v>95.49450549450549</v>
       </c>
       <c r="AP6">
-        <v>0.183115338882283</v>
+        <v>0.6269487750556793</v>
       </c>
       <c r="AQ6">
-        <v>-9.832134292565947</v>
+        <v>95.49450549450549</v>
       </c>
     </row>
     <row r="7">
@@ -1150,7 +1168,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PEH Wertpapier AG (DB:PEH)</t>
+          <t>U.C.A. Aktiengesellschaft (DB:UCA1)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1158,48 +1176,36 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.143</v>
-      </c>
-      <c r="G7">
-        <v>0.05674019607843137</v>
-      </c>
-      <c r="H7">
-        <v>0.05674019607843137</v>
-      </c>
-      <c r="I7">
-        <v>0.07475490196078431</v>
-      </c>
-      <c r="J7">
-        <v>0.05003755534471854</v>
+      <c r="E7">
+        <v>0.507</v>
       </c>
       <c r="K7">
-        <v>5.09</v>
-      </c>
-      <c r="L7">
-        <v>0.03118872549019608</v>
+        <v>3.02</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>2.12443</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.1136058823529412</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.703453642384106</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>2.12443</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.1136058823529412</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.703453642384106</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
         <v>0</v>
       </c>
@@ -1207,52 +1213,43 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>0.04477742816022075</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB7">
-        <v>0.04355538433949074</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD7">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>0.04297652208515718</v>
-      </c>
-      <c r="AI7">
-        <v>0.06758448060075094</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0.04297652208515718</v>
-      </c>
-      <c r="AK7">
-        <v>0.06758448060075094</v>
+        <v>0</v>
       </c>
       <c r="AL7">
-        <v>0.114</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.205</v>
+        <v>-0.293</v>
       </c>
       <c r="AN7">
-        <v>0.1741935483870968</v>
-      </c>
-      <c r="AO7">
-        <v>107.0175438596491</v>
+        <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.1741935483870968</v>
+        <v>0</v>
       </c>
       <c r="AQ7">
-        <v>-59.51219512195121</v>
+        <v>-5.972696245733789</v>
       </c>
     </row>
     <row r="8">
@@ -1263,7 +1260,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.C.A. Aktiengesellschaft (DB:UCA1)</t>
+          <t>Camerit AG (DB:RTML)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1271,47 +1268,65 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="E8">
-        <v>0.679</v>
+      <c r="D8">
+        <v>-0.0349</v>
+      </c>
+      <c r="G8">
+        <v>0.1468085106382979</v>
+      </c>
+      <c r="H8">
+        <v>0.1468085106382979</v>
+      </c>
+      <c r="I8">
+        <v>0.3691489361702128</v>
+      </c>
+      <c r="J8">
+        <v>0.3691489361702128</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>0.498</v>
+      </c>
+      <c r="L8">
+        <v>0.5297872340425532</v>
       </c>
       <c r="M8">
-        <v>2.43593</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.1345817679558011</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.8119766666666667</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>2.43593</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.1345817679558011</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.8119766666666667</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.714285714285714</v>
+      </c>
+      <c r="W8">
+        <v>0.05790697674418605</v>
       </c>
       <c r="X8">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y8">
+        <v>-0.0145472422965188</v>
       </c>
       <c r="AB8">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1323,31 +1338,31 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>-7.32</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>2.399999999999999</v>
+      </c>
+      <c r="AK8">
+        <v>-73.20000000000026</v>
       </c>
       <c r="AL8">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.207</v>
+        <v>0</v>
       </c>
       <c r="AN8">
         <v>0</v>
       </c>
-      <c r="AO8">
-        <v>281.6666666666666</v>
-      </c>
       <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>-16.32850241545894</v>
+        <v>-21.03448275862069</v>
       </c>
     </row>
     <row r="9">
@@ -1358,7 +1373,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cash.life AG (DUSE:SGS)</t>
+          <t>Ernst Russ AG (XTRA:HXCK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1367,25 +1382,28 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.104</v>
+        <v>0.306</v>
+      </c>
+      <c r="E9">
+        <v>0.408</v>
       </c>
       <c r="G9">
-        <v>0.2297709923664122</v>
+        <v>0.2167789344764237</v>
       </c>
       <c r="H9">
-        <v>0.2297709923664122</v>
+        <v>0.2167789344764237</v>
       </c>
       <c r="I9">
-        <v>0.2251908396946565</v>
+        <v>0.4816488804012926</v>
       </c>
       <c r="J9">
-        <v>0.2251908396946565</v>
+        <v>0.478412199924996</v>
       </c>
       <c r="K9">
-        <v>1.7</v>
+        <v>38.2</v>
       </c>
       <c r="L9">
-        <v>1.297709923664122</v>
+        <v>0.2339252908756889</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1414,47 +1432,68 @@
       <c r="V9">
         <v>0</v>
       </c>
+      <c r="W9">
+        <v>0.5387870239774331</v>
+      </c>
       <c r="X9">
-        <v>0.04387296409148227</v>
+        <v>0.08247681606071629</v>
+      </c>
+      <c r="Y9">
+        <v>0.4563102079167168</v>
+      </c>
+      <c r="Z9">
+        <v>1.133447758301832</v>
+      </c>
+      <c r="AA9">
+        <v>0.5422552355492346</v>
       </c>
       <c r="AB9">
-        <v>0.04387296409148227</v>
+        <v>0.06935130438727968</v>
+      </c>
+      <c r="AC9">
+        <v>0.4729039311619549</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>64.7</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.073689152344619</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>65.77368915234462</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>65.77368915234462</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.2984643466529037</v>
+      </c>
+      <c r="AI9">
+        <v>0.2593868842316224</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>0.2984643466529037</v>
+      </c>
+      <c r="AK9">
+        <v>0.2593868842316224</v>
       </c>
       <c r="AL9">
-        <v>0.257</v>
+        <v>2.84</v>
       </c>
       <c r="AM9">
-        <v>-0.527</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>0.7413943255259661</v>
       </c>
       <c r="AO9">
-        <v>1.147859922178988</v>
+        <v>27.42957746478874</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>0.7536976801616242</v>
       </c>
       <c r="AQ9">
-        <v>-0.5597722960151802</v>
+        <v>-3894.999999999997</v>
       </c>
     </row>
     <row r="10">
@@ -1465,7 +1504,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DLB-Anlageservice AG (BST:DLB)</t>
+          <t>PEH Wertpapier AG (DB:PEH)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1474,100 +1513,115 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.161</v>
-      </c>
-      <c r="E10">
-        <v>-0.0178</v>
+        <v>0.175</v>
       </c>
       <c r="G10">
-        <v>0.07624633431085043</v>
+        <v>0.07085346215780998</v>
       </c>
       <c r="H10">
-        <v>0.07624633431085043</v>
+        <v>0.07085346215780998</v>
       </c>
       <c r="I10">
-        <v>0.07038123167155425</v>
+        <v>0.05421363392377885</v>
       </c>
       <c r="J10">
-        <v>0.06907441835139276</v>
+        <v>0.04011808910359635</v>
       </c>
       <c r="K10">
-        <v>0.369</v>
+        <v>4.3</v>
       </c>
       <c r="L10">
-        <v>1.082111436950147</v>
+        <v>0.02308105206655931</v>
       </c>
       <c r="M10">
-        <v>0.367</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.03528846153846154</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.994579945799458</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>0.367</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.03528846153846154</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.994579945799458</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
         <v>0</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
+      <c r="W10">
+        <v>0.2402234636871508</v>
+      </c>
       <c r="X10">
-        <v>0.04387296409148227</v>
+        <v>0.07693470320223161</v>
+      </c>
+      <c r="Y10">
+        <v>0.1632887604849192</v>
+      </c>
+      <c r="Z10">
+        <v>9.287138584247259</v>
+      </c>
+      <c r="AA10">
+        <v>0.3725822532402792</v>
       </c>
       <c r="AB10">
-        <v>0.04387296409148227</v>
+        <v>0.06993160651929059</v>
+      </c>
+      <c r="AC10">
+        <v>0.3026506467209886</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.1597979260834884</v>
+      </c>
+      <c r="AI10">
+        <v>0.1798862615983239</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>0.1597979260834884</v>
+      </c>
+      <c r="AK10">
+        <v>0.1798862615983239</v>
       </c>
       <c r="AL10">
-        <v>0.001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AM10">
-        <v>-0.075</v>
+        <v>-1.3</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>0.5778846153846153</v>
       </c>
       <c r="AO10">
-        <v>24</v>
+        <v>144.2857142857143</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>0.5778846153846153</v>
       </c>
       <c r="AQ10">
-        <v>-0.32</v>
+        <v>-7.769230769230768</v>
       </c>
     </row>
     <row r="11">
@@ -1578,7 +1632,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SCI AG (HMSE:SCI)</t>
+          <t>OVB Holding AG (XTRA:O4B)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1587,91 +1641,124 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0222</v>
+        <v>0.0873</v>
+      </c>
+      <c r="E11">
+        <v>0.034</v>
+      </c>
+      <c r="F11">
+        <v>0.111</v>
       </c>
       <c r="G11">
-        <v>0.09929577464788733</v>
+        <v>0.0751145038167939</v>
       </c>
       <c r="H11">
-        <v>0.09929577464788733</v>
+        <v>0.0751145038167939</v>
       </c>
       <c r="I11">
-        <v>0.09906103286384976</v>
+        <v>0.05587786259541985</v>
       </c>
       <c r="J11">
-        <v>0.09906103286384976</v>
+        <v>0.03650880037970178</v>
       </c>
       <c r="K11">
-        <v>-0.181</v>
+        <v>12.3</v>
       </c>
       <c r="L11">
-        <v>-0.04248826291079812</v>
+        <v>0.03755725190839695</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>16.1</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.048045359594151</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.308943089430894</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>16.1</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.048045359594151</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.308943089430894</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>0</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>0.2539540435690838</v>
+      </c>
+      <c r="W11">
+        <v>0.121301775147929</v>
       </c>
       <c r="X11">
-        <v>0.04387296409148227</v>
+        <v>0.0731783220525923</v>
+      </c>
+      <c r="Y11">
+        <v>0.04812345309533669</v>
+      </c>
+      <c r="Z11">
+        <v>9.022038567493111</v>
+      </c>
+      <c r="AA11">
+        <v>0.3293838050785765</v>
       </c>
       <c r="AB11">
-        <v>0.04387296409148227</v>
+        <v>0.07198346473602688</v>
+      </c>
+      <c r="AC11">
+        <v>0.2574003403425497</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>-74.8</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.02982049797336421</v>
+      </c>
+      <c r="AI11">
+        <v>0.1074035453597498</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>-0.2873607376104494</v>
+      </c>
+      <c r="AK11">
+        <v>-6.925925925925927</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="AM11">
-        <v>-0.133</v>
+        <v>-0.9219999999999999</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>0.4858490566037736</v>
+      </c>
+      <c r="AO11">
+        <v>57.54716981132076</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>-3.528301886792453</v>
       </c>
       <c r="AQ11">
-        <v>-3.172932330827067</v>
+        <v>-19.84815618221258</v>
       </c>
     </row>
     <row r="12">
@@ -1682,7 +1769,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Beteiligungen im Baltikum AG (MUN:BI7)</t>
+          <t>Shareholder Value Beteiligungen AG (XTRA:SVE)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1691,7 +1778,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0519</v>
+        <v>0.197</v>
+      </c>
+      <c r="E12">
+        <v>0.133</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1700,16 +1790,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.3126582278481013</v>
+        <v>0.846473029045643</v>
       </c>
       <c r="J12">
-        <v>0.3126582278481013</v>
+        <v>0.846473029045643</v>
       </c>
       <c r="K12">
-        <v>0.016</v>
+        <v>19.2</v>
       </c>
       <c r="L12">
-        <v>0.02025316455696203</v>
+        <v>0.7966804979253111</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1733,16 +1823,31 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>0.1105076741440378</v>
+      </c>
+      <c r="W12">
+        <v>0.2181818181818182</v>
       </c>
       <c r="X12">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y12">
+        <v>0.1457275991411133</v>
+      </c>
+      <c r="Z12">
+        <v>0.2735683069413701</v>
+      </c>
+      <c r="AA12">
+        <v>0.2315681934275498</v>
       </c>
       <c r="AB12">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AC12">
+        <v>0.1591139743868449</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -1754,25 +1859,28 @@
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>-0.1242367932041412</v>
+      </c>
+      <c r="AK12">
+        <v>-0.1070448307410796</v>
       </c>
       <c r="AL12">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>0.08</v>
-      </c>
-      <c r="AO12">
-        <v>2.775280898876404</v>
+        <v>-0.787</v>
       </c>
       <c r="AQ12">
-        <v>3.0875</v>
+        <v>-25.92121982210927</v>
       </c>
     </row>
     <row r="13">
@@ -1783,7 +1891,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deutsche Effecten- und Wechsel-Beteiligungsgesellschaft AG (XTRA:EFF)</t>
+          <t>DWS Group GmbH &amp; Co. KGaA (XTRA:DWS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1791,26 +1899,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D13">
-        <v>3.465</v>
+      <c r="F13">
+        <v>0.083</v>
       </c>
       <c r="G13">
-        <v>0.3023809523809524</v>
+        <v>0.3389851546596495</v>
       </c>
       <c r="H13">
-        <v>0.3023809523809524</v>
+        <v>0.3292041110173278</v>
       </c>
       <c r="I13">
-        <v>0.9418759046086462</v>
+        <v>0.270939873889082</v>
       </c>
       <c r="J13">
-        <v>0.9418759046086462</v>
+        <v>0.1906508034321198</v>
       </c>
       <c r="K13">
-        <v>13.8</v>
+        <v>731.5</v>
       </c>
       <c r="L13">
-        <v>0.8214285714285714</v>
+        <v>0.181594756963408</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1834,73 +1942,73 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>0.1330049261083744</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.2</v>
+        <v>0.08887997861534348</v>
       </c>
       <c r="X13">
-        <v>0.05128320486289022</v>
+        <v>0.07308080476559012</v>
       </c>
       <c r="Y13">
-        <v>1.14871679513711</v>
+        <v>0.01579917384975336</v>
       </c>
       <c r="Z13">
-        <v>0.5453408027163243</v>
+        <v>0.6931667613098617</v>
       </c>
       <c r="AA13">
-        <v>0.5136433618784432</v>
+        <v>0.1321527999561655</v>
       </c>
       <c r="AB13">
-        <v>0.04275485541462525</v>
+        <v>0.07204522018723547</v>
       </c>
       <c r="AC13">
-        <v>0.4708885064638179</v>
+        <v>0.06010757976893005</v>
       </c>
       <c r="AD13">
-        <v>14.9</v>
+        <v>172.6</v>
       </c>
       <c r="AE13">
-        <v>0.0374240128737171</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>14.93742401287372</v>
+        <v>172.6</v>
       </c>
       <c r="AG13">
-        <v>9.537424012873718</v>
+        <v>172.6</v>
       </c>
       <c r="AH13">
-        <v>0.2689614125676982</v>
+        <v>0.02590852459508548</v>
       </c>
       <c r="AI13">
-        <v>0.3648843172979399</v>
+        <v>0.02241674892202192</v>
       </c>
       <c r="AJ13">
-        <v>0.1902256488172349</v>
+        <v>0.02590852459508548</v>
       </c>
       <c r="AK13">
-        <v>0.2683769090696813</v>
+        <v>0.02241674892202192</v>
       </c>
       <c r="AL13">
-        <v>0.78</v>
+        <v>19.6</v>
       </c>
       <c r="AM13">
-        <v>0.749</v>
+        <v>19.6</v>
       </c>
       <c r="AN13">
-        <v>0.9411913334596677</v>
+        <v>0.1520704845814978</v>
       </c>
       <c r="AO13">
-        <v>20.25641025641026</v>
+        <v>55.68367346938776</v>
       </c>
       <c r="AP13">
-        <v>0.6024524043252932</v>
+        <v>0.1520704845814978</v>
       </c>
       <c r="AQ13">
-        <v>21.09479305740988</v>
+        <v>55.68367346938776</v>
       </c>
     </row>
     <row r="14">
@@ -1911,7 +2019,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lloyd Fonds AG (XTRA:L1OA)</t>
+          <t>KST Beteiligungs AG (DB:KSW)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1920,118 +2028,121 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.282</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="E14">
-        <v>0.21</v>
+        <v>-0.447</v>
       </c>
       <c r="G14">
-        <v>0.1346072186836518</v>
+        <v>1.564885496183206</v>
       </c>
       <c r="H14">
-        <v>0.1346072186836518</v>
+        <v>1.564885496183206</v>
       </c>
       <c r="I14">
-        <v>0.3121019108280255</v>
+        <v>0.9847328244274809</v>
       </c>
       <c r="J14">
-        <v>0.3121019108280255</v>
+        <v>0.7135745104546964</v>
       </c>
       <c r="K14">
-        <v>8.220000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="L14">
-        <v>0.1745222929936306</v>
+        <v>0.03816793893129771</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>0.3416399999999999</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.05466239999999999</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>6.832799999999999</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>0.3416399999999999</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.05466239999999999</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>6.832799999999999</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>8.029999999999999</v>
+        <v>1.38</v>
       </c>
       <c r="V14">
-        <v>0.03518843120070114</v>
+        <v>0.2208</v>
       </c>
       <c r="W14">
-        <v>0.2135064935064935</v>
+        <v>0.005875440658049355</v>
       </c>
       <c r="X14">
-        <v>0.04578821967671284</v>
+        <v>0.08470435477152141</v>
       </c>
       <c r="Y14">
-        <v>0.1677182738297807</v>
+        <v>-0.07882891411347205</v>
       </c>
       <c r="Z14">
-        <v>1.429004854368932</v>
+        <v>0.137590589223821</v>
       </c>
       <c r="AA14">
-        <v>0.4459951456310679</v>
+        <v>0.09818113734856131</v>
       </c>
       <c r="AB14">
-        <v>0.0432312892440034</v>
+        <v>0.06705365445494829</v>
       </c>
       <c r="AC14">
-        <v>0.4027638563870645</v>
+        <v>0.03112748289361301</v>
       </c>
       <c r="AD14">
-        <v>21.7</v>
+        <v>3.25</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>21.7</v>
+        <v>3.25</v>
       </c>
       <c r="AG14">
-        <v>13.67</v>
+        <v>1.87</v>
       </c>
       <c r="AH14">
-        <v>0.08683473389355743</v>
+        <v>0.3421052631578947</v>
       </c>
       <c r="AI14">
-        <v>0.279639175257732</v>
+        <v>0.3266331658291458</v>
       </c>
       <c r="AJ14">
-        <v>0.05651796419564229</v>
+        <v>0.2302955665024631</v>
       </c>
       <c r="AK14">
-        <v>0.1964927411240477</v>
+        <v>0.2182030338389732</v>
       </c>
       <c r="AL14">
-        <v>14.8</v>
+        <v>0.032</v>
       </c>
       <c r="AM14">
-        <v>13.7</v>
+        <v>-0.382</v>
       </c>
       <c r="AN14">
-        <v>1.212290502793296</v>
+        <v>2.5</v>
       </c>
       <c r="AO14">
-        <v>0.9932432432432432</v>
+        <v>40.3125</v>
       </c>
       <c r="AP14">
-        <v>0.7636871508379889</v>
+        <v>1.438461538461538</v>
       </c>
       <c r="AQ14">
-        <v>1.072992700729927</v>
+        <v>-3.37696335078534</v>
       </c>
     </row>
     <row r="15">
@@ -2042,7 +2153,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deutsche Beteiligungs AG (XTRA:DBAN)</t>
+          <t>Binect AG (XTRA:MA10)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2051,124 +2162,118 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.232</v>
-      </c>
-      <c r="E15">
-        <v>0.302</v>
+        <v>0.11</v>
       </c>
       <c r="F15">
-        <v>-0.147</v>
+        <v>0.121</v>
       </c>
       <c r="G15">
-        <v>0.8465753424657535</v>
+        <v>0.0212</v>
       </c>
       <c r="H15">
-        <v>0.8465753424657535</v>
+        <v>0.0212</v>
       </c>
       <c r="I15">
-        <v>0.8454011741682974</v>
+        <v>0.01896</v>
       </c>
       <c r="J15">
-        <v>0.8427742657357912</v>
+        <v>0.01336228571428571</v>
       </c>
       <c r="K15">
-        <v>214.6</v>
+        <v>0.148</v>
       </c>
       <c r="L15">
-        <v>0.8399217221135029</v>
+        <v>0.01184</v>
       </c>
       <c r="M15">
-        <v>13.9</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.01638185032410136</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.06477166821994408</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>13.9</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.01638185032410136</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.06477166821994408</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>43.7</v>
+        <v>2.03</v>
       </c>
       <c r="V15">
-        <v>0.05150265173836182</v>
+        <v>0.2325315005727377</v>
       </c>
       <c r="W15">
-        <v>0.4315302634224814</v>
+        <v>0.01450980392156863</v>
       </c>
       <c r="X15">
-        <v>0.04398571613108649</v>
+        <v>0.07454825933657093</v>
       </c>
       <c r="Y15">
-        <v>0.3875445472913949</v>
+        <v>-0.0600384554150023</v>
       </c>
       <c r="Z15">
-        <v>0.5144985904148207</v>
+        <v>7.086167800453517</v>
       </c>
       <c r="AA15">
-        <v>0.4336061717589502</v>
+        <v>0.09468739876903146</v>
       </c>
       <c r="AB15">
-        <v>0.04383182650095602</v>
+        <v>0.07160554428868759</v>
       </c>
       <c r="AC15">
-        <v>0.3897743452579942</v>
+        <v>0.02308185448034386</v>
       </c>
       <c r="AD15">
-        <v>4.75</v>
+        <v>0.776</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>4.75</v>
+        <v>0.776</v>
       </c>
       <c r="AG15">
-        <v>-38.95</v>
+        <v>-1.254</v>
       </c>
       <c r="AH15">
-        <v>0.005566949897450923</v>
+        <v>0.0816326530612245</v>
       </c>
       <c r="AI15">
-        <v>0.005830724851163076</v>
+        <v>0.0784155214227971</v>
       </c>
       <c r="AJ15">
-        <v>-0.04811314928046447</v>
+        <v>-0.167736757624398</v>
       </c>
       <c r="AK15">
-        <v>-0.05052208314417278</v>
+        <v>-0.1594202898550725</v>
       </c>
       <c r="AL15">
-        <v>1.63</v>
+        <v>0.027</v>
       </c>
       <c r="AM15">
-        <v>0.7359999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="AN15">
-        <v>0.02196024040684235</v>
+        <v>3.527272727272727</v>
       </c>
       <c r="AO15">
-        <v>132.5153374233129</v>
+        <v>8.777777777777777</v>
       </c>
       <c r="AP15">
-        <v>-0.1800739713361073</v>
+        <v>-5.699999999999999</v>
       </c>
       <c r="AQ15">
-        <v>293.4782608695652</v>
+        <v>8.777777777777777</v>
       </c>
     </row>
     <row r="16">
@@ -2179,7 +2284,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OVB Holding AG (XTRA:O4B)</t>
+          <t>BAVARIA Industries Group AG (XTRA:B8A)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2188,124 +2293,118 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0709</v>
+        <v>-0.259</v>
       </c>
       <c r="E16">
-        <v>0.0435</v>
-      </c>
-      <c r="F16">
-        <v>0.21</v>
+        <v>-0.3</v>
       </c>
       <c r="G16">
-        <v>0.0528806011689396</v>
+        <v>0.2171979243884359</v>
       </c>
       <c r="H16">
-        <v>0.0528806011689396</v>
+        <v>0.2171979243884359</v>
       </c>
       <c r="I16">
-        <v>0.06123016977456164</v>
+        <v>0.1769452197869276</v>
       </c>
       <c r="J16">
-        <v>0.0434271120081765</v>
+        <v>0.1769452197869276</v>
       </c>
       <c r="K16">
-        <v>16.8</v>
+        <v>22.8</v>
       </c>
       <c r="L16">
-        <v>0.04675758419148344</v>
+        <v>0.1690140845070423</v>
       </c>
       <c r="M16">
-        <v>12.4</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.03073872087258305</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>0.7380952380952381</v>
+        <v>-0</v>
       </c>
       <c r="P16">
-        <v>12.4</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.03073872087258305</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.7380952380952381</v>
+        <v>-0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>78.8</v>
+        <v>62.9</v>
       </c>
       <c r="V16">
-        <v>0.19533961328706</v>
+        <v>0.1663141195134849</v>
       </c>
       <c r="W16">
-        <v>0.1640625</v>
+        <v>0.0647175702526256</v>
       </c>
       <c r="X16">
-        <v>0.04455698175543199</v>
+        <v>0.07377696817457229</v>
       </c>
       <c r="Y16">
-        <v>0.119505518244568</v>
+        <v>-0.009059397921946682</v>
       </c>
       <c r="Z16">
-        <v>8.184510250569476</v>
+        <v>0.5014209107915024</v>
       </c>
       <c r="AA16">
-        <v>0.3554296433835493</v>
+        <v>0.08872403326576379</v>
       </c>
       <c r="AB16">
-        <v>0.04363024613017228</v>
+        <v>0.07161496342364912</v>
       </c>
       <c r="AC16">
-        <v>0.311799397253377</v>
+        <v>0.01710906984211467</v>
       </c>
       <c r="AD16">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>5.635449253717359</v>
       </c>
       <c r="AF16">
-        <v>13.7</v>
+        <v>21.23544925371736</v>
       </c>
       <c r="AG16">
-        <v>-65.09999999999999</v>
+        <v>-41.66455074628264</v>
       </c>
       <c r="AH16">
-        <v>0.03284584032606089</v>
+        <v>0.05316365709000659</v>
       </c>
       <c r="AI16">
-        <v>0.118409680207433</v>
+        <v>0.05993035497419844</v>
       </c>
       <c r="AJ16">
-        <v>-0.1924327519952705</v>
+        <v>-0.1238043446498004</v>
       </c>
       <c r="AK16">
-        <v>-1.764227642276422</v>
+        <v>-0.1429632217116127</v>
       </c>
       <c r="AL16">
-        <v>0.458</v>
+        <v>1.11</v>
       </c>
       <c r="AM16">
-        <v>-0.07100000000000001</v>
+        <v>-7.089999999999999</v>
       </c>
       <c r="AN16">
-        <v>0.556910569105691</v>
+        <v>0.547426044846826</v>
       </c>
       <c r="AO16">
-        <v>48.03493449781659</v>
+        <v>21.62162162162162</v>
       </c>
       <c r="AP16">
-        <v>-2.646341463414634</v>
+        <v>-1.462067963163935</v>
       </c>
       <c r="AQ16">
-        <v>-309.8591549295774</v>
+        <v>-3.385049365303245</v>
       </c>
     </row>
     <row r="17">
@@ -2316,7 +2415,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shareholder Value Beteiligungen AG (XTRA:SVE)</t>
+          <t>NSI Asset AG (DB:VMR1)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2325,25 +2424,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.523</v>
+        <v>0.5479999999999999</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>0.1127167630057803</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.1127167630057803</v>
       </c>
       <c r="I17">
-        <v>0.9043824701195219</v>
+        <v>0.09017341040462427</v>
       </c>
       <c r="J17">
-        <v>0.9043824701195219</v>
+        <v>0.09017341040462427</v>
       </c>
       <c r="K17">
-        <v>21.7</v>
+        <v>-1.13</v>
       </c>
       <c r="L17">
-        <v>0.8645418326693226</v>
+        <v>-0.0653179190751445</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2352,7 +2451,7 @@
         <v>-0</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2361,73 +2460,79 @@
         <v>-0</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0.53</v>
+        <v>4.11</v>
       </c>
       <c r="V17">
-        <v>0.004744852282900626</v>
+        <v>0.2552795031055901</v>
       </c>
       <c r="W17">
-        <v>0.3433544303797468</v>
+        <v>-0.26036866359447</v>
       </c>
       <c r="X17">
-        <v>0.04398566034743594</v>
+        <v>0.2101438717246321</v>
       </c>
       <c r="Y17">
-        <v>0.2993687700323109</v>
+        <v>-0.4705125353191021</v>
       </c>
       <c r="Z17">
-        <v>0.3860766308276807</v>
+        <v>0.6062092648398627</v>
       </c>
       <c r="AA17">
-        <v>0.3491609370433606</v>
+        <v>0.05466395682949051</v>
       </c>
       <c r="AB17">
-        <v>0.04383184674037878</v>
+        <v>0.06357682699425204</v>
       </c>
       <c r="AC17">
-        <v>0.3053290903029818</v>
+        <v>-0.008912870164761534</v>
       </c>
       <c r="AD17">
-        <v>0.625</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0.625</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AG17">
-        <v>0.09499999999999997</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="AH17">
-        <v>0.005564210994880926</v>
+        <v>0.853901996370236</v>
       </c>
       <c r="AI17">
-        <v>0.007052186177715092</v>
+        <v>0.9022051773729626</v>
       </c>
       <c r="AJ17">
-        <v>0.000849769667695335</v>
+        <v>0.8482420586294654</v>
       </c>
       <c r="AK17">
-        <v>0.001078381292922413</v>
+        <v>0.8981934324782912</v>
       </c>
       <c r="AL17">
-        <v>0.001</v>
+        <v>1.93</v>
       </c>
       <c r="AM17">
-        <v>-1.049</v>
+        <v>1.841</v>
+      </c>
+      <c r="AN17">
+        <v>55.35294117647059</v>
       </c>
       <c r="AO17">
-        <v>22700</v>
+        <v>0.8082901554404146</v>
+      </c>
+      <c r="AP17">
+        <v>52.93529411764705</v>
       </c>
       <c r="AQ17">
-        <v>-21.63965681601525</v>
+        <v>0.8473655621944596</v>
       </c>
     </row>
     <row r="18">
@@ -2438,7 +2543,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deutsche Balaton AG (DB:BBHK)</t>
+          <t>Blue Cap AG (XTRA:B7E)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2447,115 +2552,124 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.08550000000000001</v>
+        <v>0.2</v>
+      </c>
+      <c r="E18">
+        <v>-0.139</v>
+      </c>
+      <c r="F18">
+        <v>0.132</v>
       </c>
       <c r="G18">
-        <v>0.7819043856183326</v>
+        <v>0.05772333432925008</v>
       </c>
       <c r="H18">
-        <v>0.7218490715132359</v>
+        <v>0.04989542874215715</v>
       </c>
       <c r="I18">
-        <v>0.532874855202795</v>
+        <v>0.01386316103973708</v>
       </c>
       <c r="J18">
-        <v>0.5224236322362369</v>
+        <v>0.01030400663402499</v>
       </c>
       <c r="K18">
-        <v>143.5</v>
+        <v>19.3</v>
       </c>
       <c r="L18">
-        <v>0.5669695772421968</v>
+        <v>0.05766357932476845</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>3.9116</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.03357596566523605</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>0.2026735751295337</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>3.9116</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.03357596566523605</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0.2026735751295337</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>140.5</v>
+        <v>31.7</v>
       </c>
       <c r="V18">
-        <v>0.4703716103113492</v>
+        <v>0.2721030042918455</v>
       </c>
       <c r="W18">
-        <v>0.4079022171688459</v>
+        <v>0.2091007583965331</v>
       </c>
       <c r="X18">
-        <v>0.05161833484136324</v>
+        <v>0.09595150811169999</v>
       </c>
       <c r="Y18">
-        <v>0.3562838823274827</v>
+        <v>0.1131492502848331</v>
       </c>
       <c r="Z18">
-        <v>0.5691901435749153</v>
+        <v>2.102386934673367</v>
       </c>
       <c r="AA18">
-        <v>0.2973583822394725</v>
+        <v>0.02166300892216183</v>
       </c>
       <c r="AB18">
-        <v>0.04182052354113925</v>
+        <v>0.06457126211866374</v>
       </c>
       <c r="AC18">
-        <v>0.2555378586983332</v>
+        <v>-0.04290825319650191</v>
       </c>
       <c r="AD18">
-        <v>114.6</v>
+        <v>116.2</v>
       </c>
       <c r="AE18">
-        <v>0.2668707408627761</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>114.8668707408628</v>
+        <v>116.2</v>
       </c>
       <c r="AG18">
-        <v>-25.63312925913723</v>
+        <v>84.5</v>
       </c>
       <c r="AH18">
-        <v>0.2777467898603447</v>
+        <v>0.4993553932101418</v>
       </c>
       <c r="AI18">
-        <v>0.1401897914630126</v>
+        <v>0.4989265779304423</v>
       </c>
       <c r="AJ18">
-        <v>-0.09387125281654093</v>
+        <v>0.4203980099502487</v>
       </c>
       <c r="AK18">
-        <v>-0.03775869815412147</v>
+        <v>0.4199801192842942</v>
       </c>
       <c r="AL18">
-        <v>3.16</v>
+        <v>2.11</v>
       </c>
       <c r="AM18">
-        <v>-15.04</v>
+        <v>2.106</v>
       </c>
       <c r="AN18">
-        <v>0.7979167827104106</v>
+        <v>5.868686868686869</v>
       </c>
       <c r="AO18">
-        <v>42.62658227848101</v>
+        <v>2.199052132701422</v>
       </c>
       <c r="AP18">
-        <v>-0.178473857148786</v>
+        <v>4.267676767676767</v>
       </c>
       <c r="AQ18">
-        <v>-8.956117021276595</v>
+        <v>2.203228869895537</v>
       </c>
     </row>
     <row r="19">
@@ -2566,7 +2680,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DWS Group GmbH &amp; Co. KGaA (XTRA:DWS)</t>
+          <t>Coreo AG (XTRA:CORE)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2574,26 +2688,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F19">
-        <v>0.101</v>
+      <c r="D19">
+        <v>0.795</v>
       </c>
       <c r="G19">
-        <v>0.246049072184519</v>
+        <v>0.079375</v>
       </c>
       <c r="H19">
-        <v>0.2339471311280907</v>
+        <v>0.079375</v>
       </c>
       <c r="I19">
-        <v>0.270086849224052</v>
+        <v>0.0775</v>
       </c>
       <c r="J19">
-        <v>0.1971051434768644</v>
+        <v>0.0775</v>
       </c>
       <c r="K19">
-        <v>792.8</v>
+        <v>-2.15</v>
       </c>
       <c r="L19">
-        <v>0.1881258601869868</v>
+        <v>-0.134375</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2602,7 +2716,7 @@
         <v>-0</v>
       </c>
       <c r="O19">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P19">
         <v>-0</v>
@@ -2611,79 +2725,79 @@
         <v>-0</v>
       </c>
       <c r="R19">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="U19">
-        <v>2507</v>
+        <v>13.1</v>
       </c>
       <c r="V19">
-        <v>0.3120332569949218</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="W19">
-        <v>0.09645003528066376</v>
+        <v>-0.06847133757961783</v>
       </c>
       <c r="X19">
-        <v>0.04409381800658754</v>
+        <v>0.1594468696131102</v>
       </c>
       <c r="Y19">
-        <v>0.05235621727407622</v>
+        <v>-0.227918207192728</v>
       </c>
       <c r="Z19">
-        <v>0.7635803587606451</v>
+        <v>0.1735357917570499</v>
       </c>
       <c r="AA19">
-        <v>0.1505056161696326</v>
+        <v>0.01344902386117137</v>
       </c>
       <c r="AB19">
-        <v>0.04379281331635364</v>
+        <v>0.06427336178215</v>
       </c>
       <c r="AC19">
-        <v>0.1067128028532789</v>
+        <v>-0.05082433792097863</v>
       </c>
       <c r="AD19">
-        <v>88.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>88.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AG19">
-        <v>-2418.9</v>
+        <v>57.8</v>
       </c>
       <c r="AH19">
-        <v>0.01084641428131733</v>
+        <v>0.7869034406215316</v>
       </c>
       <c r="AI19">
-        <v>0.01059110635586598</v>
+        <v>0.6903602726387537</v>
       </c>
       <c r="AJ19">
-        <v>-0.4307541625857003</v>
+        <v>0.7506493506493507</v>
       </c>
       <c r="AK19">
-        <v>-0.4162407722884724</v>
+        <v>0.6450892857142857</v>
       </c>
       <c r="AL19">
-        <v>24.3</v>
+        <v>3.39</v>
       </c>
       <c r="AM19">
-        <v>24.3</v>
+        <v>3.304</v>
       </c>
       <c r="AN19">
-        <v>0.07699702849152246</v>
+        <v>50.64285714285715</v>
       </c>
       <c r="AO19">
-        <v>46.83950617283951</v>
+        <v>0.3657817109144543</v>
       </c>
       <c r="AP19">
-        <v>-2.114053487152596</v>
+        <v>41.28571428571429</v>
       </c>
       <c r="AQ19">
-        <v>46.83950617283951</v>
+        <v>0.3753026634382566</v>
       </c>
     </row>
     <row r="20">
@@ -2694,7 +2808,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Heidelberger Beteiligungsholding AG (DB:IPOK)</t>
+          <t>AdCapital AG (DB:ADC)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2702,23 +2816,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D20">
+        <v>0.00709</v>
+      </c>
       <c r="G20">
-        <v>-0.7342657342657344</v>
+        <v>0.0834247410115783</v>
       </c>
       <c r="H20">
-        <v>-0.7342657342657344</v>
+        <v>0.07068860450944546</v>
       </c>
       <c r="I20">
-        <v>0.8531468531468531</v>
+        <v>0.007921998781230958</v>
       </c>
       <c r="J20">
-        <v>0.84998704998705</v>
+        <v>0.003960999390615479</v>
       </c>
       <c r="K20">
-        <v>4.84</v>
+        <v>-0.921</v>
       </c>
       <c r="L20">
-        <v>0.8461538461538461</v>
+        <v>-0.005612431444241317</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2727,7 +2844,7 @@
         <v>-0</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2736,79 +2853,79 @@
         <v>-0</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="U20">
-        <v>11.8</v>
+        <v>7.35</v>
       </c>
       <c r="V20">
-        <v>0.3501483679525222</v>
+        <v>0.3466981132075472</v>
       </c>
       <c r="W20">
-        <v>0.1618729096989966</v>
+        <v>-0.01412576687116564</v>
       </c>
       <c r="X20">
-        <v>0.04458417712080586</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y20">
-        <v>0.1172887325781908</v>
+        <v>-0.08657998591187049</v>
       </c>
       <c r="Z20">
-        <v>0.1667201025969862</v>
+        <v>3.078799249530956</v>
       </c>
       <c r="AA20">
-        <v>0.1417099281799506</v>
+        <v>0.01219512195121951</v>
       </c>
       <c r="AB20">
-        <v>0.04380391651249452</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC20">
-        <v>0.09790601166745611</v>
+        <v>-0.06025909708948535</v>
       </c>
       <c r="AD20">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>-10.61</v>
+        <v>-7.35</v>
       </c>
       <c r="AH20">
-        <v>0.03410719403840642</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>0.03165735567970205</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>-0.4595062797747942</v>
+        <v>-0.5306859205776173</v>
       </c>
       <c r="AK20">
-        <v>-0.4113997673516868</v>
+        <v>-0.129973474801061</v>
       </c>
       <c r="AL20">
-        <v>0.014</v>
+        <v>0.287</v>
       </c>
       <c r="AM20">
-        <v>-0.186</v>
+        <v>0.172</v>
       </c>
       <c r="AN20">
-        <v>0.2433537832310838</v>
+        <v>0</v>
       </c>
       <c r="AO20">
-        <v>348.5714285714286</v>
+        <v>4.529616724738676</v>
       </c>
       <c r="AP20">
-        <v>-2.169734151329244</v>
+        <v>-1.243654822335025</v>
       </c>
       <c r="AQ20">
-        <v>-26.23655913978494</v>
+        <v>7.558139534883722</v>
       </c>
     </row>
     <row r="21">
@@ -2819,7 +2936,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blue Cap AG (XTRA:B7E)</t>
+          <t>MPC Münchmeyer Petersen Capital AG (XTRA:MPCK)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2828,124 +2945,124 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.235</v>
+        <v>-0.034</v>
       </c>
       <c r="E21">
-        <v>0.0885</v>
+        <v>0.277</v>
       </c>
       <c r="F21">
-        <v>-0.201</v>
+        <v>0.283</v>
       </c>
       <c r="G21">
-        <v>0.115079086115993</v>
+        <v>0.02110403397027601</v>
       </c>
       <c r="H21">
-        <v>0.1026362038664323</v>
+        <v>0.02110403397027601</v>
       </c>
       <c r="I21">
-        <v>0.06748681898066784</v>
+        <v>0.007452229299363056</v>
       </c>
       <c r="J21">
-        <v>0.06244088143842098</v>
+        <v>0.006504762978411588</v>
       </c>
       <c r="K21">
-        <v>2.82</v>
+        <v>28.1</v>
       </c>
       <c r="L21">
-        <v>0.009912126537785589</v>
+        <v>0.5966029723991507</v>
       </c>
       <c r="M21">
-        <v>8.516999999999999</v>
+        <v>5.11</v>
       </c>
       <c r="N21">
-        <v>0.05519766688269604</v>
+        <v>0.04662408759124088</v>
       </c>
       <c r="O21">
-        <v>3.020212765957447</v>
+        <v>0.1818505338078292</v>
       </c>
       <c r="P21">
-        <v>8.279999999999999</v>
+        <v>5.11</v>
       </c>
       <c r="Q21">
-        <v>0.05366169799092676</v>
+        <v>0.04662408759124088</v>
       </c>
       <c r="R21">
-        <v>2.936170212765957</v>
+        <v>0.1818505338078292</v>
       </c>
       <c r="S21">
-        <v>0.2370000000000001</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>0.0278266995420923</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>34</v>
+        <v>53.1</v>
       </c>
       <c r="V21">
-        <v>0.220349967595593</v>
+        <v>0.4844890510948905</v>
       </c>
       <c r="W21">
-        <v>0.03029001074113856</v>
+        <v>0.2618825722273999</v>
       </c>
       <c r="X21">
-        <v>0.05704363456316985</v>
+        <v>0.07286906256190917</v>
       </c>
       <c r="Y21">
-        <v>-0.02675362382203129</v>
+        <v>0.1890135096654907</v>
       </c>
       <c r="Z21">
-        <v>2.030692362598144</v>
+        <v>0.7456070919740385</v>
       </c>
       <c r="AA21">
-        <v>0.1267982210508977</v>
+        <v>0.00484999740831385</v>
       </c>
       <c r="AB21">
-        <v>0.04095128821633176</v>
+        <v>0.07227431414673402</v>
       </c>
       <c r="AC21">
-        <v>0.08584693283456593</v>
+        <v>-0.06742431673842017</v>
       </c>
       <c r="AD21">
-        <v>100.9</v>
+        <v>1.93</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>100.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG21">
-        <v>66.90000000000001</v>
+        <v>-51.17</v>
       </c>
       <c r="AH21">
-        <v>0.3953761755485893</v>
+        <v>0.01730476105083834</v>
       </c>
       <c r="AI21">
-        <v>0.5078007045797686</v>
+        <v>0.01512183655880279</v>
       </c>
       <c r="AJ21">
-        <v>0.3024412296564195</v>
+        <v>-0.8757487591990417</v>
       </c>
       <c r="AK21">
-        <v>0.4061930783242259</v>
+        <v>-0.6865691667784785</v>
       </c>
       <c r="AL21">
-        <v>2.72</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AM21">
-        <v>2.207</v>
+        <v>-0.969</v>
       </c>
       <c r="AN21">
-        <v>3.374581939799331</v>
+        <v>0.8502202643171806</v>
       </c>
       <c r="AO21">
-        <v>7.058823529411764</v>
+        <v>0.6256684491978609</v>
       </c>
       <c r="AP21">
-        <v>2.237458193979934</v>
+        <v>-22.54185022026432</v>
       </c>
       <c r="AQ21">
-        <v>8.699592206615314</v>
+        <v>-0.3622291021671826</v>
       </c>
     </row>
     <row r="22">
@@ -2956,7 +3073,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ernst Russ AG (XTRA:HXCK)</t>
+          <t>ERWE Immobilien AG (XTRA:ERWE)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2964,32 +3081,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D22">
-        <v>0.181</v>
-      </c>
-      <c r="E22">
-        <v>0.257</v>
-      </c>
-      <c r="F22">
-        <v>0.8540000000000001</v>
-      </c>
       <c r="G22">
-        <v>0.1150442477876106</v>
+        <v>-0.3859844271412681</v>
       </c>
       <c r="H22">
-        <v>0.1150442477876106</v>
+        <v>-0.3859844271412681</v>
       </c>
       <c r="I22">
-        <v>0.2135817280346818</v>
+        <v>-0.2081317158795356</v>
       </c>
       <c r="J22">
-        <v>0.1441942313149568</v>
+        <v>-0.2081317158795356</v>
       </c>
       <c r="K22">
-        <v>12.9</v>
+        <v>-11.6</v>
       </c>
       <c r="L22">
-        <v>0.1426991150442478</v>
+        <v>-1.290322580645161</v>
       </c>
       <c r="M22">
         <v>-0</v>
@@ -2998,7 +3106,7 @@
         <v>-0</v>
       </c>
       <c r="O22">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P22">
         <v>-0</v>
@@ -3007,79 +3115,79 @@
         <v>-0</v>
       </c>
       <c r="R22">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>0.06079545454545454</v>
       </c>
       <c r="W22">
-        <v>0.2157190635451505</v>
+        <v>-0.1715976331360947</v>
       </c>
       <c r="X22">
-        <v>0.05023002861460082</v>
+        <v>0.1839967916668973</v>
       </c>
       <c r="Y22">
-        <v>0.1654890349305497</v>
+        <v>-0.355594424802992</v>
       </c>
       <c r="Z22">
-        <v>0.8814691296121306</v>
+        <v>0.0399847852103536</v>
       </c>
       <c r="AA22">
-        <v>0.1271027635722852</v>
+        <v>-0.008322101954905573</v>
       </c>
       <c r="AB22">
-        <v>0.04287564236550315</v>
+        <v>0.06606695315878444</v>
       </c>
       <c r="AC22">
-        <v>0.08422712120678205</v>
+        <v>-0.07438905511369001</v>
       </c>
       <c r="AD22">
-        <v>72.09999999999999</v>
+        <v>166.6</v>
       </c>
       <c r="AE22">
-        <v>0.9360589283238505</v>
+        <v>0.0655206287851258</v>
       </c>
       <c r="AF22">
-        <v>73.03605892832384</v>
+        <v>166.6655206287851</v>
       </c>
       <c r="AG22">
-        <v>73.03605892832384</v>
+        <v>164.5255206287851</v>
       </c>
       <c r="AH22">
-        <v>0.2399060715259075</v>
+        <v>0.8256264869287407</v>
       </c>
       <c r="AI22">
-        <v>0.4141867487126451</v>
+        <v>0.7464901887197056</v>
       </c>
       <c r="AJ22">
-        <v>0.2399060715259075</v>
+        <v>0.823758126206497</v>
       </c>
       <c r="AK22">
-        <v>0.4141867487126451</v>
+        <v>0.7440367812857868</v>
       </c>
       <c r="AL22">
-        <v>3.36</v>
+        <v>6.62</v>
       </c>
       <c r="AM22">
-        <v>-1.42</v>
+        <v>6.603</v>
       </c>
       <c r="AN22">
-        <v>2.333710956465447</v>
+        <v>-98.69668246445498</v>
       </c>
       <c r="AO22">
-        <v>5.535714285714286</v>
+        <v>-0.2885196374622356</v>
       </c>
       <c r="AP22">
-        <v>2.364009028267481</v>
+        <v>-97.46772549098645</v>
       </c>
       <c r="AQ22">
-        <v>-13.09859154929577</v>
+        <v>-0.2892624564591852</v>
       </c>
     </row>
     <row r="23">
@@ -3090,7 +3198,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AdCapital AG (DB:ADC)</t>
+          <t>FinLab AG (XTRA:A7A)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3099,28 +3207,25 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.039</v>
-      </c>
-      <c r="E23">
-        <v>-0.0774</v>
+        <v>0.0282</v>
       </c>
       <c r="G23">
-        <v>0.06279069767441861</v>
+        <v>-0.2022684310018904</v>
       </c>
       <c r="H23">
-        <v>0.05690252350321623</v>
+        <v>-0.2022684310018904</v>
       </c>
       <c r="I23">
-        <v>0.0433943592281049</v>
+        <v>-0.1995377131133589</v>
       </c>
       <c r="J23">
-        <v>0.02180512578128654</v>
+        <v>-0.09976885655667943</v>
       </c>
       <c r="K23">
-        <v>0.983</v>
+        <v>-0.402</v>
       </c>
       <c r="L23">
-        <v>0.004863928748144483</v>
+        <v>-0.07599243856332703</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3129,7 +3234,7 @@
         <v>-0</v>
       </c>
       <c r="O23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <v>-0</v>
@@ -3138,79 +3243,76 @@
         <v>-0</v>
       </c>
       <c r="R23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="U23">
-        <v>11.9</v>
+        <v>2.37</v>
       </c>
       <c r="V23">
-        <v>0.4204946996466431</v>
+        <v>0.04157894736842106</v>
       </c>
       <c r="W23">
-        <v>0.01606209150326797</v>
+        <v>-0.005685997171145686</v>
       </c>
       <c r="X23">
-        <v>0.04387296409148227</v>
+        <v>0.07261448442204163</v>
       </c>
       <c r="Y23">
-        <v>-0.0278108725882143</v>
+        <v>-0.07830048159318731</v>
       </c>
       <c r="Z23">
-        <v>3.826926718424541</v>
+        <v>0.08612581147799914</v>
       </c>
       <c r="AA23">
-        <v>0.08344661845101325</v>
+        <v>-0.008592673731176111</v>
       </c>
       <c r="AB23">
-        <v>0.04387296409148227</v>
+        <v>0.07238397086948974</v>
       </c>
       <c r="AC23">
-        <v>0.03957365435953098</v>
+        <v>-0.08097664460066585</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>0.3677725118483413</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>0.3877725118483413</v>
       </c>
       <c r="AG23">
-        <v>-11.9</v>
+        <v>-1.982227488151659</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>0.006757058078326378</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>0.006225499744345159</v>
       </c>
       <c r="AJ23">
-        <v>-0.7256097560975611</v>
+        <v>-0.03602885754280177</v>
       </c>
       <c r="AK23">
-        <v>-0.202037351443124</v>
+        <v>-0.03308246293300851</v>
       </c>
       <c r="AL23">
-        <v>0.621</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>0.479</v>
+        <v>-2.03</v>
       </c>
       <c r="AN23">
-        <v>0</v>
-      </c>
-      <c r="AO23">
-        <v>14.12238325281803</v>
+        <v>-0.02347417840375587</v>
       </c>
       <c r="AP23">
-        <v>-0.8095238095238095</v>
+        <v>2.326558084685046</v>
       </c>
       <c r="AQ23">
-        <v>18.30897703549061</v>
+        <v>0.6748768472906405</v>
       </c>
     </row>
     <row r="24">
@@ -3221,7 +3323,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BAVARIA Industries Group AG (XTRA:B8A)</t>
+          <t>Mountain Alliance AG (XTRA:ECF)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3230,28 +3332,25 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.283</v>
-      </c>
-      <c r="E24">
-        <v>-0.291</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G24">
-        <v>0.05466292134831461</v>
+        <v>-0.1603305785123967</v>
       </c>
       <c r="H24">
-        <v>0.05466292134831461</v>
+        <v>-0.1603305785123967</v>
       </c>
       <c r="I24">
-        <v>0.08615856429298178</v>
+        <v>-0.07263971976739873</v>
       </c>
       <c r="J24">
-        <v>0.06751321728191217</v>
+        <v>-0.07263971976739873</v>
       </c>
       <c r="K24">
-        <v>5.37</v>
+        <v>-3.89</v>
       </c>
       <c r="L24">
-        <v>0.0301685393258427</v>
+        <v>-0.3214876033057851</v>
       </c>
       <c r="M24">
         <v>-0</v>
@@ -3260,7 +3359,7 @@
         <v>-0</v>
       </c>
       <c r="O24">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3269,79 +3368,79 @@
         <v>-0</v>
       </c>
       <c r="R24">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>97.5</v>
+        <v>2.49</v>
       </c>
       <c r="V24">
-        <v>0.2176339285714286</v>
+        <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.01624319419237749</v>
+        <v>-0.07811244979919679</v>
       </c>
       <c r="X24">
-        <v>0.04534617931595169</v>
+        <v>0.07629511441755246</v>
       </c>
       <c r="Y24">
-        <v>-0.02910298512357419</v>
+        <v>-0.1544075642167493</v>
       </c>
       <c r="Z24">
-        <v>0.7557780577013484</v>
+        <v>0.2132545528164947</v>
       </c>
       <c r="AA24">
-        <v>0.05102500822649269</v>
+        <v>-0.01549075095571211</v>
       </c>
       <c r="AB24">
-        <v>0.04336929330647479</v>
+        <v>0.07024122842771237</v>
       </c>
       <c r="AC24">
-        <v>0.007655714920017896</v>
+        <v>-0.08573197938342447</v>
       </c>
       <c r="AD24">
-        <v>23.5</v>
+        <v>3.99</v>
       </c>
       <c r="AE24">
-        <v>9.268877779246221</v>
+        <v>0.06970304592762341</v>
       </c>
       <c r="AF24">
-        <v>32.76887777924622</v>
+        <v>4.059703045927623</v>
       </c>
       <c r="AG24">
-        <v>-64.73112222075378</v>
+        <v>1.569703045927623</v>
       </c>
       <c r="AH24">
-        <v>0.0681593158247083</v>
+        <v>0.1401845536706395</v>
       </c>
       <c r="AI24">
-        <v>0.08465903527881935</v>
+        <v>0.08814001779124721</v>
       </c>
       <c r="AJ24">
-        <v>-0.1688921954629391</v>
+        <v>0.05930187592977635</v>
       </c>
       <c r="AK24">
-        <v>-0.2235430917755663</v>
+        <v>0.03602739831099997</v>
       </c>
       <c r="AL24">
-        <v>2.32</v>
+        <v>1.62</v>
       </c>
       <c r="AM24">
-        <v>-3.620000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="AN24">
-        <v>0.8134302526825891</v>
+        <v>-5.215686274509804</v>
       </c>
       <c r="AO24">
-        <v>6.46551724137931</v>
+        <v>-0.5790123456790123</v>
       </c>
       <c r="AP24">
-        <v>-2.240606515083204</v>
+        <v>-2.051899406441337</v>
       </c>
       <c r="AQ24">
-        <v>-4.143646408839778</v>
+        <v>-0.5790123456790123</v>
       </c>
     </row>
     <row r="25">
@@ -3352,7 +3451,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Binect AG (XTRA:MA10)</t>
+          <t>iVestos AG (DUSE:LWD)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3360,23 +3459,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D25">
+        <v>-0.0187</v>
+      </c>
       <c r="G25">
-        <v>0.02974789915966386</v>
+        <v>3.78125</v>
       </c>
       <c r="H25">
-        <v>0.02974789915966386</v>
+        <v>3.78125</v>
       </c>
       <c r="I25">
-        <v>0.0207563025210084</v>
+        <v>-1.322916666666667</v>
       </c>
       <c r="J25">
-        <v>0.0207563025210084</v>
+        <v>-1.322916666666667</v>
       </c>
       <c r="K25">
-        <v>0.506</v>
+        <v>-0.211</v>
       </c>
       <c r="L25">
-        <v>0.04252100840336134</v>
+        <v>-2.197916666666667</v>
       </c>
       <c r="M25">
         <v>-0</v>
@@ -3385,7 +3487,7 @@
         <v>-0</v>
       </c>
       <c r="O25">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P25">
         <v>-0</v>
@@ -3394,79 +3496,73 @@
         <v>-0</v>
       </c>
       <c r="R25">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
       <c r="U25">
-        <v>3.1</v>
+        <v>0.114</v>
       </c>
       <c r="V25">
-        <v>0.31</v>
+        <v>0.02489082969432314</v>
       </c>
       <c r="W25">
-        <v>0.05615982241953385</v>
+        <v>-0.0332807570977918</v>
       </c>
       <c r="X25">
-        <v>0.04402200804547615</v>
+        <v>0.07514435213913326</v>
       </c>
       <c r="Y25">
-        <v>0.0121378143740577</v>
+        <v>-0.1084251092369251</v>
       </c>
       <c r="Z25">
-        <v>1.348136399682792</v>
+        <v>0.01462300076161462</v>
       </c>
       <c r="AA25">
-        <v>0.02798232695139912</v>
+        <v>-0.01934501142421935</v>
       </c>
       <c r="AB25">
-        <v>0.04385809336325057</v>
+        <v>0.07166133897652956</v>
       </c>
       <c r="AC25">
-        <v>-0.01587576641185145</v>
+        <v>-0.09100635040074891</v>
       </c>
       <c r="AD25">
-        <v>0.074</v>
+        <v>0.523</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0.074</v>
+        <v>0.523</v>
       </c>
       <c r="AG25">
-        <v>-3.026</v>
+        <v>0.409</v>
       </c>
       <c r="AH25">
-        <v>0.007345642247369466</v>
+        <v>0.1024887321183618</v>
       </c>
       <c r="AI25">
-        <v>0.007202647459606775</v>
+        <v>0.074363713920091</v>
       </c>
       <c r="AJ25">
-        <v>-0.4338973329509607</v>
+        <v>0.08198035678492685</v>
       </c>
       <c r="AK25">
-        <v>-0.4218009478672987</v>
+        <v>0.05911258852435324</v>
       </c>
       <c r="AL25">
-        <v>0.044</v>
+        <v>0.011</v>
       </c>
       <c r="AM25">
-        <v>0.044</v>
-      </c>
-      <c r="AN25">
-        <v>0.8043478260869565</v>
+        <v>-0.168</v>
       </c>
       <c r="AO25">
-        <v>5.613636363636364</v>
-      </c>
-      <c r="AP25">
-        <v>-32.89130434782609</v>
+        <v>-11.54545454545455</v>
       </c>
       <c r="AQ25">
-        <v>5.613636363636364</v>
+        <v>0.755952380952381</v>
       </c>
     </row>
     <row r="26">
@@ -3477,7 +3573,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KST Beteiligungs AG (DB:KSW)</t>
+          <t>AURELIUS Equity Opportunities SE &amp; Co. KGaA (XTRA:AR4)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3486,118 +3582,124 @@
         </is>
       </c>
       <c r="D26">
-        <v>-0.04389999999999999</v>
+        <v>0.0242</v>
       </c>
       <c r="E26">
-        <v>0.08109999999999999</v>
+        <v>-0.13</v>
+      </c>
+      <c r="F26">
+        <v>-0.077</v>
       </c>
       <c r="G26">
-        <v>-0.2057377049180328</v>
+        <v>0.01836120401337793</v>
       </c>
       <c r="H26">
-        <v>-0.2057377049180328</v>
+        <v>0.01501672240802676</v>
       </c>
       <c r="I26">
-        <v>0.06721311475409837</v>
+        <v>-0.01979933110367893</v>
       </c>
       <c r="J26">
-        <v>0.06721311475409837</v>
+        <v>-0.01202648705370297</v>
       </c>
       <c r="K26">
-        <v>1.11</v>
+        <v>166</v>
       </c>
       <c r="L26">
-        <v>0.4549180327868853</v>
+        <v>0.05551839464882943</v>
       </c>
       <c r="M26">
-        <v>-0</v>
+        <v>39.396</v>
       </c>
       <c r="N26">
-        <v>-0</v>
+        <v>0.07514018691588786</v>
       </c>
       <c r="O26">
-        <v>-0</v>
+        <v>0.2373253012048193</v>
       </c>
       <c r="P26">
-        <v>-0</v>
+        <v>39.396</v>
       </c>
       <c r="Q26">
-        <v>-0</v>
+        <v>0.07514018691588786</v>
       </c>
       <c r="R26">
-        <v>-0</v>
+        <v>0.2373253012048193</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
       <c r="U26">
-        <v>0.039</v>
+        <v>279.1</v>
       </c>
       <c r="V26">
-        <v>0.004352678571428571</v>
+        <v>0.5323288193782186</v>
       </c>
       <c r="W26">
-        <v>0.1487935656836461</v>
+        <v>0.306555863342567</v>
       </c>
       <c r="X26">
-        <v>0.04623324630211167</v>
+        <v>0.1043470957764756</v>
       </c>
       <c r="Y26">
-        <v>0.1025603193815345</v>
+        <v>0.2022087675660914</v>
       </c>
       <c r="Z26">
-        <v>0.2863513672104213</v>
+        <v>3.218168119685717</v>
       </c>
       <c r="AA26">
-        <v>0.01924656730430701</v>
+        <v>-0.03870325722803991</v>
       </c>
       <c r="AB26">
-        <v>0.04309783013970032</v>
+        <v>0.06647474460384585</v>
       </c>
       <c r="AC26">
-        <v>-0.02385126283539332</v>
+        <v>-0.1051780018318858</v>
       </c>
       <c r="AD26">
-        <v>1.05</v>
+        <v>709.8</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.05</v>
+        <v>709.8</v>
       </c>
       <c r="AG26">
-        <v>1.011</v>
+        <v>430.6999999999999</v>
       </c>
       <c r="AH26">
-        <v>0.1048951048951049</v>
+        <v>0.5751559841179807</v>
       </c>
       <c r="AI26">
-        <v>0.1098326359832636</v>
+        <v>0.5583700440528635</v>
       </c>
       <c r="AJ26">
-        <v>0.1013940427238993</v>
+        <v>0.4509947643979058</v>
       </c>
       <c r="AK26">
-        <v>0.1061863249658649</v>
+        <v>0.4341296240298357</v>
       </c>
       <c r="AL26">
-        <v>0.026</v>
+        <v>28.8</v>
       </c>
       <c r="AM26">
-        <v>-0.448</v>
+        <v>18.2</v>
       </c>
       <c r="AN26">
-        <v>6.140350877192982</v>
+        <v>13.86328125</v>
       </c>
       <c r="AO26">
-        <v>6.307692307692308</v>
+        <v>-2.055555555555556</v>
       </c>
       <c r="AP26">
-        <v>5.912280701754386</v>
+        <v>8.412109374999998</v>
       </c>
       <c r="AQ26">
-        <v>-0.3660714285714286</v>
+        <v>-3.252747252747252</v>
       </c>
     </row>
     <row r="27">
@@ -3608,7 +3710,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FinLab AG (XTRA:A7A)</t>
+          <t>Deutsche Effecten- und Wechsel-Beteiligungsgesellschaft AG (XTRA:EFF)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3616,29 +3718,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D27">
-        <v>0.203</v>
-      </c>
-      <c r="E27">
-        <v>0.204</v>
-      </c>
-      <c r="G27">
-        <v>0.06750572082379862</v>
-      </c>
-      <c r="H27">
-        <v>0.06750572082379862</v>
-      </c>
-      <c r="I27">
-        <v>0.3695652173913043</v>
-      </c>
-      <c r="J27">
-        <v>0.3441620937104263</v>
-      </c>
       <c r="K27">
-        <v>9.58</v>
-      </c>
-      <c r="L27">
-        <v>1.096109839816934</v>
+        <v>8.58</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3662,73 +3743,73 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>10.5</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="V27">
-        <v>0.08101851851851852</v>
+        <v>0.04776649746192893</v>
       </c>
       <c r="W27">
-        <v>0.05440090857467348</v>
+        <v>0.5107142857142857</v>
       </c>
       <c r="X27">
-        <v>0.04400568382862647</v>
+        <v>0.08960231572994104</v>
       </c>
       <c r="Y27">
-        <v>0.01039522474604701</v>
+        <v>0.4211119699843446</v>
       </c>
       <c r="Z27">
-        <v>0.05129378899120259</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>0.0176533778135531</v>
+        <v>-0.0401861146433775</v>
       </c>
       <c r="AB27">
-        <v>0.04382458897664766</v>
+        <v>0.06807462019575811</v>
       </c>
       <c r="AC27">
-        <v>-0.02617121116309456</v>
+        <v>-0.1082607348391356</v>
       </c>
       <c r="AD27">
-        <v>0.854</v>
+        <v>14.3</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>0.03984947959642204</v>
       </c>
       <c r="AF27">
-        <v>0.854</v>
+        <v>14.33984947959642</v>
       </c>
       <c r="AG27">
-        <v>-9.646000000000001</v>
+        <v>13.39884947959642</v>
       </c>
       <c r="AH27">
-        <v>0.006546368834991644</v>
+        <v>0.4212665360988676</v>
       </c>
       <c r="AI27">
-        <v>0.01193504206613187</v>
+        <v>0.3720785024650435</v>
       </c>
       <c r="AJ27">
-        <v>-0.08041415876085833</v>
+        <v>0.4048131488031346</v>
       </c>
       <c r="AK27">
-        <v>-0.1579912864022013</v>
+        <v>0.3563632841177097</v>
       </c>
       <c r="AL27">
-        <v>0.032</v>
+        <v>0.636</v>
       </c>
       <c r="AM27">
-        <v>-0.032</v>
+        <v>0.63</v>
       </c>
       <c r="AN27">
-        <v>0.2426136363636364</v>
+        <v>-10.31746031746032</v>
       </c>
       <c r="AO27">
-        <v>100.9375</v>
+        <v>-2.20125786163522</v>
       </c>
       <c r="AP27">
-        <v>-2.740340909090909</v>
+        <v>-9.667279566808386</v>
       </c>
       <c r="AQ27">
-        <v>-100.9375</v>
+        <v>-2.222222222222222</v>
       </c>
     </row>
     <row r="28">
@@ -3739,7 +3820,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sparta AG (DB:SPT6)</t>
+          <t>Murphy &amp; Spitz Green Capital Aktiengesellschaft (DUSE:6MP)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3747,29 +3828,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D28">
-        <v>0.833</v>
-      </c>
-      <c r="E28">
-        <v>0.365</v>
-      </c>
       <c r="G28">
-        <v>0.1354166666666667</v>
+        <v>-0.7310344827586207</v>
       </c>
       <c r="H28">
-        <v>0.1354166666666667</v>
+        <v>-0.7310344827586207</v>
       </c>
       <c r="I28">
-        <v>0.1256944444444444</v>
+        <v>-0.7632183908045977</v>
       </c>
       <c r="J28">
-        <v>0.1097567175018155</v>
+        <v>-0.7632183908045977</v>
       </c>
       <c r="K28">
-        <v>13.3</v>
+        <v>-0.007</v>
       </c>
       <c r="L28">
-        <v>0.9236111111111112</v>
+        <v>-0.01609195402298851</v>
       </c>
       <c r="M28">
         <v>-0</v>
@@ -3778,7 +3853,7 @@
         <v>-0</v>
       </c>
       <c r="O28">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P28">
         <v>-0</v>
@@ -3787,79 +3862,79 @@
         <v>-0</v>
       </c>
       <c r="R28">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
       <c r="U28">
-        <v>11.8</v>
+        <v>0.089</v>
       </c>
       <c r="V28">
-        <v>0.170028818443804</v>
+        <v>0.008396226415094339</v>
       </c>
       <c r="W28">
-        <v>0.1151515151515152</v>
+        <v>-0.001988636363636364</v>
       </c>
       <c r="X28">
-        <v>0.04650233207805548</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y28">
-        <v>0.06864918307345969</v>
+        <v>-0.07444285540434122</v>
       </c>
       <c r="Z28">
-        <v>0.1318077803203661</v>
+        <v>0.123614663256607</v>
       </c>
       <c r="AA28">
-        <v>0.01446678930916379</v>
+        <v>-0.09434498437055983</v>
       </c>
       <c r="AB28">
-        <v>0.04363919754684468</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC28">
-        <v>-0.02917240823768089</v>
+        <v>-0.1667992034112647</v>
       </c>
       <c r="AD28">
-        <v>9.06</v>
+        <v>0</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>9.06</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>-2.74</v>
+        <v>-0.089</v>
       </c>
       <c r="AH28">
-        <v>0.1154728524088708</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>0.05116909522195866</v>
+        <v>0</v>
       </c>
       <c r="AJ28">
-        <v>-0.0411041104110411</v>
+        <v>-0.008467319950528018</v>
       </c>
       <c r="AK28">
-        <v>-0.01657993464843277</v>
+        <v>-0.02372700613169821</v>
       </c>
       <c r="AL28">
-        <v>0.116</v>
+        <v>0.002</v>
       </c>
       <c r="AM28">
-        <v>-1.744</v>
+        <v>-0.324</v>
       </c>
       <c r="AN28">
-        <v>5.005524861878453</v>
+        <v>-0</v>
       </c>
       <c r="AO28">
-        <v>15.60344827586207</v>
+        <v>-166</v>
       </c>
       <c r="AP28">
-        <v>-1.513812154696133</v>
+        <v>0.278125</v>
       </c>
       <c r="AQ28">
-        <v>-1.037844036697248</v>
+        <v>1.024691358024691</v>
       </c>
     </row>
     <row r="29">
@@ -3870,7 +3945,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quirin Privatbank AG (XTRA:QB7)</t>
+          <t>Deutsche Beteiligungs AG (XTRA:DBAN)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3878,47 +3953,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D29">
-        <v>0.0718</v>
-      </c>
-      <c r="E29">
-        <v>0.23</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>-0.03170134450115626</v>
-      </c>
-      <c r="J29">
-        <v>-0.02818634186818287</v>
+      <c r="F29">
+        <v>-0.058</v>
       </c>
       <c r="K29">
-        <v>8.5</v>
-      </c>
-      <c r="L29">
-        <v>0.1276276276276276</v>
+        <v>-95.7</v>
       </c>
       <c r="M29">
-        <v>2.0398</v>
+        <v>29.5</v>
       </c>
       <c r="N29">
-        <v>0.009221518987341772</v>
+        <v>0.05261280542179418</v>
       </c>
       <c r="O29">
-        <v>0.2399764705882353</v>
+        <v>-0.3082549634273772</v>
       </c>
       <c r="P29">
-        <v>2.0398</v>
+        <v>29.5</v>
       </c>
       <c r="Q29">
-        <v>0.009221518987341772</v>
+        <v>0.05261280542179418</v>
       </c>
       <c r="R29">
-        <v>0.2399764705882353</v>
+        <v>-0.3082549634273772</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -3927,67 +3984,73 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>419.4</v>
+        <v>18.8</v>
       </c>
       <c r="V29">
-        <v>1.896021699819168</v>
+        <v>0.03352951667558409</v>
       </c>
       <c r="W29">
-        <v>0.1287878787878788</v>
+        <v>-0.1181627361402642</v>
       </c>
       <c r="X29">
-        <v>0.05181344151571523</v>
+        <v>0.07420205363757543</v>
       </c>
       <c r="Y29">
-        <v>0.07697443727216355</v>
+        <v>-0.1923647897778397</v>
       </c>
       <c r="Z29">
-        <v>-0.2061961303848202</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>0.005811914622922952</v>
+        <v>-0.1207601011738764</v>
       </c>
       <c r="AB29">
-        <v>0.04178344163635404</v>
+        <v>0.07136388423474771</v>
       </c>
       <c r="AC29">
-        <v>-0.03597152701343109</v>
+        <v>-0.1921239854086241</v>
       </c>
       <c r="AD29">
-        <v>69.7</v>
+        <v>41.6</v>
       </c>
       <c r="AE29">
-        <v>17.50654771888503</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>87.20654771888503</v>
+        <v>41.6</v>
       </c>
       <c r="AG29">
-        <v>-332.193452281115</v>
+        <v>22.8</v>
       </c>
       <c r="AH29">
-        <v>0.2827649035466474</v>
+        <v>0.06906857047982733</v>
       </c>
       <c r="AI29">
-        <v>0.5278637494881585</v>
+        <v>0.06820790293490736</v>
       </c>
       <c r="AJ29">
-        <v>2.992910351502204</v>
+        <v>0.0390745501285347</v>
       </c>
       <c r="AK29">
-        <v>1.306852907893705</v>
+        <v>0.03857215361191001</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>0.973</v>
       </c>
       <c r="AN29">
-        <v>50.14388489208633</v>
+        <v>-0.449244060475162</v>
+      </c>
+      <c r="AO29">
+        <v>-93.09999999999999</v>
       </c>
       <c r="AP29">
-        <v>-238.9880951662698</v>
+        <v>-0.24622030237581</v>
+      </c>
+      <c r="AQ29">
+        <v>-95.68345323741006</v>
       </c>
     </row>
     <row r="30">
@@ -3998,7 +4061,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lehner Investments AG (DB:LEH)</t>
+          <t>Deutsche Balaton AG (DB:BBHK)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4006,23 +4069,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>-6.4</v>
-      </c>
-      <c r="J30">
-        <v>-6.4</v>
-      </c>
       <c r="K30">
-        <v>0.023</v>
-      </c>
-      <c r="L30">
-        <v>0.3833333333333334</v>
+        <v>-44.3</v>
       </c>
       <c r="M30">
         <v>-0</v>
@@ -4031,7 +4079,7 @@
         <v>-0</v>
       </c>
       <c r="O30">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P30">
         <v>-0</v>
@@ -4040,73 +4088,79 @@
         <v>-0</v>
       </c>
       <c r="R30">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <v>0</v>
       </c>
       <c r="U30">
-        <v>0.032</v>
+        <v>99.7</v>
       </c>
       <c r="V30">
-        <v>0.0006049149338374292</v>
+        <v>0.5368874528809909</v>
       </c>
       <c r="W30">
-        <v>0.000222007722007722</v>
+        <v>-0.08670972793110197</v>
       </c>
       <c r="X30">
-        <v>0.04387296409148227</v>
+        <v>0.08217042843635584</v>
       </c>
       <c r="Y30">
-        <v>-0.04365095636947455</v>
+        <v>-0.1688801563674578</v>
       </c>
       <c r="Z30">
-        <v>0.0005805459066675697</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>-0.003715493802672447</v>
+        <v>-0.2214360815669685</v>
       </c>
       <c r="AB30">
-        <v>0.04387296409148227</v>
+        <v>0.06784455644733374</v>
       </c>
       <c r="AC30">
-        <v>-0.04758845789415472</v>
+        <v>-0.2892806380143022</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>0.4898488554217279</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>76.58984885542172</v>
       </c>
       <c r="AG30">
-        <v>-0.032</v>
+        <v>-23.11015114457828</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>0.2920046246152639</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>0.1237936083760113</v>
       </c>
       <c r="AJ30">
-        <v>-0.0006052810774003178</v>
+        <v>-0.1421377245090394</v>
       </c>
       <c r="AK30">
-        <v>-0.0002434052392977759</v>
+        <v>-0.04452910051236132</v>
       </c>
       <c r="AL30">
-        <v>0.002</v>
+        <v>1.85</v>
       </c>
       <c r="AM30">
-        <v>0.001</v>
+        <v>-0.9199999999999999</v>
+      </c>
+      <c r="AN30">
+        <v>-0.7601866003376386</v>
       </c>
       <c r="AO30">
-        <v>-192</v>
+        <v>-58.21621621621622</v>
+      </c>
+      <c r="AP30">
+        <v>0.2308544971338496</v>
       </c>
       <c r="AQ30">
-        <v>-384</v>
+        <v>117.0652173913044</v>
       </c>
     </row>
     <row r="31">
@@ -4117,7 +4171,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coreo AG (XTRA:CORE)</t>
+          <t>Sparta AG (DB:SPT6)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4125,26 +4179,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D31">
-        <v>7.255</v>
-      </c>
-      <c r="G31">
-        <v>-0.1685393258426966</v>
-      </c>
-      <c r="H31">
-        <v>-0.1685393258426966</v>
-      </c>
-      <c r="I31">
-        <v>-0.3274478330658106</v>
-      </c>
-      <c r="J31">
-        <v>-0.3274478330658106</v>
-      </c>
       <c r="K31">
-        <v>-2.94</v>
-      </c>
-      <c r="L31">
-        <v>-0.4719101123595505</v>
+        <v>-37.9</v>
       </c>
       <c r="M31">
         <v>-0</v>
@@ -4168,73 +4204,67 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>12.9</v>
+        <v>2.12</v>
       </c>
       <c r="V31">
-        <v>0.5512820512820513</v>
+        <v>0.03002832861189802</v>
       </c>
       <c r="W31">
-        <v>-0.0930379746835443</v>
+        <v>-0.2255952380952381</v>
       </c>
       <c r="X31">
-        <v>0.1073087426162502</v>
+        <v>0.07462315242080694</v>
       </c>
       <c r="Y31">
-        <v>-0.2003467172997945</v>
+        <v>-0.300218390516045</v>
       </c>
       <c r="Z31">
-        <v>0.08059508408796895</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>-0.02639068564036222</v>
+        <v>-0.2275202710879826</v>
       </c>
       <c r="AB31">
-        <v>0.03826416612977607</v>
+        <v>0.07112334060841725</v>
       </c>
       <c r="AC31">
-        <v>-0.06465485177013829</v>
+        <v>-0.2986436116963999</v>
       </c>
       <c r="AD31">
-        <v>73.7</v>
+        <v>6.5</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>73.7</v>
+        <v>6.5</v>
       </c>
       <c r="AG31">
-        <v>60.8</v>
+        <v>4.38</v>
       </c>
       <c r="AH31">
-        <v>0.7590113285272915</v>
+        <v>0.08430609597924774</v>
       </c>
       <c r="AI31">
-        <v>0.7005703422053232</v>
+        <v>0.05569837189374464</v>
       </c>
       <c r="AJ31">
-        <v>0.7220902612826604</v>
+        <v>0.05841557748732996</v>
       </c>
       <c r="AK31">
-        <v>0.6587215601300108</v>
+        <v>0.0382265665910281</v>
       </c>
       <c r="AL31">
-        <v>2.77</v>
+        <v>0.08</v>
       </c>
       <c r="AM31">
-        <v>2.648</v>
-      </c>
-      <c r="AN31">
-        <v>-59.43548387096774</v>
+        <v>-0.09499999999999999</v>
       </c>
       <c r="AO31">
-        <v>-0.7364620938628159</v>
-      </c>
-      <c r="AP31">
-        <v>-49.03225806451614</v>
+        <v>-470</v>
       </c>
       <c r="AQ31">
-        <v>-0.770392749244713</v>
+        <v>395.7894736842106</v>
       </c>
     </row>
     <row r="32">
@@ -4245,7 +4275,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MPC Münchmeyer Petersen Capital AG (XTRA:MPCK)</t>
+          <t>Mutares SE &amp; Co. KGaA (XTRA:MUX)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4254,121 +4284,121 @@
         </is>
       </c>
       <c r="D32">
-        <v>-0.0174</v>
+        <v>0.329</v>
       </c>
       <c r="E32">
-        <v>-0.313</v>
+        <v>0.07139999999999999</v>
+      </c>
+      <c r="F32">
+        <v>-0.254</v>
       </c>
       <c r="G32">
-        <v>0.02064777327935223</v>
+        <v>-0.05668152109328581</v>
       </c>
       <c r="H32">
-        <v>0.02064777327935223</v>
+        <v>-0.05802139037433155</v>
       </c>
       <c r="I32">
-        <v>-0.09372469635627531</v>
+        <v>-0.07620320855614973</v>
       </c>
       <c r="J32">
-        <v>-0.06195060422034107</v>
+        <v>-0.07620320855614973</v>
       </c>
       <c r="K32">
-        <v>1.45</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L32">
-        <v>0.02935222672064777</v>
+        <v>0.02008318478906714</v>
       </c>
       <c r="M32">
-        <v>1.93</v>
+        <v>-0</v>
       </c>
       <c r="N32">
-        <v>0.01413919413919414</v>
+        <v>-0</v>
       </c>
       <c r="O32">
-        <v>1.331034482758621</v>
+        <v>-0</v>
       </c>
       <c r="P32">
-        <v>1.93</v>
+        <v>-0</v>
       </c>
       <c r="Q32">
-        <v>0.01413919413919414</v>
+        <v>-0</v>
       </c>
       <c r="R32">
-        <v>1.331034482758621</v>
+        <v>-0</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
       <c r="U32">
-        <v>43.1</v>
+        <v>204.7</v>
       </c>
       <c r="V32">
-        <v>0.3157509157509157</v>
+        <v>0.5158770161290323</v>
       </c>
       <c r="W32">
-        <v>0.01435643564356436</v>
+        <v>0.1100439524662217</v>
       </c>
       <c r="X32">
-        <v>0.04427873666200317</v>
+        <v>0.1009042473547523</v>
       </c>
       <c r="Y32">
-        <v>-0.02992230101843882</v>
+        <v>0.009139705111469401</v>
       </c>
       <c r="Z32">
-        <v>0.6121437422552664</v>
+        <v>4.231301068510371</v>
       </c>
       <c r="AA32">
-        <v>-0.03792267470241448</v>
+        <v>-0.322438717787555</v>
       </c>
       <c r="AB32">
-        <v>0.04379086628932993</v>
+        <v>0.06676712939539466</v>
       </c>
       <c r="AC32">
-        <v>-0.08171354099174441</v>
+        <v>-0.3892058471829496</v>
       </c>
       <c r="AD32">
-        <v>2.75</v>
+        <v>479.2</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>2.75</v>
+        <v>479.2</v>
       </c>
       <c r="AG32">
-        <v>-40.35</v>
+        <v>274.5</v>
       </c>
       <c r="AH32">
-        <v>0.01974865350089767</v>
+        <v>0.5470319634703196</v>
       </c>
       <c r="AI32">
-        <v>0.0236152855302705</v>
+        <v>0.3962295353067636</v>
       </c>
       <c r="AJ32">
-        <v>-0.4196567862714509</v>
+        <v>0.4089080887829585</v>
       </c>
       <c r="AK32">
-        <v>-0.5501022494887526</v>
+        <v>0.2732158853389071</v>
       </c>
       <c r="AL32">
-        <v>0.045</v>
+        <v>32</v>
       </c>
       <c r="AM32">
-        <v>-2.465</v>
+        <v>25.43</v>
       </c>
       <c r="AN32">
-        <v>-1.267281105990783</v>
+        <v>-2.752441125789776</v>
       </c>
       <c r="AO32">
-        <v>-102.8888888888889</v>
+        <v>-8.015625</v>
       </c>
       <c r="AP32">
-        <v>18.59447004608295</v>
+        <v>-1.576680068925905</v>
       </c>
       <c r="AQ32">
-        <v>1.878296146044625</v>
+        <v>-10.08651199370822</v>
       </c>
     </row>
     <row r="33">
@@ -4379,7 +4409,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ERWE Immobilien AG (XTRA:ERWE)</t>
+          <t>Lloyd Fonds AG (XTRA:L1OA)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4387,29 +4417,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="E33">
-        <v>0.228</v>
+      <c r="D33">
+        <v>0.174</v>
       </c>
       <c r="F33">
-        <v>-0.394</v>
+        <v>0.154</v>
       </c>
       <c r="G33">
-        <v>-0.8458646616541353</v>
+        <v>0.1488636363636364</v>
       </c>
       <c r="H33">
-        <v>-0.8458646616541353</v>
+        <v>0.1488636363636364</v>
       </c>
       <c r="I33">
-        <v>-0.8596265085814098</v>
+        <v>-0.8806818181818181</v>
       </c>
       <c r="J33">
-        <v>-0.8596265085814098</v>
+        <v>-0.8806818181818181</v>
       </c>
       <c r="K33">
-        <v>0.314</v>
+        <v>-5.58</v>
       </c>
       <c r="L33">
-        <v>0.03934837092731829</v>
+        <v>-0.3170454545454545</v>
       </c>
       <c r="M33">
         <v>-0</v>
@@ -4418,7 +4448,7 @@
         <v>-0</v>
       </c>
       <c r="O33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P33">
         <v>-0</v>
@@ -4427,79 +4457,79 @@
         <v>-0</v>
       </c>
       <c r="R33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
       <c r="U33">
-        <v>9.74</v>
+        <v>12.9</v>
       </c>
       <c r="V33">
-        <v>0.1754954954954955</v>
+        <v>0.08939708939708939</v>
       </c>
       <c r="W33">
-        <v>0.00511400651465798</v>
+        <v>-0.1125</v>
       </c>
       <c r="X33">
-        <v>0.1051777137011564</v>
+        <v>0.0757030289591873</v>
       </c>
       <c r="Y33">
-        <v>-0.1000637071864984</v>
+        <v>-0.1882030289591873</v>
       </c>
       <c r="Z33">
-        <v>0.05827833626660214</v>
+        <v>0.3836930455635492</v>
       </c>
       <c r="AA33">
-        <v>-0.05009760273079255</v>
+        <v>-0.3379114889906257</v>
       </c>
       <c r="AB33">
-        <v>0.03831076106199889</v>
+        <v>0.07119425748362197</v>
       </c>
       <c r="AC33">
-        <v>-0.08840836379279143</v>
+        <v>-0.4091057464742476</v>
       </c>
       <c r="AD33">
-        <v>168.9</v>
+        <v>19.9</v>
       </c>
       <c r="AE33">
-        <v>0.02909769239824891</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>168.9290976923982</v>
+        <v>19.9</v>
       </c>
       <c r="AG33">
-        <v>159.1890976923982</v>
+        <v>6.999999999999998</v>
       </c>
       <c r="AH33">
-        <v>0.7527058631404913</v>
+        <v>0.1211936662606577</v>
       </c>
       <c r="AI33">
-        <v>0.7029073853912345</v>
+        <v>0.2363420427553444</v>
       </c>
       <c r="AJ33">
-        <v>0.7414866399992087</v>
+        <v>0.046265697290152</v>
       </c>
       <c r="AK33">
-        <v>0.6903583009147886</v>
+        <v>0.0981767180925666</v>
       </c>
       <c r="AL33">
-        <v>7.93</v>
+        <v>3.94</v>
       </c>
       <c r="AM33">
-        <v>7.914</v>
+        <v>1.97</v>
       </c>
       <c r="AN33">
-        <v>-25.11897679952409</v>
+        <v>-1.631147540983606</v>
       </c>
       <c r="AO33">
-        <v>-0.8675914249684742</v>
+        <v>-3.934010152284264</v>
       </c>
       <c r="AP33">
-        <v>-23.67476170321211</v>
+        <v>-0.5737704918032785</v>
       </c>
       <c r="AQ33">
-        <v>-0.8693454637351529</v>
+        <v>-7.868020304568528</v>
       </c>
     </row>
     <row r="34">
@@ -4510,7 +4540,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AURELIUS Equity Opportunities SE &amp; Co. KGaA (XTRA:AR4)</t>
+          <t>Heidelberger Beteiligungsholding AG (DB:IPOK)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4518,125 +4548,98 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D34">
-        <v>0.181</v>
-      </c>
-      <c r="E34">
-        <v>-0.121</v>
-      </c>
-      <c r="F34">
-        <v>0.006</v>
-      </c>
-      <c r="G34">
-        <v>-0.0253886506814861</v>
-      </c>
-      <c r="H34">
-        <v>-0.02680432126859415</v>
-      </c>
-      <c r="I34">
-        <v>-0.035475603037344</v>
-      </c>
-      <c r="J34">
-        <v>-0.035475603037344</v>
-      </c>
       <c r="K34">
-        <v>41.5</v>
-      </c>
-      <c r="L34">
-        <v>0.009940834071909359</v>
+        <v>-7.93</v>
       </c>
       <c r="M34">
-        <v>33.06</v>
+        <v>-0</v>
       </c>
       <c r="N34">
-        <v>0.03786074209803023</v>
+        <v>-0</v>
       </c>
       <c r="O34">
-        <v>0.7966265060240962</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>33.06</v>
+        <v>-0</v>
       </c>
       <c r="Q34">
-        <v>0.03786074209803023</v>
+        <v>-0</v>
       </c>
       <c r="R34">
-        <v>0.7966265060240962</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
       </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
       <c r="U34">
-        <v>275.6</v>
+        <v>5.64</v>
       </c>
       <c r="V34">
-        <v>0.315620705451214</v>
+        <v>0.2028776978417266</v>
       </c>
       <c r="W34">
-        <v>0.07746873249953332</v>
+        <v>-0.2178571428571429</v>
       </c>
       <c r="X34">
-        <v>0.05917021655349525</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y34">
-        <v>0.01829851594603807</v>
+        <v>-0.2903113618978477</v>
       </c>
       <c r="Z34">
-        <v>4.097261752870743</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>-0.1453528314849347</v>
+        <v>-0.3555641721597519</v>
       </c>
       <c r="AB34">
-        <v>0.04207850211722136</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC34">
-        <v>-0.1874313336021561</v>
+        <v>-0.4280183912004568</v>
       </c>
       <c r="AD34">
-        <v>663.2</v>
+        <v>0</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>663.2</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>387.6</v>
+        <v>-5.64</v>
       </c>
       <c r="AH34">
-        <v>0.431658422285863</v>
+        <v>0</v>
       </c>
       <c r="AI34">
-        <v>0.5341925090616191</v>
+        <v>0</v>
       </c>
       <c r="AJ34">
-        <v>0.3074238578680203</v>
+        <v>-0.2545126353790614</v>
       </c>
       <c r="AK34">
-        <v>0.4012837767884875</v>
+        <v>-0.3055254604550379</v>
       </c>
       <c r="AL34">
-        <v>39.5</v>
+        <v>0.002</v>
       </c>
       <c r="AM34">
-        <v>32.43</v>
+        <v>-1.228</v>
       </c>
       <c r="AN34">
-        <v>-8.416243654822336</v>
+        <v>-0</v>
       </c>
       <c r="AO34">
-        <v>-3.749367088607595</v>
+        <v>-4585</v>
       </c>
       <c r="AP34">
-        <v>-4.918781725888326</v>
+        <v>0.6150490730643402</v>
       </c>
       <c r="AQ34">
-        <v>-4.566759173604687</v>
+        <v>7.46742671009772</v>
       </c>
     </row>
     <row r="35">
@@ -4647,7 +4650,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camerit AG (DB:RTML)</t>
+          <t>Panamax AG (DB:ICP)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4655,26 +4658,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D35">
-        <v>-0.386</v>
-      </c>
       <c r="G35">
-        <v>-10.13138686131387</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>-10.14598540145985</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>-9.5487574192352</v>
+        <v>-40.61083623480545</v>
       </c>
       <c r="J35">
-        <v>-8.041625470314198</v>
+        <v>-40.61083623480545</v>
       </c>
       <c r="K35">
-        <v>7.47</v>
+        <v>-0.125</v>
       </c>
       <c r="L35">
-        <v>54.52554744525547</v>
+        <v>-41.66666666666666</v>
       </c>
       <c r="M35">
         <v>-0</v>
@@ -4683,7 +4683,7 @@
         <v>-0</v>
       </c>
       <c r="O35">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P35">
         <v>-0</v>
@@ -4692,79 +4692,73 @@
         <v>-0</v>
       </c>
       <c r="R35">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
       <c r="U35">
-        <v>10.4</v>
+        <v>0.003</v>
       </c>
       <c r="V35">
-        <v>1.765704584040747</v>
-      </c>
-      <c r="W35">
-        <v>1.412098298676749</v>
+        <v>0.001863354037267081</v>
       </c>
       <c r="X35">
-        <v>0.04425218678777997</v>
-      </c>
-      <c r="Y35">
-        <v>1.367846111888969</v>
+        <v>0.07258828784360143</v>
       </c>
       <c r="Z35">
-        <v>0.02679497570690072</v>
+        <v>2.580548549810843</v>
       </c>
       <c r="AA35">
-        <v>-0.215475159121063</v>
+        <v>-104.7982345523329</v>
       </c>
       <c r="AB35">
-        <v>0.04379613871301344</v>
+        <v>0.07253957512335406</v>
       </c>
       <c r="AC35">
-        <v>-0.2592712978340765</v>
+        <v>-104.8707741274562</v>
       </c>
       <c r="AD35">
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>0.1108988321761124</v>
+        <v>0.009162543522081731</v>
       </c>
       <c r="AF35">
-        <v>0.1108988321761124</v>
+        <v>0.009162543522081731</v>
       </c>
       <c r="AG35">
-        <v>-10.28910116782389</v>
+        <v>0.006162543522081731</v>
       </c>
       <c r="AH35">
-        <v>0.01848037023745274</v>
+        <v>0.005658816379330834</v>
       </c>
       <c r="AI35">
-        <v>0.0127310435252074</v>
+        <v>1</v>
       </c>
       <c r="AJ35">
-        <v>2.338909876199464</v>
+        <v>0.003813071616331226</v>
       </c>
       <c r="AK35">
-        <v>6.091465309374922</v>
+        <v>1</v>
       </c>
       <c r="AL35">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AM35">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AN35">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO35">
-        <v>-699.9999999999999</v>
+        <v>-43.33333333333334</v>
       </c>
       <c r="AP35">
-        <v>8.063558908952892</v>
+        <v>0.616254352208173</v>
       </c>
       <c r="AQ35">
-        <v>-699.9999999999999</v>
+        <v>-43.33333333333334</v>
       </c>
     </row>
     <row r="36">
@@ -4775,7 +4769,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Value Management &amp; Research AG (DB:VMR1)</t>
+          <t>Tio Tech A (NasdaqCM:TIOA)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4783,26 +4777,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D36">
-        <v>0.387</v>
-      </c>
-      <c r="G36">
-        <v>0.05811320754716981</v>
-      </c>
-      <c r="H36">
-        <v>0.05811320754716981</v>
-      </c>
-      <c r="I36">
-        <v>0.05729559748427673</v>
-      </c>
-      <c r="J36">
-        <v>0.05729559748427673</v>
-      </c>
       <c r="K36">
-        <v>-0.146</v>
-      </c>
-      <c r="L36">
-        <v>-0.009182389937106917</v>
+        <v>11.4</v>
       </c>
       <c r="M36">
         <v>-0</v>
@@ -4811,7 +4787,7 @@
         <v>-0</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P36">
         <v>-0</v>
@@ -4820,79 +4796,61 @@
         <v>-0</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S36">
         <v>0</v>
       </c>
       <c r="U36">
-        <v>0.502</v>
+        <v>0.021</v>
       </c>
       <c r="V36">
-        <v>0.04403508771929825</v>
+        <v>4.830917874396136e-05</v>
       </c>
       <c r="W36">
-        <v>-0.04171428571428571</v>
+        <v>-0.5454545454545455</v>
       </c>
       <c r="X36">
-        <v>0.1262040245006184</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y36">
-        <v>-0.1679183102149041</v>
-      </c>
-      <c r="Z36">
-        <v>-4.206349206349207</v>
-      </c>
-      <c r="AA36">
-        <v>-0.2410052910052911</v>
+        <v>-0.6179087644952503</v>
       </c>
       <c r="AB36">
-        <v>0.04053292181526513</v>
-      </c>
-      <c r="AC36">
-        <v>-0.2815382128205562</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD36">
-        <v>46.6</v>
+        <v>0</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>46.6</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>46.098</v>
+        <v>-0.021</v>
       </c>
       <c r="AH36">
-        <v>0.803448275862069</v>
+        <v>0</v>
       </c>
       <c r="AI36">
-        <v>0.8161120840630472</v>
+        <v>-0</v>
       </c>
       <c r="AJ36">
-        <v>0.8017322341646667</v>
+        <v>-4.831151263346056e-05</v>
       </c>
       <c r="AK36">
-        <v>0.8144810770698612</v>
+        <v>0.001822758441107543</v>
       </c>
       <c r="AL36">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AM36">
-        <v>1.412</v>
-      </c>
-      <c r="AN36">
-        <v>36.12403100775194</v>
-      </c>
-      <c r="AO36">
-        <v>0.6415492957746479</v>
-      </c>
-      <c r="AP36">
-        <v>35.73488372093023</v>
+        <v>-1.43</v>
       </c>
       <c r="AQ36">
-        <v>0.6451841359773371</v>
+        <v>1.510489510489511</v>
       </c>
     </row>
     <row r="37">
@@ -4903,7 +4861,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MLP SE (XTRA:MLP)</t>
+          <t>European Healthcare Acquisition &amp; Growth Company B.V. (ENXTAM:EHCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4911,80 +4869,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D37">
-        <v>0.0764</v>
-      </c>
-      <c r="E37">
-        <v>0.168</v>
-      </c>
-      <c r="G37">
-        <v>0.08161831141451661</v>
-      </c>
-      <c r="H37">
-        <v>0.08161831141451661</v>
-      </c>
-      <c r="I37">
-        <v>0.09145668105611886</v>
-      </c>
-      <c r="J37">
-        <v>0.06747655242505932</v>
-      </c>
       <c r="K37">
-        <v>64.7</v>
-      </c>
-      <c r="L37">
-        <v>0.06495331793996587</v>
+        <v>-5.75</v>
       </c>
       <c r="M37">
-        <v>26.6</v>
+        <v>-0</v>
       </c>
       <c r="N37">
-        <v>0.02507777882530405</v>
+        <v>-0</v>
       </c>
       <c r="O37">
-        <v>0.41112828438949</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>26.6</v>
+        <v>-0</v>
       </c>
       <c r="Q37">
-        <v>0.02507777882530405</v>
+        <v>-0</v>
       </c>
       <c r="R37">
-        <v>0.41112828438949</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
       </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
       <c r="U37">
-        <v>1507.6</v>
+        <v>213.6</v>
       </c>
       <c r="V37">
-        <v>1.421325539737909</v>
-      </c>
-      <c r="W37">
-        <v>0.1283220944069814</v>
+        <v>1.004231311706629</v>
       </c>
       <c r="X37">
-        <v>0.04387296409148227</v>
-      </c>
-      <c r="Y37">
-        <v>0.08444913031549908</v>
-      </c>
-      <c r="Z37">
-        <v>-4.060741948634325</v>
-      </c>
-      <c r="AA37">
-        <v>-0.2740048669816616</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB37">
-        <v>0.04387296409148227</v>
-      </c>
-      <c r="AC37">
-        <v>-0.3178778310731439</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD37">
         <v>0</v>
@@ -4996,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="AG37">
-        <v>-1507.6</v>
+        <v>-213.6</v>
       </c>
       <c r="AH37">
         <v>0</v>
@@ -5005,28 +4924,22 @@
         <v>0</v>
       </c>
       <c r="AJ37">
-        <v>3.373461624524503</v>
+        <v>237.3333333333318</v>
       </c>
       <c r="AK37">
-        <v>1.551028806584362</v>
+        <v>1.004940014114326</v>
       </c>
       <c r="AL37">
-        <v>4.8</v>
+        <v>1.92</v>
       </c>
       <c r="AM37">
-        <v>3.62</v>
-      </c>
-      <c r="AN37">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AO37">
-        <v>18.97916666666667</v>
-      </c>
-      <c r="AP37">
-        <v>-14.72265625</v>
+        <v>-1.197916666666667</v>
       </c>
       <c r="AQ37">
-        <v>25.16574585635359</v>
+        <v>-1.197916666666667</v>
       </c>
     </row>
     <row r="38">
@@ -5037,7 +4950,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mutares SE &amp; Co. KGaA (XTRA:MUX)</t>
+          <t>Quirin Privatbank AG (XTRA:QB7)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5046,121 +4959,106 @@
         </is>
       </c>
       <c r="D38">
-        <v>0.248</v>
-      </c>
-      <c r="F38">
-        <v>-0.254</v>
+        <v>0.08310000000000001</v>
+      </c>
+      <c r="E38">
+        <v>0.302</v>
       </c>
       <c r="G38">
-        <v>-0.05401427115188583</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>-0.05512742099898063</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>-0.07775739041794087</v>
+        <v>-0.02091652089170587</v>
       </c>
       <c r="J38">
-        <v>-0.07775739041794087</v>
+        <v>-0.01806279401035685</v>
       </c>
       <c r="K38">
-        <v>468.8</v>
+        <v>11.1</v>
       </c>
       <c r="L38">
-        <v>0.1911518858307849</v>
+        <v>0.167420814479638</v>
       </c>
       <c r="M38">
-        <v>30.36</v>
+        <v>6.336399999999999</v>
       </c>
       <c r="N38">
-        <v>0.0573262839879154</v>
+        <v>0.04138732854343566</v>
       </c>
       <c r="O38">
-        <v>0.06476109215017065</v>
+        <v>0.5708468468468468</v>
       </c>
       <c r="P38">
-        <v>27.4</v>
+        <v>6.336399999999999</v>
       </c>
       <c r="Q38">
-        <v>0.05173716012084591</v>
+        <v>0.04138732854343566</v>
       </c>
       <c r="R38">
-        <v>0.05844709897610921</v>
+        <v>0.5708468468468468</v>
       </c>
       <c r="S38">
-        <v>2.960000000000001</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>0.0974967061923584</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>291.8</v>
+        <v>378.2</v>
       </c>
       <c r="V38">
-        <v>0.5509818731117825</v>
+        <v>2.470280862181581</v>
       </c>
       <c r="W38">
-        <v>2.624860022396417</v>
+        <v>0.1423076923076923</v>
       </c>
       <c r="X38">
-        <v>0.06186149961015634</v>
+        <v>0.08801752111966646</v>
       </c>
       <c r="Y38">
-        <v>2.56299852278626</v>
-      </c>
-      <c r="Z38">
-        <v>6.343766166580444</v>
-      </c>
-      <c r="AA38">
-        <v>-0.4932747025349197</v>
+        <v>0.05429017118802584</v>
       </c>
       <c r="AB38">
-        <v>0.04191173881784307</v>
-      </c>
-      <c r="AC38">
-        <v>-0.5351864413527628</v>
+        <v>0.0683183542253476</v>
       </c>
       <c r="AD38">
-        <v>473</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>11.24382667560049</v>
       </c>
       <c r="AF38">
-        <v>473</v>
+        <v>101.1438266756005</v>
       </c>
       <c r="AG38">
-        <v>181.2</v>
+        <v>-277.0561733243995</v>
       </c>
       <c r="AH38">
-        <v>0.4717733891881109</v>
+        <v>0.3978221536314973</v>
       </c>
       <c r="AI38">
-        <v>0.426702751465945</v>
+        <v>0.5958615912960281</v>
       </c>
       <c r="AJ38">
-        <v>0.2549240292628025</v>
+        <v>2.235113959184023</v>
       </c>
       <c r="AK38">
-        <v>0.2218684951634627</v>
+        <v>1.329085960401109</v>
       </c>
       <c r="AL38">
-        <v>26.9</v>
+        <v>0</v>
       </c>
       <c r="AM38">
-        <v>25.12</v>
+        <v>0</v>
       </c>
       <c r="AN38">
-        <v>-2.712155963302752</v>
-      </c>
-      <c r="AO38">
-        <v>-7.089219330855019</v>
+        <v>104.292343387471</v>
       </c>
       <c r="AP38">
-        <v>-1.038990825688073</v>
-      </c>
-      <c r="AQ38">
-        <v>-7.591560509554141</v>
+        <v>-321.4108739262175</v>
       </c>
     </row>
     <row r="39">
@@ -5171,7 +5069,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GBK Beteiligungen AG (HMSE:GBQ)</t>
+          <t>tokentus investment AG (XTRA:14D)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5179,26 +5077,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D39">
-        <v>0.005829999999999999</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>-0.01254480286738351</v>
-      </c>
-      <c r="J39">
-        <v>-0.01254480286738351</v>
-      </c>
       <c r="K39">
-        <v>-16.4</v>
-      </c>
-      <c r="L39">
-        <v>-5.878136200716845</v>
+        <v>-1.57</v>
       </c>
       <c r="M39">
         <v>-0</v>
@@ -5222,16 +5102,16 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>7.96</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.010152284263959</v>
       </c>
       <c r="X39">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB39">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -5243,19 +5123,37 @@
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>-7.96</v>
       </c>
       <c r="AH39">
         <v>0</v>
       </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>99.49999999999991</v>
+      </c>
+      <c r="AK39">
+        <v>-1.411347517730497</v>
       </c>
       <c r="AL39">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM39">
-        <v>0</v>
+        <v>-0.015</v>
+      </c>
+      <c r="AN39">
+        <v>-0</v>
+      </c>
+      <c r="AO39">
+        <v>-795</v>
+      </c>
+      <c r="AP39">
+        <v>5.070063694267516</v>
+      </c>
+      <c r="AQ39">
+        <v>106</v>
       </c>
     </row>
     <row r="40">
@@ -5266,7 +5164,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Murphy&amp;Spitz Green Capital Aktiengesellschaft (DUSE:6MP)</t>
+          <t>NABAG Anlage- Und Beteiligungs AG (HMSE:NAB)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5274,23 +5172,11 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G40">
-        <v>-0.05596107055961071</v>
-      </c>
-      <c r="H40">
-        <v>-0.05596107055961071</v>
-      </c>
-      <c r="I40">
-        <v>-0.1046228710462287</v>
-      </c>
-      <c r="J40">
-        <v>-0.1046228710462287</v>
+      <c r="E40">
+        <v>0.598</v>
       </c>
       <c r="K40">
-        <v>0.082</v>
-      </c>
-      <c r="L40">
-        <v>0.1995133819951338</v>
+        <v>0.097</v>
       </c>
       <c r="M40">
         <v>-0</v>
@@ -5320,10 +5206,10 @@
         <v>0</v>
       </c>
       <c r="X40">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB40">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD40">
         <v>0</v>
@@ -5347,16 +5233,10 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-0.125</v>
-      </c>
-      <c r="AN40">
-        <v>-0</v>
-      </c>
-      <c r="AP40">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="AQ40">
-        <v>0.344</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="41">
@@ -5367,7 +5247,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NABAG Anlage- Und Beteiligungs AG (HMSE:NAB)</t>
+          <t>Lena Beteiligungs AG (HMSE:L1A)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5375,68 +5255,86 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>-4.294117647058823</v>
+      </c>
+      <c r="J41">
+        <v>-4.294117647058823</v>
+      </c>
       <c r="K41">
+        <v>-0.077</v>
+      </c>
+      <c r="L41">
+        <v>-4.529411764705882</v>
+      </c>
+      <c r="M41">
+        <v>-0</v>
+      </c>
+      <c r="N41">
+        <v>-0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>-0</v>
+      </c>
+      <c r="Q41">
+        <v>-0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AB41">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41">
+        <v>0</v>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
         <v>0.001</v>
       </c>
-      <c r="M41">
-        <v>-0</v>
-      </c>
-      <c r="N41">
-        <v>-0</v>
-      </c>
-      <c r="O41">
-        <v>-0</v>
-      </c>
-      <c r="P41">
-        <v>-0</v>
-      </c>
-      <c r="Q41">
-        <v>-0</v>
-      </c>
-      <c r="R41">
-        <v>-0</v>
-      </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="U41">
-        <v>0</v>
-      </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="X41">
-        <v>0.04387296409148227</v>
-      </c>
-      <c r="AB41">
-        <v>0.04387296409148227</v>
-      </c>
-      <c r="AD41">
-        <v>0</v>
-      </c>
-      <c r="AE41">
-        <v>0</v>
-      </c>
-      <c r="AF41">
-        <v>0</v>
-      </c>
-      <c r="AG41">
-        <v>0</v>
-      </c>
-      <c r="AH41">
-        <v>0</v>
-      </c>
-      <c r="AJ41">
-        <v>0</v>
-      </c>
-      <c r="AL41">
-        <v>0</v>
-      </c>
       <c r="AM41">
-        <v>-0.01</v>
+        <v>0.001</v>
+      </c>
+      <c r="AO41">
+        <v>-73</v>
       </c>
       <c r="AQ41">
-        <v>3.4</v>
+        <v>-73</v>
       </c>
     </row>
     <row r="42">
@@ -5447,7 +5345,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Trade &amp; Value AG (HMSE:TAV)</t>
+          <t>Planet Home Investment AG (BST:ILK1)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5455,26 +5353,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D42">
-        <v>0.286</v>
-      </c>
       <c r="G42">
-        <v>-0.01357798165137615</v>
+        <v>-3.434065934065934</v>
       </c>
       <c r="H42">
-        <v>-0.01357798165137615</v>
+        <v>-3.434065934065934</v>
       </c>
       <c r="I42">
-        <v>-0.01394495412844037</v>
+        <v>-5.549450549450549</v>
       </c>
       <c r="J42">
-        <v>-0.01394495412844037</v>
+        <v>-5.549450549450549</v>
       </c>
       <c r="K42">
-        <v>-0.341</v>
+        <v>-2.04</v>
       </c>
       <c r="L42">
-        <v>-0.03128440366972477</v>
+        <v>-5.604395604395605</v>
       </c>
       <c r="M42">
         <v>-0</v>
@@ -5504,10 +5399,10 @@
         <v>0</v>
       </c>
       <c r="X42">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB42">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -5528,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="AL42">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="AM42">
         <v>0.016</v>
@@ -5537,114 +5432,13 @@
         <v>-0</v>
       </c>
       <c r="AO42">
-        <v>-9.5</v>
+        <v>-112.2222222222222</v>
       </c>
       <c r="AP42">
         <v>-0</v>
       </c>
       <c r="AQ42">
-        <v>-9.5</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Lena Beteiligungs AG (HMSE:L1A)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>-0.332</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>-3.857142857142857</v>
-      </c>
-      <c r="J43">
-        <v>-3.857142857142857</v>
-      </c>
-      <c r="K43">
-        <v>-0.042</v>
-      </c>
-      <c r="L43">
-        <v>-6</v>
-      </c>
-      <c r="M43">
-        <v>-0</v>
-      </c>
-      <c r="N43">
-        <v>-0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>-0</v>
-      </c>
-      <c r="Q43">
-        <v>-0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>0.04387296409148227</v>
-      </c>
-      <c r="AB43">
-        <v>0.04387296409148227</v>
-      </c>
-      <c r="AD43">
-        <v>0</v>
-      </c>
-      <c r="AE43">
-        <v>0</v>
-      </c>
-      <c r="AF43">
-        <v>0</v>
-      </c>
-      <c r="AG43">
-        <v>0</v>
-      </c>
-      <c r="AH43">
-        <v>0</v>
-      </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
-      <c r="AL43">
-        <v>0.005</v>
-      </c>
-      <c r="AM43">
-        <v>0.005</v>
-      </c>
-      <c r="AO43">
-        <v>-5.399999999999999</v>
-      </c>
-      <c r="AQ43">
-        <v>-5.399999999999999</v>
+        <v>-126.25</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ42"/>
+  <dimension ref="A1:AQ44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08865000000000001</v>
+        <v>0.0269</v>
       </c>
       <c r="E2">
-        <v>0.205</v>
+        <v>0.01038</v>
       </c>
       <c r="F2">
-        <v>0.111</v>
+        <v>0.03855</v>
       </c>
       <c r="G2">
-        <v>0.1132358172111711</v>
+        <v>0.08088836132667929</v>
       </c>
       <c r="H2">
-        <v>0.1074716911396</v>
+        <v>0.07683297677027479</v>
       </c>
       <c r="I2">
-        <v>0.05921890461852366</v>
+        <v>0.04819596435046218</v>
       </c>
       <c r="J2">
-        <v>0.05243150751464514</v>
+        <v>0.04384731490402789</v>
       </c>
       <c r="K2">
-        <v>999.2329999999999</v>
+        <v>1064.747</v>
       </c>
       <c r="L2">
-        <v>0.07506457691742831</v>
+        <v>0.06942055530993603</v>
       </c>
       <c r="M2">
-        <v>128.46371</v>
+        <v>123.75865</v>
       </c>
       <c r="N2">
-        <v>0.01113334065365885</v>
+        <v>0.009563816140274956</v>
       </c>
       <c r="O2">
-        <v>0.1285623172973671</v>
+        <v>0.1162329173033594</v>
       </c>
       <c r="P2">
-        <v>128.14771</v>
+        <v>116.27865</v>
       </c>
       <c r="Q2">
-        <v>0.011105954431927</v>
+        <v>0.008985776991259863</v>
       </c>
       <c r="R2">
-        <v>0.1282460747393251</v>
+        <v>0.1092077742412047</v>
       </c>
       <c r="S2">
-        <v>0.3159999999999989</v>
+        <v>7.48</v>
       </c>
       <c r="T2">
-        <v>0.00245983865793693</v>
+        <v>0.06044021973413576</v>
       </c>
       <c r="U2">
-        <v>2486.338</v>
+        <v>2303.499</v>
       </c>
       <c r="V2">
-        <v>0.2154791258491354</v>
+        <v>0.178009706111914</v>
       </c>
       <c r="W2">
-        <v>0.001943402147206495</v>
+        <v>-0.005686926811724511</v>
       </c>
       <c r="X2">
-        <v>0.07347764511358229</v>
+        <v>0.06258858872067452</v>
       </c>
       <c r="Y2">
-        <v>-0.0715342429663758</v>
+        <v>-0.06827551553239904</v>
       </c>
       <c r="Z2">
-        <v>1.282149588602843</v>
+        <v>1.251297916733699</v>
       </c>
       <c r="AA2">
-        <v>-0.008457387843040842</v>
+        <v>-0.0006943583631465058</v>
       </c>
       <c r="AB2">
-        <v>0.07182240185627822</v>
+        <v>0.06208635409046343</v>
       </c>
       <c r="AC2">
-        <v>-0.07768284985717794</v>
+        <v>-0.05504201365170517</v>
       </c>
       <c r="AD2">
-        <v>2170.429</v>
+        <v>2186.18</v>
       </c>
       <c r="AE2">
-        <v>18.99482214676379</v>
+        <v>31.8749335576385</v>
       </c>
       <c r="AF2">
-        <v>2189.423822146764</v>
+        <v>2218.054933557638</v>
       </c>
       <c r="AG2">
-        <v>-296.9141778532367</v>
+        <v>-85.44406644236187</v>
       </c>
       <c r="AH2">
-        <v>0.1594851550186042</v>
+        <v>0.1463255705041777</v>
       </c>
       <c r="AI2">
-        <v>0.1540918455624718</v>
+        <v>0.1425369301935369</v>
       </c>
       <c r="AJ2">
-        <v>-0.02641177563344595</v>
+        <v>-0.006646831896366096</v>
       </c>
       <c r="AK2">
-        <v>-0.02532916379176706</v>
+        <v>-0.00644483141960506</v>
       </c>
       <c r="AL2">
-        <v>128.711</v>
+        <v>202.136</v>
       </c>
       <c r="AM2">
-        <v>80.227</v>
+        <v>131.733</v>
       </c>
       <c r="AN2">
-        <v>1.915450037374781</v>
+        <v>2.037429322587229</v>
       </c>
       <c r="AO2">
-        <v>6.125684673415637</v>
+        <v>3.660025923140856</v>
       </c>
       <c r="AP2">
-        <v>-0.2620331156034519</v>
+        <v>-0.07963033529295828</v>
       </c>
       <c r="AQ2">
-        <v>9.827651538758772</v>
+        <v>5.616079494128275</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clere AG (HMSE:CAG0)</t>
+          <t>SGT German Private Equity GmbH &amp; Co. KGaA (XTRA:SGF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,91 +725,106 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.6616702355460384</v>
+        <v>0.2557200538358008</v>
       </c>
       <c r="H3">
-        <v>0.6616702355460384</v>
+        <v>0.2557200538358008</v>
       </c>
       <c r="I3">
-        <v>0.2462526766595289</v>
+        <v>0.0740242261103634</v>
       </c>
       <c r="J3">
-        <v>0.1231263383297644</v>
+        <v>0.0740242261103634</v>
       </c>
       <c r="K3">
-        <v>-0.767</v>
+        <v>7.32</v>
       </c>
       <c r="L3">
-        <v>-0.01642398286937901</v>
+        <v>0.9851951547779274</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>8.540000000000001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1150943396226415</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.06</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01428571428571429</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.1448087431693989</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>7.48</v>
+      </c>
+      <c r="T3">
+        <v>0.8758782201405152</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.0215633423180593</v>
+      </c>
+      <c r="W3">
+        <v>0.1521829521829522</v>
       </c>
       <c r="X3">
-        <v>0.07245421904070486</v>
+        <v>0.06252462135488095</v>
+      </c>
+      <c r="Y3">
+        <v>0.08965833082807124</v>
       </c>
       <c r="AB3">
-        <v>0.07245421904070486</v>
+        <v>0.06217539663494734</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.975</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.975</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-0.6250000000000001</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.01296973727968075</v>
+      </c>
+      <c r="AI3">
+        <v>0.009097270818754374</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.008494733265375469</v>
+      </c>
+      <c r="AK3">
+        <v>-0.005919962112242483</v>
       </c>
       <c r="AL3">
-        <v>9.82</v>
+        <v>0.296</v>
       </c>
       <c r="AM3">
-        <v>8.77</v>
+        <v>-0.08300000000000002</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.5131578947368421</v>
       </c>
       <c r="AO3">
-        <v>1.171079429735234</v>
+        <v>1.858108108108108</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>-0.3289473684210527</v>
       </c>
       <c r="AQ3">
-        <v>1.311288483466363</v>
+        <v>-6.626506024096384</v>
       </c>
     </row>
     <row r="4">
@@ -820,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MLP SE (XTRA:MLP)</t>
+          <t>GBK Beteiligungen AG (BST:GBQ)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,70 +844,64 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09</v>
+        <v>-0.00628</v>
       </c>
       <c r="E4">
-        <v>0.323</v>
+        <v>-0.319</v>
       </c>
       <c r="G4">
-        <v>0.1204989384288747</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.1192144373673036</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.09915074309978769</v>
+        <v>0.6561032863849765</v>
       </c>
       <c r="J4">
-        <v>0.06671443188964044</v>
+        <v>0.6561032863849765</v>
       </c>
       <c r="K4">
-        <v>64.5</v>
+        <v>0.546</v>
       </c>
       <c r="L4">
-        <v>0.06847133757961783</v>
+        <v>0.06408450704225353</v>
       </c>
       <c r="M4">
-        <v>25.016</v>
+        <v>0.7222499999999999</v>
       </c>
       <c r="N4">
-        <v>0.04167249708479094</v>
+        <v>0.02046033994334278</v>
       </c>
       <c r="O4">
-        <v>0.38784496124031</v>
+        <v>1.322802197802198</v>
       </c>
       <c r="P4">
-        <v>24.7</v>
+        <v>0.7222499999999999</v>
       </c>
       <c r="Q4">
-        <v>0.04114609361985674</v>
+        <v>0.02046033994334278</v>
       </c>
       <c r="R4">
-        <v>0.3829457364341085</v>
+        <v>1.322802197802198</v>
       </c>
       <c r="S4">
-        <v>0.3159999999999989</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.01263191557403258</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.629185407296352</v>
-      </c>
-      <c r="W4">
-        <v>0.1205832865956254</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="Y4">
-        <v>0.0481290675549205</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB4">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -904,37 +913,19 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-978</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
       <c r="AJ4">
-        <v>2.589356632247815</v>
-      </c>
-      <c r="AK4">
-        <v>2.051174496644295</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>2.82</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>18.34970530451866</v>
-      </c>
-      <c r="AP4">
-        <v>-9.504373177842565</v>
-      </c>
-      <c r="AQ4">
-        <v>33.12056737588653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -945,7 +936,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Netfonds AG (DB:NF4)</t>
+          <t>DG-Gruppe AG (HMSE:DG6)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,53 +945,50 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.225</v>
+        <v>0.0505</v>
       </c>
       <c r="E5">
-        <v>0.6759999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="G5">
-        <v>0.07825295723384895</v>
+        <v>0.02671480144404332</v>
       </c>
       <c r="H5">
-        <v>0.07825295723384895</v>
+        <v>0.02671480144404332</v>
       </c>
       <c r="I5">
-        <v>0.06005459508644222</v>
+        <v>0.02093862815884477</v>
       </c>
       <c r="J5">
-        <v>0.05536143969264988</v>
+        <v>0.02028429602888087</v>
       </c>
       <c r="K5">
-        <v>9.550000000000001</v>
+        <v>0.031</v>
       </c>
       <c r="L5">
-        <v>0.04344858962693358</v>
+        <v>0.0111913357400722</v>
       </c>
       <c r="M5">
-        <v>0.62764</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.006606736842105263</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.06572146596858638</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.62764</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.006606736842105263</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.06572146596858638</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
         <v>0</v>
       </c>
@@ -1008,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB5">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1032,22 +1020,22 @@
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>2.93</v>
+        <v>0.042</v>
       </c>
       <c r="AM5">
-        <v>2.108</v>
+        <v>0.027</v>
       </c>
       <c r="AN5">
         <v>0</v>
       </c>
       <c r="AO5">
-        <v>4.505119453924914</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="AP5">
         <v>0</v>
       </c>
       <c r="AQ5">
-        <v>6.261859582542693</v>
+        <v>2.148148148148148</v>
       </c>
     </row>
     <row r="6">
@@ -1058,7 +1046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>capsensixx AG (XTRA:CPX)</t>
+          <t>U.C.A. Aktiengesellschaft (DB:UCA1)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1066,45 +1054,36 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G6">
-        <v>0.0513787281935847</v>
-      </c>
-      <c r="H6">
-        <v>0.0513787281935847</v>
-      </c>
-      <c r="I6">
-        <v>0.04890264490714688</v>
-      </c>
-      <c r="J6">
-        <v>0.0351504950457445</v>
+      <c r="E6">
+        <v>0.119</v>
       </c>
       <c r="K6">
-        <v>3.04</v>
-      </c>
-      <c r="L6">
-        <v>0.01710748452447946</v>
+        <v>1.16</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>1.99983</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.1092803278688525</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>1.723991379310345</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>1.99983</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.1092803278688525</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>1.723991379310345</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
         <v>0</v>
       </c>
@@ -1112,52 +1091,46 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>0.07493330833489958</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB6">
-        <v>0.07095114655702905</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD6">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>0.09521393539658379</v>
-      </c>
-      <c r="AI6">
-        <v>0.2090605272929818</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0.09521393539658379</v>
-      </c>
-      <c r="AK6">
-        <v>0.2090605272929818</v>
+        <v>0</v>
       </c>
       <c r="AL6">
-        <v>0.091</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AM6">
-        <v>0.091</v>
+        <v>-0.225</v>
       </c>
       <c r="AN6">
-        <v>0.6269487750556793</v>
+        <v>0</v>
       </c>
       <c r="AO6">
-        <v>95.49450549450549</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="AP6">
-        <v>0.6269487750556793</v>
+        <v>0</v>
       </c>
       <c r="AQ6">
-        <v>95.49450549450549</v>
+        <v>-0.7155555555555556</v>
       </c>
     </row>
     <row r="7">
@@ -1168,7 +1141,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.C.A. Aktiengesellschaft (DB:UCA1)</t>
+          <t>Netfonds AG (DB:NF4)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1176,29 +1149,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.158</v>
+      </c>
       <c r="E7">
-        <v>0.507</v>
+        <v>-0.0222</v>
+      </c>
+      <c r="G7">
+        <v>0.03961276818419676</v>
+      </c>
+      <c r="H7">
+        <v>0.03961276818419676</v>
+      </c>
+      <c r="I7">
+        <v>0.02354788069073784</v>
+      </c>
+      <c r="J7">
+        <v>0.01177394034536892</v>
       </c>
       <c r="K7">
-        <v>3.02</v>
+        <v>0.909</v>
+      </c>
+      <c r="L7">
+        <v>0.004756671899529043</v>
       </c>
       <c r="M7">
-        <v>2.12443</v>
+        <v>0.6221100000000001</v>
       </c>
       <c r="N7">
-        <v>0.1136058823529412</v>
+        <v>0.005629954751131222</v>
       </c>
       <c r="O7">
-        <v>0.703453642384106</v>
+        <v>0.6843894389438945</v>
       </c>
       <c r="P7">
-        <v>2.12443</v>
+        <v>0.6221100000000001</v>
       </c>
       <c r="Q7">
-        <v>0.1136058823529412</v>
+        <v>0.005629954751131222</v>
       </c>
       <c r="R7">
-        <v>0.703453642384106</v>
+        <v>0.6843894389438945</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1213,10 +1204,10 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB7">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1237,19 +1228,22 @@
         <v>0</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.492</v>
       </c>
       <c r="AM7">
-        <v>-0.293</v>
+        <v>0.15</v>
       </c>
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>9.146341463414634</v>
+      </c>
       <c r="AP7">
         <v>0</v>
       </c>
       <c r="AQ7">
-        <v>-5.972696245733789</v>
+        <v>30.00000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1260,7 +1254,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camerit AG (DB:RTML)</t>
+          <t>Clere AG (HMSE:CAG0)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1269,64 +1263,61 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0349</v>
+        <v>0.779</v>
       </c>
       <c r="G8">
-        <v>0.1468085106382979</v>
+        <v>0.627151051625239</v>
       </c>
       <c r="H8">
-        <v>0.1468085106382979</v>
+        <v>0.627151051625239</v>
       </c>
       <c r="I8">
-        <v>0.3691489361702128</v>
+        <v>0.237093690248566</v>
       </c>
       <c r="J8">
-        <v>0.3691489361702128</v>
+        <v>0.1768421584032208</v>
       </c>
       <c r="K8">
-        <v>0.498</v>
+        <v>4.52</v>
       </c>
       <c r="L8">
-        <v>0.5297872340425532</v>
+        <v>0.08642447418738049</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>1.66706</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.01445845620121422</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.3688185840707965</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>1.66706</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.01445845620121422</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.3688185840707965</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.714285714285714</v>
-      </c>
-      <c r="W8">
-        <v>0.05790697674418605</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="Y8">
-        <v>-0.0145472422965188</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB8">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1338,31 +1329,31 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>-7.32</v>
+        <v>0</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
       <c r="AJ8">
-        <v>2.399999999999999</v>
-      </c>
-      <c r="AK8">
-        <v>-73.20000000000026</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>7.803999999999999</v>
       </c>
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>1.528976572133169</v>
+      </c>
       <c r="AP8">
-        <v>-21.03448275862069</v>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>1.58892875448488</v>
       </c>
     </row>
     <row r="9">
@@ -1373,7 +1364,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ernst Russ AG (XTRA:HXCK)</t>
+          <t>Horus AG (BST:HRU)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1382,28 +1373,28 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.306</v>
+        <v>-0.0977</v>
       </c>
       <c r="E9">
-        <v>0.408</v>
+        <v>-0.273</v>
       </c>
       <c r="G9">
-        <v>0.2167789344764237</v>
+        <v>0.9581151832460733</v>
       </c>
       <c r="H9">
-        <v>0.2167789344764237</v>
+        <v>0.9581151832460733</v>
       </c>
       <c r="I9">
-        <v>0.4816488804012926</v>
+        <v>0.956806282722513</v>
       </c>
       <c r="J9">
-        <v>0.478412199924996</v>
+        <v>0.9470429533069772</v>
       </c>
       <c r="K9">
-        <v>38.2</v>
+        <v>0.292</v>
       </c>
       <c r="L9">
-        <v>0.2339252908756889</v>
+        <v>0.3821989528795811</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1432,68 +1423,47 @@
       <c r="V9">
         <v>0</v>
       </c>
-      <c r="W9">
-        <v>0.5387870239774331</v>
-      </c>
       <c r="X9">
-        <v>0.08247681606071629</v>
-      </c>
-      <c r="Y9">
-        <v>0.4563102079167168</v>
-      </c>
-      <c r="Z9">
-        <v>1.133447758301832</v>
-      </c>
-      <c r="AA9">
-        <v>0.5422552355492346</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB9">
-        <v>0.06935130438727968</v>
-      </c>
-      <c r="AC9">
-        <v>0.4729039311619549</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD9">
-        <v>64.7</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.073689152344619</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>65.77368915234462</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>65.77368915234462</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>0.2984643466529037</v>
-      </c>
-      <c r="AI9">
-        <v>0.2593868842316224</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>0.2984643466529037</v>
-      </c>
-      <c r="AK9">
-        <v>0.2593868842316224</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>2.84</v>
+        <v>0.003</v>
       </c>
       <c r="AM9">
-        <v>-0.02000000000000002</v>
+        <v>-0.106</v>
       </c>
       <c r="AN9">
-        <v>0.7413943255259661</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>27.42957746478874</v>
+        <v>243.6666666666667</v>
       </c>
       <c r="AP9">
-        <v>0.7536976801616242</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>-3894.999999999997</v>
+        <v>-6.89622641509434</v>
       </c>
     </row>
     <row r="10">
@@ -1504,7 +1474,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PEH Wertpapier AG (DB:PEH)</t>
+          <t>SCI AG (HMSE:SCI)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1513,25 +1483,25 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.175</v>
+        <v>-0.0124</v>
       </c>
       <c r="G10">
-        <v>0.07085346215780998</v>
+        <v>0.07063829787234042</v>
       </c>
       <c r="H10">
-        <v>0.07085346215780998</v>
+        <v>0.07063829787234042</v>
       </c>
       <c r="I10">
-        <v>0.05421363392377885</v>
+        <v>0.07021276595744681</v>
       </c>
       <c r="J10">
-        <v>0.04011808910359635</v>
+        <v>0.07021276595744681</v>
       </c>
       <c r="K10">
-        <v>4.3</v>
+        <v>-0.425</v>
       </c>
       <c r="L10">
-        <v>0.02308105206655931</v>
+        <v>-0.1808510638297872</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1540,7 +1510,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1549,7 +1519,7 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1560,68 +1530,44 @@
       <c r="V10">
         <v>0</v>
       </c>
-      <c r="W10">
-        <v>0.2402234636871508</v>
-      </c>
       <c r="X10">
-        <v>0.07693470320223161</v>
-      </c>
-      <c r="Y10">
-        <v>0.1632887604849192</v>
-      </c>
-      <c r="Z10">
-        <v>9.287138584247259</v>
-      </c>
-      <c r="AA10">
-        <v>0.3725822532402792</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB10">
-        <v>0.06993160651929059</v>
-      </c>
-      <c r="AC10">
-        <v>0.3026506467209886</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD10">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>0.1597979260834884</v>
-      </c>
-      <c r="AI10">
-        <v>0.1798862615983239</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0.1597979260834884</v>
-      </c>
-      <c r="AK10">
-        <v>0.1798862615983239</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1.3</v>
+        <v>-0.383</v>
       </c>
       <c r="AN10">
-        <v>0.5778846153846153</v>
-      </c>
-      <c r="AO10">
-        <v>144.2857142857143</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.5778846153846153</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>-7.769230769230768</v>
+        <v>-0.4308093994778068</v>
       </c>
     </row>
     <row r="11">
@@ -1632,7 +1578,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OVB Holding AG (XTRA:O4B)</t>
+          <t>MLP SE (XTRA:MLP)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1641,49 +1587,46 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0873</v>
+        <v>0.07780000000000001</v>
       </c>
       <c r="E11">
-        <v>0.034</v>
-      </c>
-      <c r="F11">
-        <v>0.111</v>
+        <v>0.077</v>
       </c>
       <c r="G11">
-        <v>0.0751145038167939</v>
+        <v>0.09429325751421609</v>
       </c>
       <c r="H11">
-        <v>0.0751145038167939</v>
+        <v>0.09270917952883835</v>
       </c>
       <c r="I11">
-        <v>0.05587786259541985</v>
+        <v>0.08671811535337125</v>
       </c>
       <c r="J11">
-        <v>0.03650880037970178</v>
+        <v>0.05595912571948316</v>
       </c>
       <c r="K11">
-        <v>12.3</v>
+        <v>52.3</v>
       </c>
       <c r="L11">
-        <v>0.03755725190839695</v>
+        <v>0.0531072298943948</v>
       </c>
       <c r="M11">
-        <v>16.1</v>
+        <v>34.7</v>
       </c>
       <c r="N11">
-        <v>0.048045359594151</v>
+        <v>0.05182972367438387</v>
       </c>
       <c r="O11">
-        <v>1.308943089430894</v>
+        <v>0.6634799235181645</v>
       </c>
       <c r="P11">
-        <v>16.1</v>
+        <v>34.7</v>
       </c>
       <c r="Q11">
-        <v>0.048045359594151</v>
+        <v>0.05182972367438387</v>
       </c>
       <c r="R11">
-        <v>1.308943089430894</v>
+        <v>0.6634799235181645</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1692,73 +1635,64 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>85.09999999999999</v>
+        <v>1014.6</v>
       </c>
       <c r="V11">
-        <v>0.2539540435690838</v>
+        <v>1.51545929798357</v>
       </c>
       <c r="W11">
-        <v>0.121301775147929</v>
+        <v>0.104620924184837</v>
       </c>
       <c r="X11">
-        <v>0.0731783220525923</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y11">
-        <v>0.04812345309533669</v>
-      </c>
-      <c r="Z11">
-        <v>9.022038567493111</v>
-      </c>
-      <c r="AA11">
-        <v>0.3293838050785765</v>
+        <v>0.04231253564903534</v>
       </c>
       <c r="AB11">
-        <v>0.07198346473602688</v>
-      </c>
-      <c r="AC11">
-        <v>0.2574003403425497</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD11">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>-74.8</v>
+        <v>-1014.6</v>
       </c>
       <c r="AH11">
-        <v>0.02982049797336421</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>0.1074035453597498</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>-0.2873607376104494</v>
+        <v>2.94001738626485</v>
       </c>
       <c r="AK11">
-        <v>-6.925925925925927</v>
+        <v>2.194204152249135</v>
       </c>
       <c r="AL11">
-        <v>0.318</v>
+        <v>19.5</v>
       </c>
       <c r="AM11">
-        <v>-0.9219999999999999</v>
+        <v>13.23</v>
       </c>
       <c r="AN11">
-        <v>0.4858490566037736</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>57.54716981132076</v>
+        <v>4.37948717948718</v>
       </c>
       <c r="AP11">
-        <v>-3.528301886792453</v>
+        <v>-10.56875</v>
       </c>
       <c r="AQ11">
-        <v>-19.84815618221258</v>
+        <v>6.455026455026455</v>
       </c>
     </row>
     <row r="12">
@@ -1769,7 +1703,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shareholder Value Beteiligungen AG (XTRA:SVE)</t>
+          <t>OVB Holding AG (XTRA:O4B)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1778,109 +1712,124 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.197</v>
+        <v>0.0863</v>
       </c>
       <c r="E12">
-        <v>0.133</v>
+        <v>0.08109999999999999</v>
+      </c>
+      <c r="F12">
+        <v>0.283</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.06593707250341997</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.06593707250341997</v>
       </c>
       <c r="I12">
-        <v>0.846473029045643</v>
+        <v>0.04678522571819426</v>
       </c>
       <c r="J12">
-        <v>0.846473029045643</v>
+        <v>0.03394599254164871</v>
       </c>
       <c r="K12">
-        <v>19.2</v>
+        <v>15.5</v>
       </c>
       <c r="L12">
-        <v>0.7966804979253111</v>
+        <v>0.04240766073871409</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>13.6</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.04593042890915231</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.8774193548387097</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>13.6</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.04593042890915231</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.8774193548387097</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>9.359999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="V12">
-        <v>0.1105076741440378</v>
+        <v>0.2640999662276258</v>
       </c>
       <c r="W12">
-        <v>0.2181818181818182</v>
+        <v>0.1823529411764706</v>
       </c>
       <c r="X12">
-        <v>0.07245421904070486</v>
+        <v>0.06300863840708083</v>
       </c>
       <c r="Y12">
-        <v>0.1457275991411133</v>
+        <v>0.1193443027693897</v>
       </c>
       <c r="Z12">
-        <v>0.2735683069413701</v>
+        <v>35.83333333333332</v>
       </c>
       <c r="AA12">
-        <v>0.2315681934275498</v>
+        <v>1.216398066075745</v>
       </c>
       <c r="AB12">
-        <v>0.07245421904070486</v>
+        <v>0.061723800104751</v>
       </c>
       <c r="AC12">
-        <v>0.1591139743868449</v>
+        <v>1.154674265970994</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="AG12">
-        <v>-9.359999999999999</v>
+        <v>-65.60000000000001</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.04081632653061223</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.1168831168831169</v>
       </c>
       <c r="AJ12">
-        <v>-0.1242367932041412</v>
+        <v>-0.2845986984815619</v>
       </c>
       <c r="AK12">
-        <v>-0.1070448307410796</v>
+        <v>-2.216216216216217</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>0.358</v>
       </c>
       <c r="AM12">
-        <v>-0.787</v>
+        <v>-2.482</v>
+      </c>
+      <c r="AN12">
+        <v>0.65625</v>
+      </c>
+      <c r="AO12">
+        <v>47.76536312849163</v>
+      </c>
+      <c r="AP12">
+        <v>-3.416666666666667</v>
       </c>
       <c r="AQ12">
-        <v>-25.92121982210927</v>
+        <v>-6.889605157131347</v>
       </c>
     </row>
     <row r="13">
@@ -1891,7 +1840,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DWS Group GmbH &amp; Co. KGaA (XTRA:DWS)</t>
+          <t>capsensixx AG (XTRA:CPX)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1899,26 +1848,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F13">
-        <v>0.083</v>
+      <c r="D13">
+        <v>-0.0216</v>
+      </c>
+      <c r="E13">
+        <v>-0.00284</v>
       </c>
       <c r="G13">
-        <v>0.3389851546596495</v>
+        <v>0.07033639143730885</v>
       </c>
       <c r="H13">
-        <v>0.3292041110173278</v>
+        <v>0.07033639143730885</v>
       </c>
       <c r="I13">
-        <v>0.270939873889082</v>
+        <v>0.06024464831804281</v>
       </c>
       <c r="J13">
-        <v>0.1906508034321198</v>
+        <v>0.04267609724428954</v>
       </c>
       <c r="K13">
-        <v>731.5</v>
+        <v>3.1</v>
       </c>
       <c r="L13">
-        <v>0.181594756963408</v>
+        <v>0.02370030581039755</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1942,73 +1894,70 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>0.2074468085106383</v>
       </c>
       <c r="W13">
-        <v>0.08887997861534348</v>
+        <v>0.2214285714285714</v>
       </c>
       <c r="X13">
-        <v>0.07308080476559012</v>
+        <v>0.06394814031771376</v>
       </c>
       <c r="Y13">
-        <v>0.01579917384975336</v>
+        <v>0.1574804311108577</v>
       </c>
       <c r="Z13">
-        <v>0.6931667613098617</v>
+        <v>27.82978723404256</v>
       </c>
       <c r="AA13">
-        <v>0.1321527999561655</v>
+        <v>1.187666706287888</v>
       </c>
       <c r="AB13">
-        <v>0.07204522018723547</v>
+        <v>0.06101054943436079</v>
       </c>
       <c r="AC13">
-        <v>0.06010757976893005</v>
+        <v>1.126656156853527</v>
       </c>
       <c r="AD13">
-        <v>172.6</v>
+        <v>5.62</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>172.6</v>
+        <v>5.62</v>
       </c>
       <c r="AG13">
-        <v>172.6</v>
+        <v>-6.079999999999999</v>
       </c>
       <c r="AH13">
-        <v>0.02590852459508548</v>
+        <v>0.09061593034504999</v>
       </c>
       <c r="AI13">
-        <v>0.02241674892202192</v>
+        <v>0.1811734364925854</v>
       </c>
       <c r="AJ13">
-        <v>0.02590852459508548</v>
+        <v>-0.1208267090620032</v>
       </c>
       <c r="AK13">
-        <v>0.02241674892202192</v>
+        <v>-0.3146997929606625</v>
       </c>
       <c r="AL13">
-        <v>19.6</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>19.6</v>
+        <v>-0.826</v>
       </c>
       <c r="AN13">
-        <v>0.1520704845814978</v>
-      </c>
-      <c r="AO13">
-        <v>55.68367346938776</v>
+        <v>0.678743961352657</v>
       </c>
       <c r="AP13">
-        <v>0.1520704845814978</v>
+        <v>-0.7342995169082125</v>
       </c>
       <c r="AQ13">
-        <v>55.68367346938776</v>
+        <v>-9.53995157384988</v>
       </c>
     </row>
     <row r="14">
@@ -2019,7 +1968,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KST Beteiligungs AG (DB:KSW)</t>
+          <t>Ernst Russ AG (XTRA:HXCK)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2028,121 +1977,118 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.06610000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="E14">
-        <v>-0.447</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G14">
-        <v>1.564885496183206</v>
+        <v>0.432249322493225</v>
       </c>
       <c r="H14">
-        <v>1.564885496183206</v>
+        <v>0.432249322493225</v>
       </c>
       <c r="I14">
-        <v>0.9847328244274809</v>
+        <v>0.2014643445900377</v>
       </c>
       <c r="J14">
-        <v>0.7135745104546964</v>
+        <v>0.2006297426118237</v>
       </c>
       <c r="K14">
-        <v>0.05</v>
+        <v>52.6</v>
       </c>
       <c r="L14">
-        <v>0.03816793893129771</v>
+        <v>0.2375790424570912</v>
       </c>
       <c r="M14">
-        <v>0.3416399999999999</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.05466239999999999</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>6.832799999999999</v>
+        <v>-0</v>
       </c>
       <c r="P14">
-        <v>0.3416399999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.05466239999999999</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>6.832799999999999</v>
+        <v>-0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>0.2208</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>0.005875440658049355</v>
+        <v>0.5502092050209205</v>
       </c>
       <c r="X14">
-        <v>0.08470435477152141</v>
+        <v>0.06278374082957247</v>
       </c>
       <c r="Y14">
-        <v>-0.07882891411347205</v>
+        <v>0.487425464191348</v>
       </c>
       <c r="Z14">
-        <v>0.137590589223821</v>
+        <v>1.372436231526228</v>
       </c>
       <c r="AA14">
-        <v>0.09818113734856131</v>
+        <v>0.2753515278822483</v>
       </c>
       <c r="AB14">
-        <v>0.06705365445494829</v>
+        <v>0.06202050207141376</v>
       </c>
       <c r="AC14">
-        <v>0.03112748289361301</v>
+        <v>0.2133310258108345</v>
       </c>
       <c r="AD14">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.018970538828244</v>
       </c>
       <c r="AF14">
-        <v>3.25</v>
+        <v>4.358970538828244</v>
       </c>
       <c r="AG14">
-        <v>1.87</v>
+        <v>4.358970538828244</v>
       </c>
       <c r="AH14">
-        <v>0.3421052631578947</v>
+        <v>0.02807548268354724</v>
       </c>
       <c r="AI14">
-        <v>0.3266331658291458</v>
+        <v>0.01760069715764582</v>
       </c>
       <c r="AJ14">
-        <v>0.2302955665024631</v>
+        <v>0.02807548268354724</v>
       </c>
       <c r="AK14">
-        <v>0.2182030338389732</v>
+        <v>0.01760069715764582</v>
       </c>
       <c r="AL14">
-        <v>0.032</v>
+        <v>3.01</v>
       </c>
       <c r="AM14">
-        <v>-0.382</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="AN14">
-        <v>2.5</v>
+        <v>0.03414853590708326</v>
       </c>
       <c r="AO14">
-        <v>40.3125</v>
+        <v>14.58471760797342</v>
       </c>
       <c r="AP14">
-        <v>1.438461538461538</v>
+        <v>0.04456660537817196</v>
       </c>
       <c r="AQ14">
-        <v>-3.37696335078534</v>
+        <v>-1097.499999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2153,7 +2099,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Binect AG (XTRA:MA10)</t>
+          <t>PEH Wertpapier AG (DB:PEH)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2162,118 +2108,121 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.11</v>
-      </c>
-      <c r="F15">
-        <v>0.121</v>
+        <v>0.00498</v>
+      </c>
+      <c r="E15">
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G15">
-        <v>0.0212</v>
+        <v>0.0900297619047619</v>
       </c>
       <c r="H15">
-        <v>0.0212</v>
+        <v>0.0900297619047619</v>
       </c>
       <c r="I15">
-        <v>0.01896</v>
+        <v>0.07589285714285714</v>
       </c>
       <c r="J15">
-        <v>0.01336228571428571</v>
+        <v>0.05170356751682052</v>
       </c>
       <c r="K15">
-        <v>0.148</v>
+        <v>2.41</v>
       </c>
       <c r="L15">
-        <v>0.01184</v>
+        <v>0.01793154761904762</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>2.62</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.0691292875989446</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>1.087136929460581</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>2.62</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.0691292875989446</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>1.087136929460581</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>2.03</v>
+        <v>12.2</v>
       </c>
       <c r="V15">
-        <v>0.2325315005727377</v>
+        <v>0.3218997361477572</v>
       </c>
       <c r="W15">
-        <v>0.01450980392156863</v>
+        <v>0.09601593625498007</v>
       </c>
       <c r="X15">
-        <v>0.07454825933657093</v>
+        <v>0.06497432663413608</v>
       </c>
       <c r="Y15">
-        <v>-0.0600384554150023</v>
+        <v>0.031041609620844</v>
       </c>
       <c r="Z15">
-        <v>7.086167800453517</v>
+        <v>4.183006535947713</v>
       </c>
       <c r="AA15">
-        <v>0.09468739876903146</v>
+        <v>0.2162763608546741</v>
       </c>
       <c r="AB15">
-        <v>0.07160554428868759</v>
+        <v>0.06031157569104807</v>
       </c>
       <c r="AC15">
-        <v>0.02308185448034386</v>
+        <v>0.155964785163626</v>
       </c>
       <c r="AD15">
-        <v>0.776</v>
+        <v>6.14</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.776</v>
+        <v>6.14</v>
       </c>
       <c r="AG15">
-        <v>-1.254</v>
+        <v>-6.06</v>
       </c>
       <c r="AH15">
-        <v>0.0816326530612245</v>
+        <v>0.1394187102633969</v>
       </c>
       <c r="AI15">
-        <v>0.0784155214227971</v>
+        <v>0.1722783389450056</v>
       </c>
       <c r="AJ15">
-        <v>-0.167736757624398</v>
+        <v>-0.1903266331658291</v>
       </c>
       <c r="AK15">
-        <v>-0.1594202898550725</v>
+        <v>-0.2585324232081911</v>
       </c>
       <c r="AL15">
-        <v>0.027</v>
+        <v>1.67</v>
       </c>
       <c r="AM15">
-        <v>0.027</v>
+        <v>1.67</v>
       </c>
       <c r="AN15">
-        <v>3.527272727272727</v>
+        <v>0.5074380165289256</v>
       </c>
       <c r="AO15">
-        <v>8.777777777777777</v>
+        <v>6.107784431137724</v>
       </c>
       <c r="AP15">
-        <v>-5.699999999999999</v>
+        <v>-0.5008264462809917</v>
       </c>
       <c r="AQ15">
-        <v>8.777777777777777</v>
+        <v>6.107784431137724</v>
       </c>
     </row>
     <row r="16">
@@ -2284,7 +2233,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BAVARIA Industries Group AG (XTRA:B8A)</t>
+          <t>Deutsche Beteiligungs AG (XTRA:DBAN)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2293,118 +2242,124 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.259</v>
+        <v>0.21</v>
       </c>
       <c r="E16">
-        <v>-0.3</v>
+        <v>0.289</v>
+      </c>
+      <c r="F16">
+        <v>0.0433</v>
       </c>
       <c r="G16">
-        <v>0.2171979243884359</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H16">
-        <v>0.2171979243884359</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I16">
-        <v>0.1769452197869276</v>
+        <v>0.711854103343465</v>
       </c>
       <c r="J16">
-        <v>0.1769452197869276</v>
+        <v>0.6935156512468884</v>
       </c>
       <c r="K16">
-        <v>22.8</v>
+        <v>112</v>
       </c>
       <c r="L16">
-        <v>0.1690140845070423</v>
+        <v>0.6808510638297872</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>15.9</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.0260655737704918</v>
       </c>
       <c r="O16">
-        <v>-0</v>
+        <v>0.1419642857142857</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>15.9</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.0260655737704918</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>0.1419642857142857</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
       <c r="U16">
-        <v>62.9</v>
+        <v>21.2</v>
       </c>
       <c r="V16">
-        <v>0.1663141195134849</v>
+        <v>0.03475409836065574</v>
       </c>
       <c r="W16">
-        <v>0.0647175702526256</v>
+        <v>0.1971136923618444</v>
       </c>
       <c r="X16">
-        <v>0.07377696817457229</v>
+        <v>0.0626833666021186</v>
       </c>
       <c r="Y16">
-        <v>-0.009059397921946682</v>
+        <v>0.1344303257597258</v>
       </c>
       <c r="Z16">
-        <v>0.5014209107915024</v>
+        <v>0.2783417935702199</v>
       </c>
       <c r="AA16">
-        <v>0.08872403326576379</v>
+        <v>0.193034390237078</v>
       </c>
       <c r="AB16">
-        <v>0.07161496342364912</v>
+        <v>0.06198929638931294</v>
       </c>
       <c r="AC16">
-        <v>0.01710906984211467</v>
+        <v>0.1310450938477651</v>
       </c>
       <c r="AD16">
-        <v>15.6</v>
+        <v>13.9</v>
       </c>
       <c r="AE16">
-        <v>5.635449253717359</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>21.23544925371736</v>
+        <v>13.9</v>
       </c>
       <c r="AG16">
-        <v>-41.66455074628264</v>
+        <v>-7.299999999999999</v>
       </c>
       <c r="AH16">
-        <v>0.05316365709000659</v>
+        <v>0.02227921141208527</v>
       </c>
       <c r="AI16">
-        <v>0.05993035497419844</v>
+        <v>0.01924141749723145</v>
       </c>
       <c r="AJ16">
-        <v>-0.1238043446498004</v>
+        <v>-0.01211216193794591</v>
       </c>
       <c r="AK16">
-        <v>-0.1429632217116127</v>
+        <v>-0.01041072447233314</v>
       </c>
       <c r="AL16">
-        <v>1.11</v>
+        <v>2.31</v>
       </c>
       <c r="AM16">
-        <v>-7.089999999999999</v>
+        <v>2.175</v>
       </c>
       <c r="AN16">
-        <v>0.547426044846826</v>
+        <v>0.1182978723404255</v>
       </c>
       <c r="AO16">
-        <v>21.62162162162162</v>
+        <v>50.69264069264069</v>
       </c>
       <c r="AP16">
-        <v>-1.462067963163935</v>
+        <v>-0.06212765957446808</v>
       </c>
       <c r="AQ16">
-        <v>-3.385049365303245</v>
+        <v>53.83908045977012</v>
       </c>
     </row>
     <row r="17">
@@ -2415,7 +2370,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NSI Asset AG (DB:VMR1)</t>
+          <t>DWS Group GmbH &amp; Co. KGaA (XTRA:DWS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2424,25 +2379,31 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.5479999999999999</v>
+        <v>0.108</v>
+      </c>
+      <c r="E17">
+        <v>0.0236</v>
+      </c>
+      <c r="F17">
+        <v>0.0338</v>
       </c>
       <c r="G17">
-        <v>0.1127167630057803</v>
+        <v>0.2708947648281529</v>
       </c>
       <c r="H17">
-        <v>0.1127167630057803</v>
+        <v>0.2629670807753662</v>
       </c>
       <c r="I17">
-        <v>0.09017341040462427</v>
+        <v>0.2330449074297868</v>
       </c>
       <c r="J17">
-        <v>0.09017341040462427</v>
+        <v>0.1637885492114121</v>
       </c>
       <c r="K17">
-        <v>-1.13</v>
+        <v>567.3</v>
       </c>
       <c r="L17">
-        <v>-0.0653179190751445</v>
+        <v>0.1371150964373761</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2451,7 +2412,7 @@
         <v>-0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2460,79 +2421,79 @@
         <v>-0</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>0.2552795031055901</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>-0.26036866359447</v>
+        <v>0.07561479506831055</v>
       </c>
       <c r="X17">
-        <v>0.2101438717246321</v>
+        <v>0.06265255608646811</v>
       </c>
       <c r="Y17">
-        <v>-0.4705125353191021</v>
+        <v>0.01296223898184244</v>
       </c>
       <c r="Z17">
-        <v>0.6062092648398627</v>
+        <v>0.5390678948808484</v>
       </c>
       <c r="AA17">
-        <v>0.05466395682949051</v>
+        <v>0.08829314842898418</v>
       </c>
       <c r="AB17">
-        <v>0.06357682699425204</v>
+        <v>0.06201497785544065</v>
       </c>
       <c r="AC17">
-        <v>-0.008912870164761534</v>
+        <v>0.02627817057354353</v>
       </c>
       <c r="AD17">
-        <v>94.09999999999999</v>
+        <v>160.9</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>94.09999999999999</v>
+        <v>160.9</v>
       </c>
       <c r="AG17">
-        <v>89.98999999999999</v>
+        <v>160.9</v>
       </c>
       <c r="AH17">
-        <v>0.853901996370236</v>
+        <v>0.02048611553201513</v>
       </c>
       <c r="AI17">
-        <v>0.9022051773729626</v>
+        <v>0.01963560035634527</v>
       </c>
       <c r="AJ17">
-        <v>0.8482420586294654</v>
+        <v>0.02048611553201513</v>
       </c>
       <c r="AK17">
-        <v>0.8981934324782912</v>
+        <v>0.01963560035634527</v>
       </c>
       <c r="AL17">
-        <v>1.93</v>
+        <v>19.1</v>
       </c>
       <c r="AM17">
-        <v>1.841</v>
+        <v>19.1</v>
       </c>
       <c r="AN17">
-        <v>55.35294117647059</v>
+        <v>0.1691369704614738</v>
       </c>
       <c r="AO17">
-        <v>0.8082901554404146</v>
+        <v>50.48167539267016</v>
       </c>
       <c r="AP17">
-        <v>52.93529411764705</v>
+        <v>0.1691369704614738</v>
       </c>
       <c r="AQ17">
-        <v>0.8473655621944596</v>
+        <v>50.48167539267016</v>
       </c>
     </row>
     <row r="18">
@@ -2543,7 +2504,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blue Cap AG (XTRA:B7E)</t>
+          <t>Binect AG (XTRA:MA10)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2552,124 +2513,118 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.2</v>
-      </c>
-      <c r="E18">
-        <v>-0.139</v>
+        <v>0.136</v>
       </c>
       <c r="F18">
-        <v>0.132</v>
+        <v>0.7490000000000001</v>
       </c>
       <c r="G18">
-        <v>0.05772333432925008</v>
+        <v>0.02770700636942675</v>
       </c>
       <c r="H18">
-        <v>0.04989542874215715</v>
+        <v>0.02770700636942675</v>
       </c>
       <c r="I18">
-        <v>0.01386316103973708</v>
+        <v>0.0256687898089172</v>
       </c>
       <c r="J18">
-        <v>0.01030400663402499</v>
+        <v>0.0153064551367158</v>
       </c>
       <c r="K18">
-        <v>19.3</v>
+        <v>0.226</v>
       </c>
       <c r="L18">
-        <v>0.05766357932476845</v>
+        <v>0.01439490445859873</v>
       </c>
       <c r="M18">
-        <v>3.9116</v>
+        <v>-0</v>
       </c>
       <c r="N18">
-        <v>0.03357596566523605</v>
+        <v>-0</v>
       </c>
       <c r="O18">
-        <v>0.2026735751295337</v>
+        <v>-0</v>
       </c>
       <c r="P18">
-        <v>3.9116</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.03357596566523605</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.2026735751295337</v>
+        <v>-0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>31.7</v>
+        <v>2.55</v>
       </c>
       <c r="V18">
-        <v>0.2721030042918455</v>
+        <v>0.3175591531755915</v>
       </c>
       <c r="W18">
-        <v>0.2091007583965331</v>
+        <v>0.02478070175438597</v>
       </c>
       <c r="X18">
-        <v>0.09595150811169999</v>
+        <v>0.0640011096131865</v>
       </c>
       <c r="Y18">
-        <v>0.1131492502848331</v>
+        <v>-0.03922040785880053</v>
       </c>
       <c r="Z18">
-        <v>2.102386934673367</v>
+        <v>5.071059431524548</v>
       </c>
       <c r="AA18">
-        <v>0.02166300892216183</v>
+        <v>0.07761994368425</v>
       </c>
       <c r="AB18">
-        <v>0.06457126211866374</v>
+        <v>0.06097253531999634</v>
       </c>
       <c r="AC18">
-        <v>-0.04290825319650191</v>
+        <v>0.01664740836425366</v>
       </c>
       <c r="AD18">
-        <v>116.2</v>
+        <v>0.826</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>116.2</v>
+        <v>0.826</v>
       </c>
       <c r="AG18">
-        <v>84.5</v>
+        <v>-1.724</v>
       </c>
       <c r="AH18">
-        <v>0.4993553932101418</v>
+        <v>0.09327009936766034</v>
       </c>
       <c r="AI18">
-        <v>0.4989265779304423</v>
+        <v>0.07810136157337366</v>
       </c>
       <c r="AJ18">
-        <v>0.4203980099502487</v>
+        <v>-0.2733904218204884</v>
       </c>
       <c r="AK18">
-        <v>0.4199801192842942</v>
+        <v>-0.2148018938450037</v>
       </c>
       <c r="AL18">
-        <v>2.11</v>
+        <v>0.025</v>
       </c>
       <c r="AM18">
-        <v>2.106</v>
+        <v>0.025</v>
       </c>
       <c r="AN18">
-        <v>5.868686868686869</v>
+        <v>1.699588477366255</v>
       </c>
       <c r="AO18">
-        <v>2.199052132701422</v>
+        <v>16.12</v>
       </c>
       <c r="AP18">
-        <v>4.267676767676767</v>
+        <v>-3.547325102880658</v>
       </c>
       <c r="AQ18">
-        <v>2.203228869895537</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="19">
@@ -2680,7 +2635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coreo AG (XTRA:CORE)</t>
+          <t>BAVARIA Industries Group AG (XTRA:B8A)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2689,25 +2644,25 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.795</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="G19">
-        <v>0.079375</v>
+        <v>0.183617747440273</v>
       </c>
       <c r="H19">
-        <v>0.079375</v>
+        <v>0.183617747440273</v>
       </c>
       <c r="I19">
-        <v>0.0775</v>
+        <v>0.1101174663706863</v>
       </c>
       <c r="J19">
-        <v>0.0775</v>
+        <v>0.1101174663706863</v>
       </c>
       <c r="K19">
-        <v>-2.15</v>
+        <v>-5.13</v>
       </c>
       <c r="L19">
-        <v>-0.134375</v>
+        <v>-0.03501706484641638</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2731,73 +2686,73 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>13.1</v>
+        <v>62.1</v>
       </c>
       <c r="V19">
-        <v>0.6822916666666666</v>
+        <v>0.1153203342618384</v>
       </c>
       <c r="W19">
-        <v>-0.06847133757961783</v>
+        <v>-0.01549848942598187</v>
       </c>
       <c r="X19">
-        <v>0.1594468696131102</v>
+        <v>0.06286666448591577</v>
       </c>
       <c r="Y19">
-        <v>-0.227918207192728</v>
+        <v>-0.07836515391189763</v>
       </c>
       <c r="Z19">
-        <v>0.1735357917570499</v>
+        <v>0.5076846547477488</v>
       </c>
       <c r="AA19">
-        <v>0.01344902386117137</v>
+        <v>0.05590494789609871</v>
       </c>
       <c r="AB19">
-        <v>0.06427336178215</v>
+        <v>0.06183843489789147</v>
       </c>
       <c r="AC19">
-        <v>-0.05082433792097863</v>
+        <v>-0.005933487001792762</v>
       </c>
       <c r="AD19">
-        <v>70.90000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>4.86895588347227</v>
       </c>
       <c r="AF19">
-        <v>70.90000000000001</v>
+        <v>18.26895588347227</v>
       </c>
       <c r="AG19">
-        <v>57.8</v>
+        <v>-43.83104411652774</v>
       </c>
       <c r="AH19">
-        <v>0.7869034406215316</v>
+        <v>0.03281245423334241</v>
       </c>
       <c r="AI19">
-        <v>0.6903602726387537</v>
+        <v>0.05155348847623007</v>
       </c>
       <c r="AJ19">
-        <v>0.7506493506493507</v>
+        <v>-0.08860682198713292</v>
       </c>
       <c r="AK19">
-        <v>0.6450892857142857</v>
+        <v>-0.1499681825051689</v>
       </c>
       <c r="AL19">
-        <v>3.39</v>
+        <v>0.806</v>
       </c>
       <c r="AM19">
-        <v>3.304</v>
+        <v>-17.394</v>
       </c>
       <c r="AN19">
-        <v>50.64285714285715</v>
+        <v>0.7013503611430965</v>
       </c>
       <c r="AO19">
-        <v>0.3657817109144543</v>
+        <v>20.09925558312655</v>
       </c>
       <c r="AP19">
-        <v>41.28571428571429</v>
+        <v>-2.29409840450789</v>
       </c>
       <c r="AQ19">
-        <v>0.3753026634382566</v>
+        <v>-0.9313556398758193</v>
       </c>
     </row>
     <row r="20">
@@ -2808,7 +2763,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AdCapital AG (DB:ADC)</t>
+          <t>Shareholder Value Beteiligungen AG (XTRA:SVE)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2817,25 +2772,25 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.00709</v>
+        <v>-0.151</v>
       </c>
       <c r="G20">
-        <v>0.0834247410115783</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>0.07068860450944546</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>0.007921998781230958</v>
+        <v>0.3850877192982456</v>
       </c>
       <c r="J20">
-        <v>0.003960999390615479</v>
+        <v>0.3850877192982456</v>
       </c>
       <c r="K20">
-        <v>-0.921</v>
+        <v>-2.91</v>
       </c>
       <c r="L20">
-        <v>-0.005612431444241317</v>
+        <v>-0.2552631578947369</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2859,73 +2814,67 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>7.35</v>
+        <v>2.54</v>
       </c>
       <c r="V20">
-        <v>0.3466981132075472</v>
+        <v>0.03866057838660578</v>
       </c>
       <c r="W20">
-        <v>-0.01412576687116564</v>
+        <v>-0.03006198347107438</v>
       </c>
       <c r="X20">
-        <v>0.07245421904070486</v>
+        <v>0.06339292317281861</v>
       </c>
       <c r="Y20">
-        <v>-0.08657998591187049</v>
+        <v>-0.093454906643893</v>
       </c>
       <c r="Z20">
-        <v>3.078799249530956</v>
+        <v>0.1303751143641354</v>
       </c>
       <c r="AA20">
-        <v>0.01219512195121951</v>
+        <v>0.05020585544373284</v>
       </c>
       <c r="AB20">
-        <v>0.07245421904070486</v>
+        <v>0.06142282429607571</v>
       </c>
       <c r="AC20">
-        <v>-0.06025909708948535</v>
+        <v>-0.01121696885234287</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AG20">
-        <v>-7.35</v>
+        <v>1.79</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>0.06183064400971013</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>0.04227277164893098</v>
       </c>
       <c r="AJ20">
-        <v>-0.5306859205776173</v>
+        <v>0.02652244777004</v>
       </c>
       <c r="AK20">
-        <v>-0.129973474801061</v>
+        <v>0.01791971168285114</v>
       </c>
       <c r="AL20">
-        <v>0.287</v>
+        <v>0.08</v>
       </c>
       <c r="AM20">
-        <v>0.172</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
+        <v>-0.9900000000000001</v>
       </c>
       <c r="AO20">
-        <v>4.529616724738676</v>
-      </c>
-      <c r="AP20">
-        <v>-1.243654822335025</v>
+        <v>54.87499999999999</v>
       </c>
       <c r="AQ20">
-        <v>7.558139534883722</v>
+        <v>-4.434343434343433</v>
       </c>
     </row>
     <row r="21">
@@ -2936,7 +2885,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MPC Münchmeyer Petersen Capital AG (XTRA:MPCK)</t>
+          <t>RM Rheiner Management AG (DUSE:RMO)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2945,124 +2894,112 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.034</v>
+        <v>-0.0276</v>
       </c>
       <c r="E21">
-        <v>0.277</v>
-      </c>
-      <c r="F21">
-        <v>0.283</v>
+        <v>-0.329</v>
       </c>
       <c r="G21">
-        <v>0.02110403397027601</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>0.02110403397027601</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>0.007452229299363056</v>
+        <v>0.8010948905109488</v>
       </c>
       <c r="J21">
-        <v>0.006504762978411588</v>
+        <v>0.7235695785260183</v>
       </c>
       <c r="K21">
-        <v>28.1</v>
+        <v>0.027</v>
       </c>
       <c r="L21">
-        <v>0.5966029723991507</v>
+        <v>0.04927007299270073</v>
       </c>
       <c r="M21">
-        <v>5.11</v>
+        <v>-0</v>
       </c>
       <c r="N21">
-        <v>0.04662408759124088</v>
+        <v>-0</v>
       </c>
       <c r="O21">
-        <v>0.1818505338078292</v>
+        <v>-0</v>
       </c>
       <c r="P21">
-        <v>5.11</v>
+        <v>-0</v>
       </c>
       <c r="Q21">
-        <v>0.04662408759124088</v>
+        <v>-0</v>
       </c>
       <c r="R21">
-        <v>0.1818505338078292</v>
+        <v>-0</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
       <c r="U21">
-        <v>53.1</v>
+        <v>1.17</v>
       </c>
       <c r="V21">
-        <v>0.4844890510948905</v>
+        <v>0.1202466598150051</v>
       </c>
       <c r="W21">
-        <v>0.2618825722273999</v>
+        <v>0.003253012048192771</v>
       </c>
       <c r="X21">
-        <v>0.07286906256190917</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y21">
-        <v>0.1890135096654907</v>
+        <v>-0.05905537648760886</v>
       </c>
       <c r="Z21">
-        <v>0.7456070919740385</v>
+        <v>0.067280540208717</v>
       </c>
       <c r="AA21">
-        <v>0.00484999740831385</v>
+        <v>0.04868215212182419</v>
       </c>
       <c r="AB21">
-        <v>0.07227431414673402</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC21">
-        <v>-0.06742431673842017</v>
+        <v>-0.01362623641397744</v>
       </c>
       <c r="AD21">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>-51.17</v>
+        <v>-1.17</v>
       </c>
       <c r="AH21">
-        <v>0.01730476105083834</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>0.01512183655880279</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>-0.8757487591990417</v>
+        <v>-0.1366822429906542</v>
       </c>
       <c r="AK21">
-        <v>-0.6865691667784785</v>
+        <v>-0.1555851063829787</v>
       </c>
       <c r="AL21">
-        <v>0.5610000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="AM21">
-        <v>-0.969</v>
-      </c>
-      <c r="AN21">
-        <v>0.8502202643171806</v>
+        <v>-0.524</v>
       </c>
       <c r="AO21">
-        <v>0.6256684491978609</v>
-      </c>
-      <c r="AP21">
-        <v>-22.54185022026432</v>
+        <v>439</v>
       </c>
       <c r="AQ21">
-        <v>-0.3622291021671826</v>
+        <v>-0.8377862595419847</v>
       </c>
     </row>
     <row r="22">
@@ -3073,7 +3010,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ERWE Immobilien AG (XTRA:ERWE)</t>
+          <t>KST Beteiligungs AG (DB:KSW)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3081,23 +3018,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D22">
+        <v>0.231</v>
+      </c>
       <c r="G22">
-        <v>-0.3859844271412681</v>
+        <v>-0.1345864661654135</v>
       </c>
       <c r="H22">
-        <v>-0.3859844271412681</v>
+        <v>-0.1345864661654135</v>
       </c>
       <c r="I22">
-        <v>-0.2081317158795356</v>
+        <v>0.01729323308270677</v>
       </c>
       <c r="J22">
-        <v>-0.2081317158795356</v>
+        <v>0.01729323308270677</v>
       </c>
       <c r="K22">
-        <v>-11.6</v>
+        <v>-0.098</v>
       </c>
       <c r="L22">
-        <v>-1.290322580645161</v>
+        <v>-0.03684210526315789</v>
       </c>
       <c r="M22">
         <v>-0</v>
@@ -3121,73 +3061,73 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>2.14</v>
+        <v>0.736</v>
       </c>
       <c r="V22">
-        <v>0.06079545454545454</v>
+        <v>0.1355432780847146</v>
       </c>
       <c r="W22">
-        <v>-0.1715976331360947</v>
+        <v>-0.01462686567164179</v>
       </c>
       <c r="X22">
-        <v>0.1839967916668973</v>
+        <v>0.07173339071672985</v>
       </c>
       <c r="Y22">
-        <v>-0.355594424802992</v>
+        <v>-0.08636025638837164</v>
       </c>
       <c r="Z22">
-        <v>0.0399847852103536</v>
+        <v>0.3103850641773629</v>
       </c>
       <c r="AA22">
-        <v>-0.008322101954905573</v>
+        <v>0.005367561260210035</v>
       </c>
       <c r="AB22">
-        <v>0.06606695315878444</v>
+        <v>0.05709261388663267</v>
       </c>
       <c r="AC22">
-        <v>-0.07438905511369001</v>
+        <v>-0.05172505262642264</v>
       </c>
       <c r="AD22">
-        <v>166.6</v>
+        <v>3.11</v>
       </c>
       <c r="AE22">
-        <v>0.0655206287851258</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>166.6655206287851</v>
+        <v>3.11</v>
       </c>
       <c r="AG22">
-        <v>164.5255206287851</v>
+        <v>2.374</v>
       </c>
       <c r="AH22">
-        <v>0.8256264869287407</v>
+        <v>0.3641686182669789</v>
       </c>
       <c r="AI22">
-        <v>0.7464901887197056</v>
+        <v>0.3106893106893107</v>
       </c>
       <c r="AJ22">
-        <v>0.823758126206497</v>
+        <v>0.3042029728344439</v>
       </c>
       <c r="AK22">
-        <v>0.7440367812857868</v>
+        <v>0.2559844727194306</v>
       </c>
       <c r="AL22">
-        <v>6.62</v>
+        <v>0.106</v>
       </c>
       <c r="AM22">
-        <v>6.603</v>
+        <v>-0.203</v>
       </c>
       <c r="AN22">
-        <v>-98.69668246445498</v>
+        <v>63.46938775510203</v>
       </c>
       <c r="AO22">
-        <v>-0.2885196374622356</v>
+        <v>0.4339622641509434</v>
       </c>
       <c r="AP22">
-        <v>-97.46772549098645</v>
+        <v>48.44897959183672</v>
       </c>
       <c r="AQ22">
-        <v>-0.2892624564591852</v>
+        <v>-0.2266009852216748</v>
       </c>
     </row>
     <row r="23">
@@ -3198,7 +3138,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FinLab AG (XTRA:A7A)</t>
+          <t>NSI Asset AG (DB:VMR1)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3207,25 +3147,25 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.0282</v>
+        <v>0.329</v>
       </c>
       <c r="G23">
-        <v>-0.2022684310018904</v>
+        <v>0.1293213828425096</v>
       </c>
       <c r="H23">
-        <v>-0.2022684310018904</v>
+        <v>0.1293213828425096</v>
       </c>
       <c r="I23">
-        <v>-0.1995377131133589</v>
+        <v>-0.002816901408450704</v>
       </c>
       <c r="J23">
-        <v>-0.09976885655667943</v>
+        <v>-0.002816901408450704</v>
       </c>
       <c r="K23">
-        <v>-0.402</v>
+        <v>-2.96</v>
       </c>
       <c r="L23">
-        <v>-0.07599243856332703</v>
+        <v>-0.3790012804097311</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3249,70 +3189,73 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>2.37</v>
+        <v>3.25</v>
       </c>
       <c r="V23">
-        <v>0.04157894736842106</v>
+        <v>0.5</v>
       </c>
       <c r="W23">
-        <v>-0.005685997171145686</v>
+        <v>-0.3915343915343916</v>
       </c>
       <c r="X23">
-        <v>0.07261448442204163</v>
+        <v>0.3334505252325783</v>
       </c>
       <c r="Y23">
-        <v>-0.07830048159318731</v>
+        <v>-0.7249849167669699</v>
       </c>
       <c r="Z23">
-        <v>0.08612581147799914</v>
+        <v>0.09830081812460668</v>
       </c>
       <c r="AA23">
-        <v>-0.008592673731176111</v>
+        <v>-0.0002769037130270611</v>
       </c>
       <c r="AB23">
-        <v>0.07238397086948974</v>
+        <v>0.05440248850362463</v>
       </c>
       <c r="AC23">
-        <v>-0.08097664460066585</v>
+        <v>-0.05467939221665169</v>
       </c>
       <c r="AD23">
-        <v>0.02</v>
+        <v>107.1</v>
       </c>
       <c r="AE23">
-        <v>0.3677725118483413</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>0.3877725118483413</v>
+        <v>107.1</v>
       </c>
       <c r="AG23">
-        <v>-1.982227488151659</v>
+        <v>103.85</v>
       </c>
       <c r="AH23">
-        <v>0.006757058078326378</v>
+        <v>0.9427816901408451</v>
       </c>
       <c r="AI23">
-        <v>0.006225499744345159</v>
+        <v>0.934391903681731</v>
       </c>
       <c r="AJ23">
-        <v>-0.03602885754280177</v>
+        <v>0.9410965111010421</v>
       </c>
       <c r="AK23">
-        <v>-0.03308246293300851</v>
+        <v>0.9324773278261651</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AM23">
-        <v>-2.03</v>
+        <v>3.53</v>
       </c>
       <c r="AN23">
-        <v>-0.02347417840375587</v>
+        <v>682.1656050955413</v>
+      </c>
+      <c r="AO23">
+        <v>-0.006232294617563739</v>
       </c>
       <c r="AP23">
-        <v>2.326558084685046</v>
+        <v>661.4649681528662</v>
       </c>
       <c r="AQ23">
-        <v>0.6748768472906405</v>
+        <v>-0.006232294617563739</v>
       </c>
     </row>
     <row r="24">
@@ -3323,7 +3266,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mountain Alliance AG (XTRA:ECF)</t>
+          <t>Blue Cap AG (XTRA:B7E)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3332,115 +3275,121 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.08599999999999999</v>
+        <v>0.184</v>
+      </c>
+      <c r="F24">
+        <v>-0.257</v>
       </c>
       <c r="G24">
-        <v>-0.1603305785123967</v>
+        <v>0.05896151818661045</v>
       </c>
       <c r="H24">
-        <v>-0.1603305785123967</v>
+        <v>0.0521876647337902</v>
       </c>
       <c r="I24">
-        <v>-0.07263971976739873</v>
+        <v>-0.0004638903531892462</v>
       </c>
       <c r="J24">
-        <v>-0.07263971976739873</v>
+        <v>-0.0004638903531892462</v>
       </c>
       <c r="K24">
-        <v>-3.89</v>
+        <v>-11.3</v>
       </c>
       <c r="L24">
-        <v>-0.3214876033057851</v>
+        <v>-0.0297838692672641</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>2.72</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.03162790697674419</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>-0.2407079646017699</v>
       </c>
       <c r="P24">
-        <v>-0</v>
+        <v>2.72</v>
       </c>
       <c r="Q24">
-        <v>-0</v>
+        <v>0.03162790697674419</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>-0.2407079646017699</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
       <c r="U24">
-        <v>2.49</v>
+        <v>31</v>
       </c>
       <c r="V24">
-        <v>0.1</v>
+        <v>0.3604651162790697</v>
       </c>
       <c r="W24">
-        <v>-0.07811244979919679</v>
+        <v>-0.1036697247706422</v>
       </c>
       <c r="X24">
-        <v>0.07629511441755246</v>
+        <v>0.08322265373201307</v>
       </c>
       <c r="Y24">
-        <v>-0.1544075642167493</v>
+        <v>-0.1868923785026553</v>
       </c>
       <c r="Z24">
-        <v>0.2132545528164947</v>
+        <v>2.39671509791535</v>
       </c>
       <c r="AA24">
-        <v>-0.01549075095571211</v>
+        <v>-0.001111813013265951</v>
       </c>
       <c r="AB24">
-        <v>0.07024122842771237</v>
+        <v>0.0542928220734927</v>
       </c>
       <c r="AC24">
-        <v>-0.08573197938342447</v>
+        <v>-0.05540463508675865</v>
       </c>
       <c r="AD24">
-        <v>3.99</v>
+        <v>109.3</v>
       </c>
       <c r="AE24">
-        <v>0.06970304592762341</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>4.059703045927623</v>
+        <v>109.3</v>
       </c>
       <c r="AG24">
-        <v>1.569703045927623</v>
+        <v>78.3</v>
       </c>
       <c r="AH24">
-        <v>0.1401845536706395</v>
+        <v>0.5596518177163338</v>
       </c>
       <c r="AI24">
-        <v>0.08814001779124721</v>
+        <v>0.5060185185185185</v>
       </c>
       <c r="AJ24">
-        <v>0.05930187592977635</v>
+        <v>0.4765672550213024</v>
       </c>
       <c r="AK24">
-        <v>0.03602739831099997</v>
+        <v>0.4232432432432433</v>
       </c>
       <c r="AL24">
-        <v>1.62</v>
+        <v>4.82</v>
       </c>
       <c r="AM24">
-        <v>1.62</v>
+        <v>4.286</v>
       </c>
       <c r="AN24">
-        <v>-5.215686274509804</v>
+        <v>6.664634146341464</v>
       </c>
       <c r="AO24">
-        <v>-0.5790123456790123</v>
+        <v>-0.03651452282157676</v>
       </c>
       <c r="AP24">
-        <v>-2.051899406441337</v>
+        <v>4.774390243902439</v>
       </c>
       <c r="AQ24">
-        <v>-0.5790123456790123</v>
+        <v>-0.04106392907139524</v>
       </c>
     </row>
     <row r="25">
@@ -3451,7 +3400,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>iVestos AG (DUSE:LWD)</t>
+          <t>Coreo AG (XTRA:CORE)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3460,25 +3409,25 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.0187</v>
+        <v>1.054</v>
       </c>
       <c r="G25">
-        <v>3.78125</v>
+        <v>-0.01893551688843398</v>
       </c>
       <c r="H25">
-        <v>3.78125</v>
+        <v>-0.01893551688843398</v>
       </c>
       <c r="I25">
-        <v>-1.322916666666667</v>
+        <v>-0.03275332650972364</v>
       </c>
       <c r="J25">
-        <v>-1.322916666666667</v>
+        <v>-0.03275332650972364</v>
       </c>
       <c r="K25">
-        <v>-0.211</v>
+        <v>-1.78</v>
       </c>
       <c r="L25">
-        <v>-2.197916666666667</v>
+        <v>-0.1821903787103378</v>
       </c>
       <c r="M25">
         <v>-0</v>
@@ -3502,67 +3451,73 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>0.114</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="V25">
-        <v>0.02489082969432314</v>
+        <v>1.003712871287129</v>
       </c>
       <c r="W25">
-        <v>-0.0332807570977918</v>
+        <v>-0.0559748427672956</v>
       </c>
       <c r="X25">
-        <v>0.07514435213913326</v>
+        <v>0.2189242987934999</v>
       </c>
       <c r="Y25">
-        <v>-0.1084251092369251</v>
+        <v>-0.2748991415607955</v>
       </c>
       <c r="Z25">
-        <v>0.01462300076161462</v>
+        <v>0.1090401785714286</v>
       </c>
       <c r="AA25">
-        <v>-0.01934501142421935</v>
+        <v>-0.003571428571428571</v>
       </c>
       <c r="AB25">
-        <v>0.07166133897652956</v>
+        <v>0.0530293361291066</v>
       </c>
       <c r="AC25">
-        <v>-0.09100635040074891</v>
+        <v>-0.05660076470053517</v>
       </c>
       <c r="AD25">
-        <v>0.523</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0.523</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AG25">
-        <v>0.409</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="AH25">
-        <v>0.1024887321183618</v>
+        <v>0.9049188044245705</v>
       </c>
       <c r="AI25">
-        <v>0.074363713920091</v>
+        <v>0.7100646352723915</v>
       </c>
       <c r="AJ25">
-        <v>0.08198035678492685</v>
+        <v>0.8948874723559256</v>
       </c>
       <c r="AK25">
-        <v>0.05911258852435324</v>
+        <v>0.6865954686096417</v>
       </c>
       <c r="AL25">
-        <v>0.011</v>
+        <v>3.28</v>
       </c>
       <c r="AM25">
-        <v>-0.168</v>
+        <v>3.251</v>
+      </c>
+      <c r="AN25">
+        <v>662.9310344827586</v>
       </c>
       <c r="AO25">
-        <v>-11.54545454545455</v>
+        <v>-0.0975609756097561</v>
+      </c>
+      <c r="AP25">
+        <v>593.0172413793103</v>
       </c>
       <c r="AQ25">
-        <v>0.755952380952381</v>
+        <v>-0.09843125192248539</v>
       </c>
     </row>
     <row r="26">
@@ -3573,7 +3528,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AURELIUS Equity Opportunities SE &amp; Co. KGaA (XTRA:AR4)</t>
+          <t>Lehner Investments AG (DB:LEH)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3582,124 +3537,106 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.0242</v>
-      </c>
-      <c r="E26">
-        <v>-0.13</v>
-      </c>
-      <c r="F26">
-        <v>-0.077</v>
+        <v>-0.159</v>
       </c>
       <c r="G26">
-        <v>0.01836120401337793</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>0.01501672240802676</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>-0.01979933110367893</v>
+        <v>-24.8125</v>
       </c>
       <c r="J26">
-        <v>-0.01202648705370297</v>
+        <v>-24.8125</v>
       </c>
       <c r="K26">
-        <v>166</v>
+        <v>-26.6</v>
       </c>
       <c r="L26">
-        <v>0.05551839464882943</v>
+        <v>-1662.5</v>
       </c>
       <c r="M26">
-        <v>39.396</v>
+        <v>-0</v>
       </c>
       <c r="N26">
-        <v>0.07514018691588786</v>
+        <v>-0</v>
       </c>
       <c r="O26">
-        <v>0.2373253012048193</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>39.396</v>
+        <v>-0</v>
       </c>
       <c r="Q26">
-        <v>0.07514018691588786</v>
+        <v>-0</v>
       </c>
       <c r="R26">
-        <v>0.2373253012048193</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
       <c r="U26">
-        <v>279.1</v>
+        <v>0.407</v>
       </c>
       <c r="V26">
-        <v>0.5323288193782186</v>
+        <v>0.1761904761904762</v>
       </c>
       <c r="W26">
-        <v>0.306555863342567</v>
+        <v>-0.3911764705882353</v>
       </c>
       <c r="X26">
-        <v>0.1043470957764756</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y26">
-        <v>0.2022087675660914</v>
+        <v>-0.4534848591240369</v>
       </c>
       <c r="Z26">
-        <v>3.218168119685717</v>
+        <v>0.0002354811173579019</v>
       </c>
       <c r="AA26">
-        <v>-0.03870325722803991</v>
+        <v>-0.005842875224442941</v>
       </c>
       <c r="AB26">
-        <v>0.06647474460384585</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC26">
-        <v>-0.1051780018318858</v>
+        <v>-0.06815126376024458</v>
       </c>
       <c r="AD26">
-        <v>709.8</v>
+        <v>0</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>709.8</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>430.6999999999999</v>
+        <v>-0.407</v>
       </c>
       <c r="AH26">
-        <v>0.5751559841179807</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>0.5583700440528635</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>0.4509947643979058</v>
+        <v>-0.2138728323699422</v>
       </c>
       <c r="AK26">
-        <v>0.4341296240298357</v>
+        <v>-0.009251471825063078</v>
       </c>
       <c r="AL26">
-        <v>28.8</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>18.2</v>
-      </c>
-      <c r="AN26">
-        <v>13.86328125</v>
-      </c>
-      <c r="AO26">
-        <v>-2.055555555555556</v>
-      </c>
-      <c r="AP26">
-        <v>8.412109374999998</v>
+        <v>-2.74</v>
       </c>
       <c r="AQ26">
-        <v>-3.252747252747252</v>
+        <v>0.1448905109489051</v>
       </c>
     </row>
     <row r="27">
@@ -3710,7 +3647,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deutsche Effecten- und Wechsel-Beteiligungsgesellschaft AG (XTRA:EFF)</t>
+          <t>AURELIUS Equity Opportunities SE &amp; Co. KGaA (LSE:0W1D)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3718,98 +3655,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D27">
+        <v>0.0131</v>
+      </c>
+      <c r="E27">
+        <v>-0.06559999999999999</v>
+      </c>
+      <c r="G27">
+        <v>0.007582054886620622</v>
+      </c>
+      <c r="H27">
+        <v>0.007181712609253713</v>
+      </c>
+      <c r="I27">
+        <v>-0.008801418006234338</v>
+      </c>
+      <c r="J27">
+        <v>-0.006092848899566256</v>
+      </c>
       <c r="K27">
-        <v>8.58</v>
+        <v>186.6</v>
+      </c>
+      <c r="L27">
+        <v>0.05702585416539332</v>
       </c>
       <c r="M27">
-        <v>-0</v>
+        <v>14.5782</v>
       </c>
       <c r="N27">
-        <v>-0</v>
+        <v>0.03680434233779348</v>
       </c>
       <c r="O27">
-        <v>-0</v>
+        <v>0.07812540192926046</v>
       </c>
       <c r="P27">
-        <v>-0</v>
+        <v>14.5782</v>
       </c>
       <c r="Q27">
-        <v>-0</v>
+        <v>0.03680434233779348</v>
       </c>
       <c r="R27">
-        <v>-0</v>
+        <v>0.07812540192926046</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
       <c r="U27">
-        <v>0.9409999999999999</v>
+        <v>349.6</v>
       </c>
       <c r="V27">
-        <v>0.04776649746192893</v>
+        <v>0.8826054026760919</v>
       </c>
       <c r="W27">
-        <v>0.5107142857142857</v>
+        <v>0.2914714151827554</v>
       </c>
       <c r="X27">
-        <v>0.08960231572994104</v>
+        <v>0.09380345681223146</v>
       </c>
       <c r="Y27">
-        <v>0.4211119699843446</v>
+        <v>0.1976679583705239</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.251068057625435</v>
       </c>
       <c r="AA27">
-        <v>-0.0401861146433775</v>
+        <v>-0.01980826643731813</v>
       </c>
       <c r="AB27">
-        <v>0.06807462019575811</v>
+        <v>0.05557335998381986</v>
       </c>
       <c r="AC27">
-        <v>-0.1082607348391356</v>
+        <v>-0.07538162642113799</v>
       </c>
       <c r="AD27">
-        <v>14.3</v>
+        <v>758.1</v>
       </c>
       <c r="AE27">
-        <v>0.03984947959642204</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>14.33984947959642</v>
+        <v>758.1</v>
       </c>
       <c r="AG27">
-        <v>13.39884947959642</v>
+        <v>408.5</v>
       </c>
       <c r="AH27">
-        <v>0.4212665360988676</v>
+        <v>0.6568185756368047</v>
       </c>
       <c r="AI27">
-        <v>0.3720785024650435</v>
+        <v>0.5232245151494237</v>
       </c>
       <c r="AJ27">
-        <v>0.4048131488031346</v>
+        <v>0.5077056922694506</v>
       </c>
       <c r="AK27">
-        <v>0.3563632841177097</v>
+        <v>0.3716001091603748</v>
       </c>
       <c r="AL27">
-        <v>0.636</v>
+        <v>40.5</v>
       </c>
       <c r="AM27">
-        <v>0.63</v>
+        <v>35.04</v>
       </c>
       <c r="AN27">
-        <v>-10.31746031746032</v>
+        <v>19.48843187660669</v>
       </c>
       <c r="AO27">
-        <v>-2.20125786163522</v>
+        <v>-0.7111111111111111</v>
       </c>
       <c r="AP27">
-        <v>-9.667279566808386</v>
+        <v>10.5012853470437</v>
       </c>
       <c r="AQ27">
-        <v>-2.222222222222222</v>
+        <v>-0.8219178082191781</v>
       </c>
     </row>
     <row r="28">
@@ -3820,7 +3781,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Murphy &amp; Spitz Green Capital Aktiengesellschaft (DUSE:6MP)</t>
+          <t>Deutsche Effecten- und Wechsel-Beteiligungsgesellschaft AG (XTRA:EFF)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3828,23 +3789,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G28">
-        <v>-0.7310344827586207</v>
-      </c>
-      <c r="H28">
-        <v>-0.7310344827586207</v>
-      </c>
-      <c r="I28">
-        <v>-0.7632183908045977</v>
-      </c>
-      <c r="J28">
-        <v>-0.7632183908045977</v>
-      </c>
       <c r="K28">
-        <v>-0.007</v>
-      </c>
-      <c r="L28">
-        <v>-0.01609195402298851</v>
+        <v>-5.31</v>
       </c>
       <c r="M28">
         <v>-0</v>
@@ -3868,73 +3814,73 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>0.089</v>
+        <v>0.003</v>
       </c>
       <c r="V28">
-        <v>0.008396226415094339</v>
+        <v>0.000234375</v>
       </c>
       <c r="W28">
-        <v>-0.001988636363636364</v>
+        <v>-0.2469767441860465</v>
       </c>
       <c r="X28">
-        <v>0.07245421904070486</v>
+        <v>0.08262110550501774</v>
       </c>
       <c r="Y28">
-        <v>-0.07444285540434122</v>
+        <v>-0.3295978496910642</v>
       </c>
       <c r="Z28">
-        <v>0.123614663256607</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>-0.09434498437055983</v>
+        <v>-0.02494592240919179</v>
       </c>
       <c r="AB28">
-        <v>0.07245421904070486</v>
+        <v>0.05664358218406389</v>
       </c>
       <c r="AC28">
-        <v>-0.1667992034112647</v>
+        <v>-0.08158950459325567</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AG28">
-        <v>-0.089</v>
+        <v>15.797</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>0.5524475524475524</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>0.4802431610942249</v>
       </c>
       <c r="AJ28">
-        <v>-0.008467319950528018</v>
+        <v>0.5524006014616918</v>
       </c>
       <c r="AK28">
-        <v>-0.02372700613169821</v>
+        <v>0.4801957625315378</v>
       </c>
       <c r="AL28">
-        <v>0.002</v>
+        <v>0.669</v>
       </c>
       <c r="AM28">
-        <v>-0.324</v>
+        <v>0.669</v>
       </c>
       <c r="AN28">
-        <v>-0</v>
+        <v>-17.87330316742081</v>
       </c>
       <c r="AO28">
-        <v>-166</v>
+        <v>-1.327354260089686</v>
       </c>
       <c r="AP28">
-        <v>0.278125</v>
+        <v>-17.86990950226244</v>
       </c>
       <c r="AQ28">
-        <v>1.024691358024691</v>
+        <v>-1.327354260089686</v>
       </c>
     </row>
     <row r="29">
@@ -3945,7 +3891,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deutsche Beteiligungs AG (XTRA:DBAN)</t>
+          <t>Mountain Alliance AG (XTRA:ECF)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3953,104 +3899,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F29">
-        <v>-0.058</v>
+      <c r="D29">
+        <v>-0.0731</v>
+      </c>
+      <c r="G29">
+        <v>-0.1008196721311476</v>
+      </c>
+      <c r="H29">
+        <v>-0.1008196721311476</v>
+      </c>
+      <c r="I29">
+        <v>-0.106560810241091</v>
+      </c>
+      <c r="J29">
+        <v>-0.106560810241091</v>
       </c>
       <c r="K29">
-        <v>-95.7</v>
+        <v>-2.81</v>
+      </c>
+      <c r="L29">
+        <v>-0.230327868852459</v>
       </c>
       <c r="M29">
-        <v>29.5</v>
+        <v>-0</v>
       </c>
       <c r="N29">
-        <v>0.05261280542179418</v>
+        <v>-0</v>
       </c>
       <c r="O29">
-        <v>-0.3082549634273772</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>29.5</v>
+        <v>-0</v>
       </c>
       <c r="Q29">
-        <v>0.05261280542179418</v>
+        <v>-0</v>
       </c>
       <c r="R29">
-        <v>-0.3082549634273772</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <v>0</v>
       </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
       <c r="U29">
-        <v>18.8</v>
+        <v>1.76</v>
       </c>
       <c r="V29">
-        <v>0.03352951667558409</v>
+        <v>0.09166666666666667</v>
       </c>
       <c r="W29">
-        <v>-0.1181627361402642</v>
+        <v>-0.06082251082251082</v>
       </c>
       <c r="X29">
-        <v>0.07420205363757543</v>
+        <v>0.06516691870783228</v>
       </c>
       <c r="Y29">
-        <v>-0.1923647897778397</v>
+        <v>-0.1259894295303431</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>0.2822427042545861</v>
       </c>
       <c r="AA29">
-        <v>-0.1207601011738764</v>
+        <v>-0.03007601125000531</v>
       </c>
       <c r="AB29">
-        <v>0.07136388423474771</v>
+        <v>0.06079079479926489</v>
       </c>
       <c r="AC29">
-        <v>-0.1921239854086241</v>
+        <v>-0.09086680604927019</v>
       </c>
       <c r="AD29">
-        <v>41.6</v>
+        <v>3.3</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>0.03520942470654848</v>
       </c>
       <c r="AF29">
-        <v>41.6</v>
+        <v>3.335209424706548</v>
       </c>
       <c r="AG29">
-        <v>22.8</v>
+        <v>1.575209424706548</v>
       </c>
       <c r="AH29">
-        <v>0.06906857047982733</v>
+        <v>0.1479999303245871</v>
       </c>
       <c r="AI29">
-        <v>0.06820790293490736</v>
+        <v>0.07260681874485336</v>
       </c>
       <c r="AJ29">
-        <v>0.0390745501285347</v>
+        <v>0.07582159065184964</v>
       </c>
       <c r="AK29">
-        <v>0.03857215361191001</v>
+        <v>0.0356582220032568</v>
       </c>
       <c r="AL29">
-        <v>1</v>
+        <v>0.12</v>
       </c>
       <c r="AM29">
-        <v>0.973</v>
+        <v>0.103</v>
       </c>
       <c r="AN29">
-        <v>-0.449244060475162</v>
+        <v>-2.766135792120704</v>
       </c>
       <c r="AO29">
-        <v>-93.09999999999999</v>
+        <v>-11.08333333333333</v>
       </c>
       <c r="AP29">
-        <v>-0.24622030237581</v>
+        <v>-1.320376718111105</v>
       </c>
       <c r="AQ29">
-        <v>-95.68345323741006</v>
+        <v>-12.9126213592233</v>
       </c>
     </row>
     <row r="30">
@@ -4061,7 +4019,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deutsche Balaton AG (DB:BBHK)</t>
+          <t>MPC Münchmeyer Petersen Capital AG (XTRA:MPCK)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4069,8 +4027,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D30">
+        <v>-0.0318</v>
+      </c>
+      <c r="F30">
+        <v>-0.168</v>
+      </c>
+      <c r="G30">
+        <v>-0.2010204081632653</v>
+      </c>
+      <c r="H30">
+        <v>-0.2010204081632653</v>
+      </c>
+      <c r="I30">
+        <v>-0.1081632653061224</v>
+      </c>
+      <c r="J30">
+        <v>-0.09441272253582282</v>
+      </c>
       <c r="K30">
-        <v>-44.3</v>
+        <v>14.1</v>
+      </c>
+      <c r="L30">
+        <v>0.3596938775510204</v>
       </c>
       <c r="M30">
         <v>-0</v>
@@ -4079,7 +4058,7 @@
         <v>-0</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P30">
         <v>-0</v>
@@ -4088,79 +4067,79 @@
         <v>-0</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S30">
         <v>0</v>
       </c>
       <c r="U30">
-        <v>99.7</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>0.5368874528809909</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>-0.08670972793110197</v>
+        <v>0.1191885038038884</v>
       </c>
       <c r="X30">
-        <v>0.08217042843635584</v>
+        <v>0.06248981416997974</v>
       </c>
       <c r="Y30">
-        <v>-0.1688801563674578</v>
+        <v>0.05669868963390867</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>0.6013192207393773</v>
       </c>
       <c r="AA30">
-        <v>-0.2214360815669685</v>
+        <v>-0.05677218474312403</v>
       </c>
       <c r="AB30">
-        <v>0.06784455644733374</v>
+        <v>0.06215220610951311</v>
       </c>
       <c r="AC30">
-        <v>-0.2892806380143022</v>
+        <v>-0.1189243908526371</v>
       </c>
       <c r="AD30">
-        <v>76.09999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>0.4898488554217279</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>76.58984885542172</v>
+        <v>1.28</v>
       </c>
       <c r="AG30">
-        <v>-23.11015114457828</v>
+        <v>1.28</v>
       </c>
       <c r="AH30">
-        <v>0.2920046246152639</v>
+        <v>0.01090475379110581</v>
       </c>
       <c r="AI30">
-        <v>0.1237936083760113</v>
+        <v>0.009809932556713674</v>
       </c>
       <c r="AJ30">
-        <v>-0.1421377245090394</v>
+        <v>0.01090475379110581</v>
       </c>
       <c r="AK30">
-        <v>-0.04452910051236132</v>
+        <v>0.009809932556713674</v>
       </c>
       <c r="AL30">
-        <v>1.85</v>
+        <v>0.531</v>
       </c>
       <c r="AM30">
-        <v>-0.9199999999999999</v>
+        <v>-3.099</v>
       </c>
       <c r="AN30">
-        <v>-0.7601866003376386</v>
+        <v>-0.3890577507598784</v>
       </c>
       <c r="AO30">
-        <v>-58.21621621621622</v>
+        <v>-7.984934086629002</v>
       </c>
       <c r="AP30">
-        <v>0.2308544971338496</v>
+        <v>-0.3890577507598784</v>
       </c>
       <c r="AQ30">
-        <v>117.0652173913044</v>
+        <v>1.368183284930623</v>
       </c>
     </row>
     <row r="31">
@@ -4171,7 +4150,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sparta AG (DB:SPT6)</t>
+          <t>Heidelberger Beteiligungsholding AG (DB:IPOK)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4180,7 +4159,7 @@
         </is>
       </c>
       <c r="K31">
-        <v>-37.9</v>
+        <v>-0.961</v>
       </c>
       <c r="M31">
         <v>-0</v>
@@ -4204,67 +4183,73 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>2.12</v>
+        <v>6.54</v>
       </c>
       <c r="V31">
-        <v>0.03002832861189802</v>
+        <v>0.2477272727272727</v>
       </c>
       <c r="W31">
-        <v>-0.2255952380952381</v>
+        <v>-0.03987551867219916</v>
       </c>
       <c r="X31">
-        <v>0.07462315242080694</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y31">
-        <v>-0.300218390516045</v>
+        <v>-0.1021839072080008</v>
       </c>
       <c r="Z31">
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>-0.2275202710879826</v>
+        <v>-0.1294691224268689</v>
       </c>
       <c r="AB31">
-        <v>0.07112334060841725</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC31">
-        <v>-0.2986436116963999</v>
+        <v>-0.1917775109626705</v>
       </c>
       <c r="AD31">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>4.38</v>
+        <v>-6.54</v>
       </c>
       <c r="AH31">
-        <v>0.08430609597924774</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>0.05569837189374464</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>0.05841557748732996</v>
+        <v>-0.3293051359516617</v>
       </c>
       <c r="AK31">
-        <v>0.0382265665910281</v>
+        <v>-0.3703284258210646</v>
       </c>
       <c r="AL31">
-        <v>0.08</v>
+        <v>0.004</v>
       </c>
       <c r="AM31">
-        <v>-0.09499999999999999</v>
+        <v>-1.146</v>
+      </c>
+      <c r="AN31">
+        <v>-0</v>
       </c>
       <c r="AO31">
-        <v>-470</v>
+        <v>-597.5</v>
+      </c>
+      <c r="AP31">
+        <v>2.736401673640167</v>
       </c>
       <c r="AQ31">
-        <v>395.7894736842106</v>
+        <v>2.085514834205934</v>
       </c>
     </row>
     <row r="32">
@@ -4275,7 +4260,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mutares SE &amp; Co. KGaA (XTRA:MUX)</t>
+          <t>AdCapital AG (DB:ADC)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4284,31 +4269,25 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.329</v>
-      </c>
-      <c r="E32">
-        <v>0.07139999999999999</v>
-      </c>
-      <c r="F32">
-        <v>-0.254</v>
+        <v>0.00222</v>
       </c>
       <c r="G32">
-        <v>-0.05668152109328581</v>
+        <v>-0.01939875212705616</v>
       </c>
       <c r="H32">
-        <v>-0.05802139037433155</v>
+        <v>-0.03114010209869541</v>
       </c>
       <c r="I32">
-        <v>-0.07620320855614973</v>
+        <v>-0.04322178105501985</v>
       </c>
       <c r="J32">
-        <v>-0.07620320855614973</v>
+        <v>-0.04322178105501985</v>
       </c>
       <c r="K32">
-        <v>67.59999999999999</v>
+        <v>-12.5</v>
       </c>
       <c r="L32">
-        <v>0.02008318478906714</v>
+        <v>-0.07090187180941576</v>
       </c>
       <c r="M32">
         <v>-0</v>
@@ -4317,7 +4296,7 @@
         <v>-0</v>
       </c>
       <c r="O32">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P32">
         <v>-0</v>
@@ -4326,79 +4305,79 @@
         <v>-0</v>
       </c>
       <c r="R32">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
       <c r="U32">
-        <v>204.7</v>
+        <v>6.26</v>
       </c>
       <c r="V32">
-        <v>0.5158770161290323</v>
+        <v>0.3277486910994764</v>
       </c>
       <c r="W32">
-        <v>0.1100439524662217</v>
+        <v>-0.2155172413793103</v>
       </c>
       <c r="X32">
-        <v>0.1009042473547523</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y32">
-        <v>0.009139705111469401</v>
+        <v>-0.2778256299151119</v>
       </c>
       <c r="Z32">
-        <v>4.231301068510371</v>
+        <v>3.480750246791708</v>
       </c>
       <c r="AA32">
-        <v>-0.322438717787555</v>
+        <v>-0.1504442250740375</v>
       </c>
       <c r="AB32">
-        <v>0.06676712939539466</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC32">
-        <v>-0.3892058471829496</v>
+        <v>-0.2127526136098392</v>
       </c>
       <c r="AD32">
-        <v>479.2</v>
+        <v>0</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>479.2</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>274.5</v>
+        <v>-6.26</v>
       </c>
       <c r="AH32">
-        <v>0.5470319634703196</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>0.3962295353067636</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>0.4089080887829585</v>
+        <v>-0.4875389408099688</v>
       </c>
       <c r="AK32">
-        <v>0.2732158853389071</v>
+        <v>-0.1308528428093645</v>
       </c>
       <c r="AL32">
-        <v>32</v>
+        <v>2.18</v>
       </c>
       <c r="AM32">
-        <v>25.43</v>
+        <v>2.124</v>
       </c>
       <c r="AN32">
-        <v>-2.752441125789776</v>
+        <v>-0</v>
       </c>
       <c r="AO32">
-        <v>-8.015625</v>
+        <v>-3.495412844036697</v>
       </c>
       <c r="AP32">
-        <v>-1.576680068925905</v>
+        <v>1.758426966292135</v>
       </c>
       <c r="AQ32">
-        <v>-10.08651199370822</v>
+        <v>-3.587570621468926</v>
       </c>
     </row>
     <row r="33">
@@ -4409,7 +4388,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lloyd Fonds AG (XTRA:L1OA)</t>
+          <t>Sparta AG (DB:SPT6)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4417,29 +4396,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D33">
-        <v>0.174</v>
-      </c>
-      <c r="F33">
-        <v>0.154</v>
-      </c>
-      <c r="G33">
-        <v>0.1488636363636364</v>
-      </c>
-      <c r="H33">
-        <v>0.1488636363636364</v>
-      </c>
-      <c r="I33">
-        <v>-0.8806818181818181</v>
-      </c>
-      <c r="J33">
-        <v>-0.8806818181818181</v>
-      </c>
       <c r="K33">
-        <v>-5.58</v>
-      </c>
-      <c r="L33">
-        <v>-0.3170454545454545</v>
+        <v>-20.4</v>
       </c>
       <c r="M33">
         <v>-0</v>
@@ -4463,73 +4421,67 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>12.9</v>
+        <v>2.28</v>
       </c>
       <c r="V33">
-        <v>0.08939708939708939</v>
+        <v>0.02111111111111111</v>
       </c>
       <c r="W33">
-        <v>-0.1125</v>
+        <v>-0.1851179673321234</v>
       </c>
       <c r="X33">
-        <v>0.0757030289591873</v>
+        <v>0.0695154509841386</v>
       </c>
       <c r="Y33">
-        <v>-0.1882030289591873</v>
+        <v>-0.254633418316262</v>
       </c>
       <c r="Z33">
-        <v>0.3836930455635492</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>-0.3379114889906257</v>
+        <v>-0.1649502530982719</v>
       </c>
       <c r="AB33">
-        <v>0.07119425748362197</v>
+        <v>0.05794618439334816</v>
       </c>
       <c r="AC33">
-        <v>-0.4091057464742476</v>
+        <v>-0.2228964374916201</v>
       </c>
       <c r="AD33">
-        <v>19.9</v>
+        <v>47.3</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>19.9</v>
+        <v>47.3</v>
       </c>
       <c r="AG33">
-        <v>6.999999999999998</v>
+        <v>45.02</v>
       </c>
       <c r="AH33">
-        <v>0.1211936662606577</v>
+        <v>0.3045717965228589</v>
       </c>
       <c r="AI33">
-        <v>0.2363420427553444</v>
+        <v>0.2331197634302612</v>
       </c>
       <c r="AJ33">
-        <v>0.046265697290152</v>
+        <v>0.294209907201673</v>
       </c>
       <c r="AK33">
-        <v>0.0981767180925666</v>
+        <v>0.2244043465257701</v>
       </c>
       <c r="AL33">
-        <v>3.94</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="AM33">
-        <v>1.97</v>
-      </c>
-      <c r="AN33">
-        <v>-1.631147540983606</v>
+        <v>0.781</v>
       </c>
       <c r="AO33">
-        <v>-3.934010152284264</v>
-      </c>
-      <c r="AP33">
-        <v>-0.5737704918032785</v>
+        <v>-23.42007434944238</v>
       </c>
       <c r="AQ33">
-        <v>-7.868020304568528</v>
+        <v>-24.19974391805377</v>
       </c>
     </row>
     <row r="34">
@@ -4540,7 +4492,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Heidelberger Beteiligungsholding AG (DB:IPOK)</t>
+          <t>Heliad AG (XTRA:A7A)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4548,8 +4500,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D34">
+        <v>-0.166</v>
+      </c>
+      <c r="G34">
+        <v>-0.959090909090909</v>
+      </c>
+      <c r="H34">
+        <v>-0.959090909090909</v>
+      </c>
+      <c r="I34">
+        <v>-5.863636363636363</v>
+      </c>
+      <c r="J34">
+        <v>-5.863636363636363</v>
+      </c>
       <c r="K34">
-        <v>-7.93</v>
+        <v>-8.33</v>
+      </c>
+      <c r="L34">
+        <v>-3.786363636363636</v>
       </c>
       <c r="M34">
         <v>-0</v>
@@ -4573,73 +4543,73 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>5.64</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="V34">
-        <v>0.2028776978417266</v>
+        <v>0.142687074829932</v>
       </c>
       <c r="W34">
-        <v>-0.2178571428571429</v>
+        <v>-0.1345718901453958</v>
       </c>
       <c r="X34">
-        <v>0.07245421904070486</v>
+        <v>0.06232490038013035</v>
       </c>
       <c r="Y34">
-        <v>-0.2903113618978477</v>
+        <v>-0.1968967905255262</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>0.03694374475230899</v>
       </c>
       <c r="AA34">
-        <v>-0.3555641721597519</v>
+        <v>-0.216624685138539</v>
       </c>
       <c r="AB34">
-        <v>0.07245421904070486</v>
+        <v>0.06229810995517533</v>
       </c>
       <c r="AC34">
-        <v>-0.4280183912004568</v>
+        <v>-0.2789227950937144</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AG34">
-        <v>-5.64</v>
+        <v>-8.331000000000001</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>0.001002395555480046</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>0.001046860306250998</v>
       </c>
       <c r="AJ34">
-        <v>-0.2545126353790614</v>
+        <v>-0.1650716281281579</v>
       </c>
       <c r="AK34">
-        <v>-0.3055254604550379</v>
+        <v>-0.1736746648877401</v>
       </c>
       <c r="AL34">
-        <v>0.002</v>
+        <v>0.021</v>
       </c>
       <c r="AM34">
-        <v>-1.228</v>
+        <v>-3.879</v>
       </c>
       <c r="AN34">
-        <v>-0</v>
+        <v>-0.004609375</v>
       </c>
       <c r="AO34">
-        <v>-4585</v>
+        <v>-614.2857142857142</v>
       </c>
       <c r="AP34">
-        <v>0.6150490730643402</v>
+        <v>0.650859375</v>
       </c>
       <c r="AQ34">
-        <v>7.46742671009772</v>
+        <v>3.325599381283836</v>
       </c>
     </row>
     <row r="35">
@@ -4650,7 +4620,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Panamax AG (DB:ICP)</t>
+          <t>Mutares SE &amp; Co. KGaA (XTRA:MUX)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4658,107 +4628,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D35">
+        <v>0.375</v>
+      </c>
+      <c r="E35">
+        <v>0.7240000000000001</v>
+      </c>
       <c r="G35">
-        <v>0</v>
+        <v>-0.03211701859173888</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>-0.03282998233364179</v>
       </c>
       <c r="I35">
-        <v>-40.61083623480545</v>
+        <v>-0.05705813073105073</v>
       </c>
       <c r="J35">
-        <v>-40.61083623480545</v>
+        <v>-0.05705813073105073</v>
       </c>
       <c r="K35">
-        <v>-0.125</v>
+        <v>308.6</v>
       </c>
       <c r="L35">
-        <v>-41.66666666666666</v>
+        <v>0.06490283502986456</v>
       </c>
       <c r="M35">
-        <v>-0</v>
+        <v>21.836</v>
       </c>
       <c r="N35">
-        <v>-0</v>
+        <v>0.0270548878701524</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>0.07075826312378483</v>
       </c>
       <c r="P35">
-        <v>-0</v>
+        <v>21.836</v>
       </c>
       <c r="Q35">
-        <v>-0</v>
+        <v>0.0270548878701524</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>0.07075826312378483</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
       <c r="U35">
-        <v>0.003</v>
+        <v>386.7</v>
       </c>
       <c r="V35">
-        <v>0.001863354037267081</v>
+        <v>0.4791227852806343</v>
+      </c>
+      <c r="W35">
+        <v>0.422623938646946</v>
       </c>
       <c r="X35">
-        <v>0.07258828784360143</v>
+        <v>0.07585272722125957</v>
+      </c>
+      <c r="Y35">
+        <v>0.3467712114256865</v>
       </c>
       <c r="Z35">
-        <v>2.580548549810843</v>
+        <v>4.732556982183737</v>
       </c>
       <c r="AA35">
-        <v>-104.7982345523329</v>
+        <v>-0.2700308549815865</v>
       </c>
       <c r="AB35">
-        <v>0.07253957512335406</v>
+        <v>0.05584217858521041</v>
       </c>
       <c r="AC35">
-        <v>-104.8707741274562</v>
+        <v>-0.3258730335667969</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>664.3</v>
       </c>
       <c r="AE35">
-        <v>0.009162543522081731</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>0.009162543522081731</v>
+        <v>664.3</v>
       </c>
       <c r="AG35">
-        <v>0.006162543522081731</v>
+        <v>277.6</v>
       </c>
       <c r="AH35">
-        <v>0.005658816379330834</v>
+        <v>0.4514747859181731</v>
       </c>
       <c r="AI35">
-        <v>1</v>
+        <v>0.372511635731509</v>
       </c>
       <c r="AJ35">
-        <v>0.003813071616331226</v>
+        <v>0.2559232967640822</v>
       </c>
       <c r="AK35">
-        <v>1</v>
+        <v>0.1987684376342546</v>
       </c>
       <c r="AL35">
-        <v>0.003</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AM35">
-        <v>0.003</v>
+        <v>71.5</v>
       </c>
       <c r="AN35">
-        <v>0</v>
+        <v>-4.731481481481481</v>
       </c>
       <c r="AO35">
-        <v>-43.33333333333334</v>
+        <v>-3.612516644474035</v>
       </c>
       <c r="AP35">
-        <v>0.616254352208173</v>
+        <v>-1.977207977207977</v>
       </c>
       <c r="AQ35">
-        <v>-43.33333333333334</v>
+        <v>-3.794405594405595</v>
       </c>
     </row>
     <row r="36">
@@ -4769,7 +4754,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tio Tech A (NasdaqCM:TIOA)</t>
+          <t>Deutsche Balaton AG (HMSE:BBHK)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4778,7 +4763,7 @@
         </is>
       </c>
       <c r="K36">
-        <v>11.4</v>
+        <v>-131.2</v>
       </c>
       <c r="M36">
         <v>-0</v>
@@ -4787,7 +4772,7 @@
         <v>-0</v>
       </c>
       <c r="O36">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P36">
         <v>-0</v>
@@ -4796,61 +4781,79 @@
         <v>-0</v>
       </c>
       <c r="R36">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
       </c>
       <c r="U36">
-        <v>0.021</v>
+        <v>37.1</v>
       </c>
       <c r="V36">
-        <v>4.830917874396136e-05</v>
+        <v>0.1904517453798768</v>
       </c>
       <c r="W36">
-        <v>-0.5454545454545455</v>
+        <v>-0.2678644344630461</v>
       </c>
       <c r="X36">
-        <v>0.07245421904070486</v>
+        <v>0.06756835579925993</v>
       </c>
       <c r="Y36">
-        <v>-0.6179087644952503</v>
+        <v>-0.335432790262306</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>-0.321395784897041</v>
       </c>
       <c r="AB36">
-        <v>0.07245421904070486</v>
+        <v>0.06027721699756813</v>
+      </c>
+      <c r="AC36">
+        <v>-0.3816730018946091</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>61.8</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>0.466018140790028</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>62.26601814079002</v>
       </c>
       <c r="AG36">
-        <v>-0.021</v>
+        <v>25.16601814079002</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>0.2422180052856622</v>
       </c>
       <c r="AI36">
-        <v>-0</v>
+        <v>0.1196351269257056</v>
       </c>
       <c r="AJ36">
-        <v>-4.831151263346056e-05</v>
+        <v>0.1144086634540178</v>
       </c>
       <c r="AK36">
-        <v>0.001822758441107543</v>
+        <v>0.0520641029702256</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM36">
-        <v>-1.43</v>
+        <v>-6.58</v>
+      </c>
+      <c r="AN36">
+        <v>-0.3571903338978251</v>
+      </c>
+      <c r="AO36">
+        <v>-93.24607329842932</v>
+      </c>
+      <c r="AP36">
+        <v>-0.1454540197829694</v>
       </c>
       <c r="AQ36">
-        <v>1.510489510489511</v>
+        <v>27.06686930091185</v>
       </c>
     </row>
     <row r="37">
@@ -4861,7 +4864,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>European Healthcare Acquisition &amp; Growth Company B.V. (ENXTAM:EHCS)</t>
+          <t>Laiqon AG (XTRA:LQAG)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4869,8 +4872,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D37">
+        <v>0.341</v>
+      </c>
+      <c r="G37">
+        <v>-0.4647435897435898</v>
+      </c>
+      <c r="H37">
+        <v>-0.4647435897435898</v>
+      </c>
+      <c r="I37">
+        <v>-0.5320512820512822</v>
+      </c>
+      <c r="J37">
+        <v>-0.5320512820512822</v>
+      </c>
       <c r="K37">
-        <v>-5.75</v>
+        <v>-6.77</v>
+      </c>
+      <c r="L37">
+        <v>-0.2169871794871795</v>
       </c>
       <c r="M37">
         <v>-0</v>
@@ -4894,52 +4915,73 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>213.6</v>
+        <v>15.2</v>
       </c>
       <c r="V37">
-        <v>1.004231311706629</v>
+        <v>0.1192156862745098</v>
+      </c>
+      <c r="W37">
+        <v>-0.1161234991423671</v>
       </c>
       <c r="X37">
-        <v>0.07245421904070486</v>
+        <v>0.06781949232666525</v>
+      </c>
+      <c r="Y37">
+        <v>-0.1839429914690323</v>
+      </c>
+      <c r="Z37">
+        <v>0.7918781725888328</v>
+      </c>
+      <c r="AA37">
+        <v>-0.4213197969543149</v>
       </c>
       <c r="AB37">
-        <v>0.07245421904070486</v>
+        <v>0.05973584736574512</v>
+      </c>
+      <c r="AC37">
+        <v>-0.48105564432006</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>42.7</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>42.7</v>
       </c>
       <c r="AG37">
-        <v>-213.6</v>
+        <v>27.5</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>0.2508813160987075</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>0.373578302712161</v>
       </c>
       <c r="AJ37">
-        <v>237.3333333333318</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="AK37">
-        <v>1.004940014114326</v>
+        <v>0.277497477295661</v>
       </c>
       <c r="AL37">
-        <v>1.92</v>
+        <v>3.38</v>
       </c>
       <c r="AM37">
-        <v>1.92</v>
+        <v>2.976</v>
+      </c>
+      <c r="AN37">
+        <v>-3.61864406779661</v>
       </c>
       <c r="AO37">
-        <v>-1.197916666666667</v>
+        <v>-4.911242603550297</v>
+      </c>
+      <c r="AP37">
+        <v>-2.330508474576271</v>
       </c>
       <c r="AQ37">
-        <v>-1.197916666666667</v>
+        <v>-5.577956989247312</v>
       </c>
     </row>
     <row r="38">
@@ -4950,7 +4992,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quirin Privatbank AG (XTRA:QB7)</t>
+          <t>CAMERIT AG (DB:RTML)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4959,106 +5001,112 @@
         </is>
       </c>
       <c r="D38">
-        <v>0.08310000000000001</v>
-      </c>
-      <c r="E38">
-        <v>0.302</v>
+        <v>-0.392</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>-3.474226804123711</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>-3.474226804123711</v>
       </c>
       <c r="I38">
-        <v>-0.02091652089170587</v>
+        <v>-3.288659793814433</v>
       </c>
       <c r="J38">
-        <v>-0.01806279401035685</v>
+        <v>-3.288659793814433</v>
       </c>
       <c r="K38">
-        <v>11.1</v>
+        <v>-0.248</v>
       </c>
       <c r="L38">
-        <v>0.167420814479638</v>
+        <v>-2.556701030927835</v>
       </c>
       <c r="M38">
-        <v>6.336399999999999</v>
+        <v>-0</v>
       </c>
       <c r="N38">
-        <v>0.04138732854343566</v>
+        <v>-0</v>
       </c>
       <c r="O38">
-        <v>0.5708468468468468</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>6.336399999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q38">
-        <v>0.04138732854343566</v>
+        <v>-0</v>
       </c>
       <c r="R38">
-        <v>0.5708468468468468</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
       </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
       <c r="U38">
-        <v>378.2</v>
+        <v>7.53</v>
       </c>
       <c r="V38">
-        <v>2.470280862181581</v>
+        <v>1.494047619047619</v>
       </c>
       <c r="W38">
-        <v>0.1423076923076923</v>
+        <v>-0.03342318059299192</v>
       </c>
       <c r="X38">
-        <v>0.08801752111966646</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y38">
-        <v>0.05429017118802584</v>
+        <v>-0.09573156912879355</v>
+      </c>
+      <c r="Z38">
+        <v>0.9700000000000035</v>
+      </c>
+      <c r="AA38">
+        <v>-3.190000000000011</v>
       </c>
       <c r="AB38">
-        <v>0.0683183542253476</v>
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AC38">
+        <v>-3.252308388535813</v>
       </c>
       <c r="AD38">
-        <v>89.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>11.24382667560049</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>101.1438266756005</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>-277.0561733243995</v>
+        <v>-7.53</v>
       </c>
       <c r="AH38">
-        <v>0.3978221536314973</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>0.5958615912960281</v>
+        <v>0</v>
       </c>
       <c r="AJ38">
-        <v>2.235113959184023</v>
+        <v>3.024096385542169</v>
       </c>
       <c r="AK38">
-        <v>1.329085960401109</v>
+        <v>376.4999999999913</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="AN38">
-        <v>104.292343387471</v>
+        <v>-0</v>
       </c>
       <c r="AP38">
-        <v>-321.4108739262175</v>
+        <v>23.60501567398119</v>
+      </c>
+      <c r="AQ38">
+        <v>4.492957746478874</v>
       </c>
     </row>
     <row r="39">
@@ -5069,7 +5117,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>tokentus investment AG (XTRA:14D)</t>
+          <t>European Healthcare Acquisition &amp; Growth Company B.V. (ENXTAM:EHCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5078,7 +5126,7 @@
         </is>
       </c>
       <c r="K39">
-        <v>-1.57</v>
+        <v>-3.45</v>
       </c>
       <c r="M39">
         <v>-0</v>
@@ -5102,16 +5150,22 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>7.96</v>
+        <v>223</v>
       </c>
       <c r="V39">
-        <v>1.010152284263959</v>
+        <v>1.008593396653098</v>
+      </c>
+      <c r="W39">
+        <v>-3.285714285714286</v>
       </c>
       <c r="X39">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="Y39">
+        <v>-3.348022674250087</v>
       </c>
       <c r="AB39">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -5123,37 +5177,31 @@
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>-7.96</v>
+        <v>-223</v>
       </c>
       <c r="AH39">
         <v>0</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ39">
-        <v>99.49999999999991</v>
+        <v>117.3684210526312</v>
       </c>
       <c r="AK39">
-        <v>-1.411347517730497</v>
+        <v>0.9895278665246716</v>
       </c>
       <c r="AL39">
-        <v>0.002</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AM39">
-        <v>-0.015</v>
-      </c>
-      <c r="AN39">
-        <v>-0</v>
+        <v>5.57</v>
       </c>
       <c r="AO39">
-        <v>-795</v>
-      </c>
-      <c r="AP39">
-        <v>5.070063694267516</v>
+        <v>-0.5694143167028199</v>
       </c>
       <c r="AQ39">
-        <v>106</v>
+        <v>-0.9425493716337522</v>
       </c>
     </row>
     <row r="40">
@@ -5164,7 +5212,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NABAG Anlage- Und Beteiligungs AG (HMSE:NAB)</t>
+          <t>tokentus investment AG (XTRA:14D)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5172,11 +5220,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="E40">
-        <v>0.598</v>
+      <c r="G40">
+        <v>-228</v>
+      </c>
+      <c r="H40">
+        <v>-228</v>
+      </c>
+      <c r="I40">
+        <v>-222</v>
+      </c>
+      <c r="J40">
+        <v>-222</v>
       </c>
       <c r="K40">
-        <v>0.097</v>
+        <v>-2.57</v>
+      </c>
+      <c r="L40">
+        <v>-514</v>
       </c>
       <c r="M40">
         <v>-0</v>
@@ -5185,7 +5245,7 @@
         <v>-0</v>
       </c>
       <c r="O40">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P40">
         <v>-0</v>
@@ -5194,22 +5254,22 @@
         <v>-0</v>
       </c>
       <c r="R40">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S40">
         <v>0</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>0.6649006622516556</v>
       </c>
       <c r="X40">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB40">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD40">
         <v>0</v>
@@ -5221,22 +5281,34 @@
         <v>0</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>-5.02</v>
       </c>
       <c r="AH40">
         <v>0</v>
       </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>-1.984189723320158</v>
+      </c>
+      <c r="AK40">
+        <v>-0.7514970059880239</v>
       </c>
       <c r="AL40">
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-0.005</v>
+        <v>-0.034</v>
+      </c>
+      <c r="AN40">
+        <v>-0</v>
+      </c>
+      <c r="AP40">
+        <v>4.735849056603773</v>
       </c>
       <c r="AQ40">
-        <v>8.4</v>
+        <v>32.64705882352941</v>
       </c>
     </row>
     <row r="41">
@@ -5247,7 +5319,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lena Beteiligungs AG (HMSE:L1A)</t>
+          <t>Murphy &amp; Spitz Green Capital Aktiengesellschaft (DUSE:6MP)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5256,22 +5328,22 @@
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>-0.8980099502487562</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>-0.8980099502487562</v>
       </c>
       <c r="I41">
-        <v>-4.294117647058823</v>
+        <v>-1.139303482587065</v>
       </c>
       <c r="J41">
-        <v>-4.294117647058823</v>
+        <v>-1.139303482587065</v>
       </c>
       <c r="K41">
-        <v>-0.077</v>
+        <v>1.08</v>
       </c>
       <c r="L41">
-        <v>-4.529411764705882</v>
+        <v>2.686567164179105</v>
       </c>
       <c r="M41">
         <v>-0</v>
@@ -5280,7 +5352,7 @@
         <v>-0</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P41">
         <v>-0</v>
@@ -5289,7 +5361,7 @@
         <v>-0</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -5301,10 +5373,10 @@
         <v>0</v>
       </c>
       <c r="X41">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB41">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD41">
         <v>0</v>
@@ -5325,16 +5397,19 @@
         <v>0</v>
       </c>
       <c r="AL41">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM41">
-        <v>0.001</v>
-      </c>
-      <c r="AO41">
-        <v>-73</v>
+        <v>-1.54</v>
+      </c>
+      <c r="AN41">
+        <v>-0</v>
+      </c>
+      <c r="AP41">
+        <v>-0</v>
       </c>
       <c r="AQ41">
-        <v>-73</v>
+        <v>0.2974025974025974</v>
       </c>
     </row>
     <row r="42">
@@ -5345,7 +5420,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Planet Home Investment AG (BST:ILK1)</t>
+          <t>Quirin Privatbank AG (XTRA:QB7)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5353,92 +5428,315 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D42">
+        <v>0.0407</v>
+      </c>
+      <c r="E42">
+        <v>-0.0109</v>
+      </c>
       <c r="G42">
-        <v>-3.434065934065934</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>-3.434065934065934</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>-5.549450549450549</v>
+        <v>-0.01922863451432182</v>
       </c>
       <c r="J42">
-        <v>-5.549450549450549</v>
+        <v>-0.009930280735095776</v>
       </c>
       <c r="K42">
-        <v>-2.04</v>
+        <v>4.08</v>
       </c>
       <c r="L42">
-        <v>-5.604395604395605</v>
+        <v>0.05738396624472574</v>
       </c>
       <c r="M42">
-        <v>-0</v>
+        <v>4.2532</v>
       </c>
       <c r="N42">
-        <v>-0</v>
+        <v>0.0250335491465568</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>1.042450980392157</v>
       </c>
       <c r="P42">
-        <v>-0</v>
+        <v>4.2532</v>
       </c>
       <c r="Q42">
-        <v>-0</v>
+        <v>0.0250335491465568</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.042450980392157</v>
       </c>
       <c r="S42">
         <v>0</v>
       </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>0.01618599175985874</v>
+      </c>
+      <c r="W42">
+        <v>0.05947521865889213</v>
       </c>
       <c r="X42">
-        <v>0.07245421904070486</v>
+        <v>0.07185703460503594</v>
+      </c>
+      <c r="Y42">
+        <v>-0.01238181594614381</v>
       </c>
       <c r="AB42">
-        <v>0.07245421904070486</v>
+        <v>0.05854319762706041</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>25.48577956984141</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>98.58577956984141</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>95.83577956984141</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>0.3671918107833947</v>
+      </c>
+      <c r="AI42">
+        <v>0.6048735038727485</v>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>0.3606431159739767</v>
+      </c>
+      <c r="AK42">
+        <v>0.5980922602125189</v>
       </c>
       <c r="AL42">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="AM42">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="AN42">
-        <v>-0</v>
-      </c>
-      <c r="AO42">
-        <v>-112.2222222222222</v>
+        <v>19.59785522788204</v>
       </c>
       <c r="AP42">
-        <v>-0</v>
-      </c>
-      <c r="AQ42">
-        <v>-126.25</v>
+        <v>25.6932384905741</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Elbstein AG (HMSE:EBS)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>-0.75</v>
+      </c>
+      <c r="G43">
+        <v>-124.3333333333333</v>
+      </c>
+      <c r="H43">
+        <v>-124.3333333333333</v>
+      </c>
+      <c r="I43">
+        <v>-124.3333333333333</v>
+      </c>
+      <c r="J43">
+        <v>-124.3333333333333</v>
+      </c>
+      <c r="K43">
+        <v>-24.1</v>
+      </c>
+      <c r="L43">
+        <v>-8033.333333333334</v>
+      </c>
+      <c r="M43">
+        <v>-0</v>
+      </c>
+      <c r="N43">
+        <v>-0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>-0</v>
+      </c>
+      <c r="Q43">
+        <v>-0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AB43">
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43">
+        <v>0</v>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0.062</v>
+      </c>
+      <c r="AM43">
+        <v>0.058</v>
+      </c>
+      <c r="AN43">
+        <v>-0</v>
+      </c>
+      <c r="AO43">
+        <v>-6.016129032258065</v>
+      </c>
+      <c r="AP43">
+        <v>-0</v>
+      </c>
+      <c r="AQ43">
+        <v>-6.431034482758621</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Panamax AG (DB:ICP)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>-1.238636363636364</v>
+      </c>
+      <c r="H44">
+        <v>-1.238636363636364</v>
+      </c>
+      <c r="I44">
+        <v>-1.102272727272727</v>
+      </c>
+      <c r="J44">
+        <v>-1.102272727272727</v>
+      </c>
+      <c r="K44">
+        <v>-0.102</v>
+      </c>
+      <c r="L44">
+        <v>-1.159090909090909</v>
+      </c>
+      <c r="M44">
+        <v>-0</v>
+      </c>
+      <c r="N44">
+        <v>-0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>-0</v>
+      </c>
+      <c r="Q44">
+        <v>-0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0.003</v>
+      </c>
+      <c r="V44">
+        <v>0.002027027027027027</v>
+      </c>
+      <c r="X44">
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AB44">
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>-0.003</v>
+      </c>
+      <c r="AH44">
+        <v>0</v>
+      </c>
+      <c r="AJ44">
+        <v>-0.002031144211238998</v>
+      </c>
+      <c r="AK44">
+        <v>1</v>
+      </c>
+      <c r="AL44">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AM44">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AO44">
+        <v>-10.77777777777778</v>
+      </c>
+      <c r="AQ44">
+        <v>-10.77777777777778</v>
       </c>
     </row>
   </sheetData>
